--- a/rates-nodispo/week-20/Analisis_Rates_NoDispo_OP_7d.xlsx
+++ b/rates-nodispo/week-20/Analisis_Rates_NoDispo_OP_7d.xlsx
@@ -547,7 +547,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -738,10 +738,10 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>0</v>
+        <v>12299</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>0</v>
+        <v>0.7076117599677809</v>
       </c>
     </row>
     <row r="7">
@@ -756,10 +756,10 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>13355</v>
+        <v>1056</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0.7683677578965538</v>
+        <v>0.0607559979287728</v>
       </c>
     </row>
     <row r="8">
@@ -792,10 +792,10 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1050</v>
+        <v>472</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0.06041079339508659</v>
+        <v>0.02715608998331511</v>
       </c>
     </row>
     <row r="10">
@@ -810,10 +810,10 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>2394</v>
+        <v>2972</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>0.1377366089407974</v>
+        <v>0.1709913123525689</v>
       </c>
     </row>
   </sheetData>
@@ -861,7 +861,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -5969,7 +5969,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -9964,7 +9964,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14547,7 +14547,7 @@
     <col width="24" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -14567,7 +14567,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14682,9 +14682,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I7" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -14752,9 +14752,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I9" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I9" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -14962,9 +14962,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I15" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I15" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -14997,9 +14997,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I16" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I16" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -15032,9 +15032,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I17" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I17" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -16152,9 +16152,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I49" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I49" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -16362,9 +16362,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I55" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I55" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -16502,9 +16502,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I59" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I59" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -16572,9 +16572,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I61" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I61" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -16607,9 +16607,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I62" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I62" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -16747,9 +16747,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I66" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I66" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -16817,9 +16817,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I68" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I68" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -16852,9 +16852,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I69" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I69" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -16957,9 +16957,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I72" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I72" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -16992,9 +16992,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I73" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I73" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -17027,9 +17027,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I74" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I74" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -17062,9 +17062,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I75" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I75" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -17097,9 +17097,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I76" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I76" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -17167,9 +17167,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I78" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I78" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -17202,9 +17202,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I79" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I79" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -17237,9 +17237,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I80" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I80" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -17272,9 +17272,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I81" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I81" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -17307,9 +17307,9 @@
           <t>Crítica</t>
         </is>
       </c>
-      <c r="I82" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I82" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -17342,9 +17342,9 @@
           <t>Crítica</t>
         </is>
       </c>
-      <c r="I83" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I83" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -17377,9 +17377,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I84" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I84" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -17412,9 +17412,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I85" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I85" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -17447,9 +17447,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I86" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I86" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -17517,9 +17517,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I88" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I88" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -17552,9 +17552,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I89" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I89" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -17587,9 +17587,9 @@
           <t>Crítica</t>
         </is>
       </c>
-      <c r="I90" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I90" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -17622,9 +17622,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I91" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I91" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -17670,7 +17670,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -18450,9 +18450,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I26" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I26" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -18520,9 +18520,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I28" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I28" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -18625,9 +18625,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I31" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I31" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -18940,9 +18940,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I40" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I40" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -19220,9 +19220,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I48" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I48" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -19290,9 +19290,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I50" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I50" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -19325,9 +19325,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I51" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I51" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -19675,9 +19675,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I61" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I61" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -19850,9 +19850,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I66" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I66" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -20025,9 +20025,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I71" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I71" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -20235,9 +20235,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I77" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I77" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -20305,9 +20305,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I79" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I79" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -20375,9 +20375,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I81" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I81" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -20515,9 +20515,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I85" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I85" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -20830,9 +20830,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I94" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I94" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -20970,9 +20970,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I98" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I98" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -21040,9 +21040,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I100" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I100" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -21145,9 +21145,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I103" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I103" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -21243,7 +21243,7 @@
     <col width="24" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -21263,7 +21263,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -21868,9 +21868,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I21" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I21" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -22708,9 +22708,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I45" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I45" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -23058,9 +23058,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I55" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I55" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -23233,9 +23233,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I60" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I60" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -23513,9 +23513,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I68" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I68" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -23548,9 +23548,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I69" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I69" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -23618,9 +23618,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I71" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I71" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -23653,9 +23653,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I72" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I72" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -23688,9 +23688,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I73" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I73" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -23793,9 +23793,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I76" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I76" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -23933,9 +23933,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I80" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I80" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -23968,9 +23968,9 @@
           <t>Crítica</t>
         </is>
       </c>
-      <c r="I81" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I81" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -24003,9 +24003,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I82" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I82" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -24038,9 +24038,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I83" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I83" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -24073,9 +24073,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I84" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I84" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -24108,9 +24108,9 @@
           <t>Crítica</t>
         </is>
       </c>
-      <c r="I85" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I85" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -24143,9 +24143,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I86" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I86" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -24178,9 +24178,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I87" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I87" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -24213,9 +24213,9 @@
           <t>Crítica</t>
         </is>
       </c>
-      <c r="I88" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I88" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -24248,9 +24248,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I89" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I89" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -24283,9 +24283,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I90" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I90" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -24318,9 +24318,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I91" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I91" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>

--- a/rates-nodispo/week-20/Analisis_Rates_NoDispo_OP_7d.xlsx
+++ b/rates-nodispo/week-20/Analisis_Rates_NoDispo_OP_7d.xlsx
@@ -547,7 +547,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>$650-$1500</t>
+          <t>$650-$1000</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
@@ -806,7 +806,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>≥$1500</t>
+          <t>≥$1000</t>
         </is>
       </c>
       <c r="C10" s="5" t="n">
@@ -861,7 +861,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -5969,7 +5969,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -9964,7 +9964,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14567,7 +14567,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -17670,7 +17670,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -21263,7 +21263,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>

--- a/rates-nodispo/week-20/Analisis_Rates_NoDispo_OP_7d.xlsx
+++ b/rates-nodispo/week-20/Analisis_Rates_NoDispo_OP_7d.xlsx
@@ -547,7 +547,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -674,13 +674,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -700,7 +700,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -781,39 +781,21 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>$650-$1000</t>
+          <t>≥$650</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>472</v>
+        <v>3444</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0.02715608998331511</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>≥$1000</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="n">
-        <v>2972</v>
-      </c>
-      <c r="D10" s="6" t="n">
-        <v>0.1709913123525689</v>
+        <v>0.198147402335884</v>
       </c>
     </row>
   </sheetData>
@@ -861,7 +843,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -5969,7 +5951,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -9964,7 +9946,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14567,7 +14549,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14647,9 +14629,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I6" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -15417,9 +15399,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I28" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I28" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -15872,9 +15854,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I41" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I41" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -15942,9 +15924,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I43" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I43" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -16327,9 +16309,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I54" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I54" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -17670,7 +17652,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -17750,9 +17732,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I6" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -17855,9 +17837,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I9" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I9" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -18030,9 +18012,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I14" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I14" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -18100,9 +18082,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I16" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I16" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -18135,9 +18117,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I17" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I17" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -18170,9 +18152,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I18" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I18" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -18240,9 +18222,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I20" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I20" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -18275,9 +18257,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I21" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I21" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -18380,9 +18362,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I24" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I24" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -18555,9 +18537,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I29" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I29" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -18695,9 +18677,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I33" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I33" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -18730,9 +18712,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I34" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I34" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -18765,9 +18747,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I35" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I35" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -18870,9 +18852,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I38" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I38" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -18905,9 +18887,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I39" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I39" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -18975,9 +18957,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I41" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I41" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -19115,9 +19097,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I45" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I45" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -19150,9 +19132,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I46" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I46" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -19185,9 +19167,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I47" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I47" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -19255,9 +19237,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I49" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I49" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -19465,9 +19447,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I55" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I55" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -19500,9 +19482,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I56" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I56" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -19570,9 +19552,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I58" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I58" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -19710,9 +19692,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I62" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I62" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -19780,9 +19762,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I64" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I64" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -20270,9 +20252,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I78" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I78" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -20340,9 +20322,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I80" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I80" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -20550,9 +20532,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I86" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I86" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -20585,9 +20567,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I87" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I87" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -20935,9 +20917,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I97" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I97" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -21005,9 +20987,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I99" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I99" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -21180,9 +21162,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I104" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I104" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -21263,7 +21245,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -21343,9 +21325,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I6" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -21413,9 +21395,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I8" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -21448,9 +21430,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I9" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I9" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -21483,9 +21465,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I10" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I10" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -21553,9 +21535,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I12" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I12" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -21588,9 +21570,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I13" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I13" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -21658,9 +21640,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I15" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I15" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -21798,9 +21780,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I19" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I19" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -21973,9 +21955,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I24" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I24" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -22043,9 +22025,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I26" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I26" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -22253,9 +22235,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I32" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I32" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -23198,9 +23180,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I59" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I59" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>

--- a/rates-nodispo/week-20/Analisis_Rates_NoDispo_OP_7d.xlsx
+++ b/rates-nodispo/week-20/Analisis_Rates_NoDispo_OP_7d.xlsx
@@ -547,7 +547,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -5951,7 +5951,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -9946,7 +9946,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14549,7 +14549,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -17652,7 +17652,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -21245,7 +21245,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>

--- a/rates-nodispo/week-20/Analisis_Rates_NoDispo_OP_7d.xlsx
+++ b/rates-nodispo/week-20/Analisis_Rates_NoDispo_OP_7d.xlsx
@@ -547,7 +547,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -5951,7 +5951,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -9946,7 +9946,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14549,7 +14549,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -17652,7 +17652,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -21245,7 +21245,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>

--- a/rates-nodispo/week-20/Analisis_Rates_NoDispo_OP_7d.xlsx
+++ b/rates-nodispo/week-20/Analisis_Rates_NoDispo_OP_7d.xlsx
@@ -547,7 +547,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -674,13 +674,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -700,7 +700,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -781,21 +781,39 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>≥$650</t>
+          <t>$650-$1500</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>3444</v>
+        <v>1050</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0.198147402335884</v>
+        <v>0.06041079339508659</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>≥$1500</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>2394</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>0.1377366089407974</v>
       </c>
     </row>
   </sheetData>
@@ -843,7 +861,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -5951,7 +5969,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -9946,7 +9964,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14549,7 +14567,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14629,9 +14647,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I6" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -14664,9 +14682,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I7" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I7" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -14734,9 +14752,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I9" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I9" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -14944,9 +14962,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I15" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I15" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -14979,9 +14997,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I16" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I16" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -15014,9 +15032,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I17" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I17" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -15399,9 +15417,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I28" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I28" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -15854,9 +15872,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I41" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I41" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -15924,9 +15942,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I43" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I43" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -16134,9 +16152,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I49" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I49" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -16309,9 +16327,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I54" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I54" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -17044,9 +17062,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I75" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I75" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -17219,9 +17237,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I80" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I80" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -17652,7 +17670,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -17732,9 +17750,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I6" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -17837,9 +17855,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I9" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I9" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -18012,9 +18030,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I14" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I14" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -18082,9 +18100,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I16" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I16" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -18117,9 +18135,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I17" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I17" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -18152,9 +18170,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I18" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I18" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -18222,9 +18240,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I20" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I20" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -18257,9 +18275,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I21" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I21" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -18362,9 +18380,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I24" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I24" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -18432,9 +18450,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I26" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I26" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -18502,9 +18520,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I28" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I28" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -18537,9 +18555,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I29" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I29" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -18607,9 +18625,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I31" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I31" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -18677,9 +18695,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I33" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I33" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -18712,9 +18730,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I34" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I34" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -18747,9 +18765,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I35" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I35" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -18852,9 +18870,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I38" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I38" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -18887,9 +18905,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I39" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I39" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -18922,9 +18940,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I40" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I40" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -18957,9 +18975,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I41" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I41" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -19097,9 +19115,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I45" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I45" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -19132,9 +19150,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I46" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I46" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -19167,9 +19185,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I47" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I47" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -19202,9 +19220,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I48" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I48" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -19237,9 +19255,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I49" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I49" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -19272,9 +19290,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I50" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I50" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -19307,9 +19325,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I51" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I51" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -19447,9 +19465,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I55" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I55" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -19482,9 +19500,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I56" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I56" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -19552,9 +19570,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I58" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I58" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -19657,9 +19675,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I61" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I61" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -19692,9 +19710,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I62" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I62" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -19762,9 +19780,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I64" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I64" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -19832,9 +19850,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I66" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I66" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -20007,9 +20025,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I71" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I71" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -20217,9 +20235,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I77" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I77" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -20252,9 +20270,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I78" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I78" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -20287,9 +20305,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I79" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I79" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -20322,9 +20340,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I80" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I80" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -20357,9 +20375,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I81" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I81" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -20497,9 +20515,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I85" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I85" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -20532,9 +20550,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I86" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I86" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -20567,9 +20585,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I87" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I87" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -20812,9 +20830,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I94" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I94" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -20917,9 +20935,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I97" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I97" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -20952,9 +20970,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I98" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I98" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -20987,9 +21005,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I99" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I99" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -21022,9 +21040,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I100" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I100" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -21127,9 +21145,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I103" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I103" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -21162,9 +21180,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I104" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I104" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -21245,7 +21263,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -21325,9 +21343,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I6" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -21395,9 +21413,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I8" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I8" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -21430,9 +21448,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I9" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I9" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -21465,9 +21483,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I10" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I10" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -21535,9 +21553,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I12" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I12" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -21570,9 +21588,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I13" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I13" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -21640,9 +21658,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I15" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I15" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -21780,9 +21798,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I19" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I19" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -21850,9 +21868,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I21" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I21" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -21955,9 +21973,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I24" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I24" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -22025,9 +22043,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I26" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I26" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -22235,9 +22253,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I32" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I32" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -22690,9 +22708,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I45" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I45" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -23180,9 +23198,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I59" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I59" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -24055,9 +24073,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I84" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I84" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>

--- a/rates-nodispo/week-20/Analisis_Rates_NoDispo_OP_7d.xlsx
+++ b/rates-nodispo/week-20/Analisis_Rates_NoDispo_OP_7d.xlsx
@@ -547,7 +547,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -861,7 +861,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -5969,7 +5969,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -9964,7 +9964,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14567,7 +14567,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -17670,7 +17670,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -21263,7 +21263,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>

--- a/rates-nodispo/week-20/Analisis_Rates_NoDispo_OP_7d.xlsx
+++ b/rates-nodispo/week-20/Analisis_Rates_NoDispo_OP_7d.xlsx
@@ -547,7 +547,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -861,7 +861,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -5969,7 +5969,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -9964,7 +9964,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14567,7 +14567,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -17670,7 +17670,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -21263,7 +21263,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>

--- a/rates-nodispo/week-20/Analisis_Rates_NoDispo_OP_7d.xlsx
+++ b/rates-nodispo/week-20/Analisis_Rates_NoDispo_OP_7d.xlsx
@@ -547,7 +547,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -674,13 +674,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -700,7 +700,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -781,39 +781,21 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>$650-$1500</t>
+          <t>≥$650</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1050</v>
+        <v>3444</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0.06041079339508659</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>≥$1500</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="n">
-        <v>2394</v>
-      </c>
-      <c r="D10" s="6" t="n">
-        <v>0.1377366089407974</v>
+        <v>0.198147402335884</v>
       </c>
     </row>
   </sheetData>
@@ -861,7 +843,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -5969,7 +5951,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -9964,7 +9946,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14567,7 +14549,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14647,9 +14629,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I6" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -14682,9 +14664,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I7" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -14752,9 +14734,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I9" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I9" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -14962,9 +14944,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I15" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I15" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -14997,9 +14979,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I16" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I16" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -15032,9 +15014,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I17" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I17" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -15417,9 +15399,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I28" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I28" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -15872,9 +15854,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I41" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I41" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -15942,9 +15924,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I43" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I43" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -16152,9 +16134,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I49" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I49" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -16327,9 +16309,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I54" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I54" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -17062,9 +17044,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I75" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I75" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -17237,9 +17219,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I80" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I80" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -17670,7 +17652,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -17750,9 +17732,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I6" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -17855,9 +17837,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I9" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I9" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -18030,9 +18012,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I14" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I14" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -18100,9 +18082,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I16" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I16" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -18135,9 +18117,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I17" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I17" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -18170,9 +18152,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I18" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I18" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -18240,9 +18222,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I20" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I20" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -18275,9 +18257,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I21" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I21" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -18380,9 +18362,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I24" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I24" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -18450,9 +18432,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I26" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I26" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -18520,9 +18502,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I28" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I28" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -18555,9 +18537,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I29" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I29" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -18625,9 +18607,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I31" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I31" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -18695,9 +18677,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I33" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I33" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -18730,9 +18712,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I34" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I34" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -18765,9 +18747,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I35" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I35" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -18870,9 +18852,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I38" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I38" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -18905,9 +18887,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I39" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I39" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -18940,9 +18922,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I40" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I40" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -18975,9 +18957,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I41" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I41" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -19115,9 +19097,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I45" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I45" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -19150,9 +19132,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I46" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I46" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -19185,9 +19167,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I47" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I47" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -19220,9 +19202,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I48" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I48" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -19255,9 +19237,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I49" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I49" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -19290,9 +19272,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I50" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I50" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -19325,9 +19307,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I51" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I51" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -19465,9 +19447,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I55" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I55" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -19500,9 +19482,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I56" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I56" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -19570,9 +19552,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I58" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I58" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -19675,9 +19657,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I61" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I61" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -19710,9 +19692,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I62" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I62" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -19780,9 +19762,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I64" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I64" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -19850,9 +19832,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I66" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I66" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -20025,9 +20007,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I71" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I71" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -20235,9 +20217,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I77" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I77" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -20270,9 +20252,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I78" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I78" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -20305,9 +20287,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I79" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I79" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -20340,9 +20322,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I80" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I80" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -20375,9 +20357,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I81" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I81" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -20515,9 +20497,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I85" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I85" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -20550,9 +20532,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I86" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I86" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -20585,9 +20567,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I87" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I87" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -20830,9 +20812,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I94" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I94" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -20935,9 +20917,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I97" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I97" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -20970,9 +20952,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I98" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I98" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -21005,9 +20987,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I99" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I99" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -21040,9 +21022,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I100" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I100" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -21145,9 +21127,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I103" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I103" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -21180,9 +21162,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I104" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I104" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -21263,7 +21245,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -21343,9 +21325,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I6" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -21413,9 +21395,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I8" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -21448,9 +21430,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I9" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I9" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -21483,9 +21465,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I10" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I10" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -21553,9 +21535,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I12" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I12" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -21588,9 +21570,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I13" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I13" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -21658,9 +21640,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I15" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I15" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -21798,9 +21780,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I19" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I19" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -21868,9 +21850,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I21" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I21" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -21973,9 +21955,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I24" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I24" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -22043,9 +22025,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I26" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I26" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -22253,9 +22235,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I32" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I32" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -22708,9 +22690,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I45" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I45" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -23198,9 +23180,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I59" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I59" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -24073,9 +24055,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I84" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I84" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>

--- a/rates-nodispo/week-20/Analisis_Rates_NoDispo_OP_7d.xlsx
+++ b/rates-nodispo/week-20/Analisis_Rates_NoDispo_OP_7d.xlsx
@@ -547,7 +547,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -674,13 +674,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -700,7 +700,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -752,14 +752,14 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>&lt;$200</t>
+          <t>&lt;$199</t>
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0.0607559979287728</v>
+        <v>0.0606984638398251</v>
       </c>
     </row>
     <row r="8">
@@ -770,31 +770,49 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>$200-$650</t>
+          <t>$200-$499</t>
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>582</v>
+        <v>374</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>0.03348483976756228</v>
+        <v>0.02151774926644037</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
+          <t>$500-$649</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>209</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>0.01202462459006962</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
           <t>≥$650</t>
         </is>
       </c>
-      <c r="C9" s="5" t="n">
+      <c r="C10" s="5" t="n">
         <v>3444</v>
       </c>
-      <c r="D9" s="6" t="n">
+      <c r="D10" s="6" t="n">
         <v>0.198147402335884</v>
       </c>
     </row>
@@ -843,7 +861,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -1015,12 +1033,12 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Wyndham Garden Lake Buena Vista Disney Springs</t>
+          <t>The LINQ Hotel + Experience</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Wyndham</t>
+          <t>Caesars Entertainment</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
@@ -1030,23 +1048,23 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>Orlando</t>
+          <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
       <c r="F8" s="12" t="n">
-        <v>3077012</v>
+        <v>2684945</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="H8" s="13" t="n">
-        <v>1694.91</v>
+        <v>864.6000000000003</v>
       </c>
       <c r="I8" s="14" t="n">
-        <v>0.002336032488661078</v>
+        <v>0.01319095921890392</v>
       </c>
       <c r="J8" s="13" t="n">
-        <v>550.8298310178836</v>
+        <v>322.0177694515158</v>
       </c>
       <c r="K8" s="10" t="inlineStr">
         <is>
@@ -1065,12 +1083,12 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>The LINQ Hotel + Experience</t>
+          <t>Hilton Los Angeles Airport</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Caesars Entertainment</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
@@ -1080,23 +1098,23 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>Las Vegas (and vicinity), NV, US</t>
+          <t>Los Angeles (and vicinity), CA, US</t>
         </is>
       </c>
       <c r="F9" s="12" t="n">
-        <v>2684945</v>
+        <v>2664974</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="H9" s="13" t="n">
-        <v>864.6000000000003</v>
+        <v>1292</v>
       </c>
       <c r="I9" s="14" t="n">
-        <v>0.01319095921890392</v>
+        <v>0.01183276084494633</v>
       </c>
       <c r="J9" s="13" t="n">
-        <v>322.0177694515158</v>
+        <v>484.8077317077015</v>
       </c>
       <c r="K9" s="10" t="inlineStr">
         <is>
@@ -1115,47 +1133,47 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Hilton Los Angeles Airport</t>
+          <t>Flamingo Cancun All Inclusive</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>AA-Independent</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Estados Unidos de América</t>
+          <t>México</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>Los Angeles (and vicinity), CA, US</t>
+          <t>Cancún</t>
         </is>
       </c>
       <c r="F10" s="12" t="n">
-        <v>2664974</v>
+        <v>2612003</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="H10" s="13" t="n">
-        <v>1292</v>
+        <v>-3557.379999999999</v>
       </c>
       <c r="I10" s="14" t="n">
-        <v>0.01183276084494633</v>
+        <v>0.09078282069354437</v>
       </c>
       <c r="J10" s="13" t="n">
-        <v>484.8077317077015</v>
-      </c>
-      <c r="K10" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="L10" s="8" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="K10" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
+        </is>
+      </c>
+      <c r="L10" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1183,12 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Flamingo Cancun All Inclusive</t>
+          <t>Krystal Cancun Hotel &amp; Resort</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>AA-Independent</t>
+          <t>Krystal</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
@@ -1184,28 +1202,28 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>2612003</v>
+        <v>2427022</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H11" s="13" t="n">
-        <v>-3557.379999999999</v>
+        <v>507.1399999999999</v>
       </c>
       <c r="I11" s="14" t="n">
-        <v>0.09078282069354437</v>
+        <v>0.02589634539777555</v>
       </c>
       <c r="J11" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" s="8" t="inlineStr">
+        <v>208.9556666565033</v>
+      </c>
+      <c r="K11" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="L11" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
-        </is>
-      </c>
-      <c r="L11" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1233,47 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Krystal Cancun Hotel &amp; Resort</t>
+          <t>The Manhattan at Times Square Hotel</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>Krystal</t>
+          <t>IHG</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>Estados Unidos de América</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>Cancún</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>2427022</v>
+        <v>2336066</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H12" s="13" t="n">
-        <v>507.1399999999999</v>
+        <v>314.08</v>
       </c>
       <c r="I12" s="14" t="n">
-        <v>0.02589634539777555</v>
+        <v>0.0379805193860105</v>
       </c>
       <c r="J12" s="13" t="n">
-        <v>208.9556666565033</v>
-      </c>
-      <c r="K12" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="L12" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+        <v>134.4482561708445</v>
+      </c>
+      <c r="K12" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="L12" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -1265,12 +1283,12 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>The Manhattan at Times Square Hotel</t>
+          <t>DoubleTree by Hilton New York Times Square West</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>IHG</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
@@ -1284,23 +1302,23 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>2336066</v>
+        <v>2327519</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H13" s="13" t="n">
-        <v>314.08</v>
+        <v>-3026.99</v>
       </c>
       <c r="I13" s="14" t="n">
-        <v>0.0379805193860105</v>
+        <v>0.01668342986673793</v>
       </c>
       <c r="J13" s="13" t="n">
-        <v>134.4482561708445</v>
-      </c>
-      <c r="K13" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+        <v>0</v>
+      </c>
+      <c r="K13" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="L13" s="7" t="inlineStr">
@@ -1315,12 +1333,12 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>DoubleTree by Hilton New York Times Square West</t>
+          <t>Hotel Indigo Lower East Side New York by IHG</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>IHG</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
@@ -1334,16 +1352,16 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>2327519</v>
+        <v>2182191</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H14" s="13" t="n">
-        <v>-3026.99</v>
+        <v>-589.83</v>
       </c>
       <c r="I14" s="14" t="n">
-        <v>0.01668342986673793</v>
+        <v>0.01017555291906162</v>
       </c>
       <c r="J14" s="13" t="n">
         <v>0</v>
@@ -1365,38 +1383,38 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Hotel Indigo Lower East Side New York by IHG</t>
+          <t>Emporio Cancun - with Optional All Inclusive</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>IHG</t>
+          <t>Emporio</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>Estados Unidos de América</t>
+          <t>México</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Cancún</t>
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>2182191</v>
+        <v>2153705</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H15" s="13" t="n">
-        <v>-589.83</v>
+        <v>10.37</v>
       </c>
       <c r="I15" s="14" t="n">
-        <v>0.01017555291906162</v>
+        <v>0.01881641171841083</v>
       </c>
       <c r="J15" s="13" t="n">
-        <v>0</v>
+        <v>4.814958408881439</v>
       </c>
       <c r="K15" s="10" t="inlineStr">
         <is>
@@ -1415,42 +1433,42 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Emporio Cancun - with Optional All Inclusive</t>
+          <t>Caribe Deluxe Princess</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>Emporio</t>
+          <t>AA-Independent</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>República Dominicana</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>Cancún</t>
+          <t>Punta Cana</t>
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>2153705</v>
+        <v>2153598</v>
       </c>
       <c r="G16" s="5" t="n">
         <v>2</v>
       </c>
       <c r="H16" s="13" t="n">
-        <v>10.37</v>
+        <v>0</v>
       </c>
       <c r="I16" s="14" t="n">
-        <v>0.01881641171841083</v>
+        <v>0.08855273825477178</v>
       </c>
       <c r="J16" s="13" t="n">
-        <v>4.814958408881439</v>
-      </c>
-      <c r="K16" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+        <v>0</v>
+      </c>
+      <c r="K16" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
       <c r="L16" s="7" t="inlineStr">
@@ -1465,42 +1483,42 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Caribe Deluxe Princess</t>
+          <t>Hotel Xcaret Mexico All Parks All Fun Inclusive</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>AA-Independent</t>
+          <t>Hoteles Xcaret</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>República Dominicana</t>
+          <t>México</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>Punta Cana</t>
+          <t>Riviera Maya</t>
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>2153598</v>
+        <v>2131069</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H17" s="13" t="n">
-        <v>0</v>
+        <v>-32243.04</v>
       </c>
       <c r="I17" s="14" t="n">
-        <v>0.08855273825477178</v>
+        <v>0.008712528782503054</v>
       </c>
       <c r="J17" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="K17" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="K17" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="L17" s="7" t="inlineStr">
@@ -1515,35 +1533,35 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Hotel Xcaret Mexico All Parks All Fun Inclusive</t>
+          <t>Ocean El Faro</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>Hoteles Xcaret</t>
+          <t>Ocean by H10</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>República Dominicana</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>Riviera Maya</t>
+          <t>Punta Cana</t>
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>2131069</v>
+        <v>2121251</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="H18" s="13" t="n">
-        <v>-32243.04</v>
+        <v>-896.8999999999999</v>
       </c>
       <c r="I18" s="14" t="n">
-        <v>0.008712528782503054</v>
+        <v>0.01072338916988136</v>
       </c>
       <c r="J18" s="13" t="n">
         <v>0</v>
@@ -1565,47 +1583,47 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Ocean El Faro</t>
+          <t>Oceanside Hotel and Suites</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>Ocean by H10</t>
+          <t>AA-Independent</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>República Dominicana</t>
+          <t>Estados Unidos de América</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>Punta Cana</t>
+          <t>Miami Area</t>
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>2121251</v>
+        <v>2088370</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="H19" s="13" t="n">
-        <v>-896.8999999999999</v>
+        <v>1001.02</v>
       </c>
       <c r="I19" s="14" t="n">
-        <v>0.01072338916988136</v>
+        <v>0.02256209388183128</v>
       </c>
       <c r="J19" s="13" t="n">
-        <v>0</v>
+        <v>479.3307699306157</v>
       </c>
       <c r="K19" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="L19" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="L19" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -1615,47 +1633,47 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Oceanside Hotel and Suites</t>
+          <t>Occidental at Xcaret Destination</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>AA-Independent</t>
+          <t>Barcelo</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Estados Unidos de América</t>
+          <t>México</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>Miami Area</t>
+          <t>Riviera Maya</t>
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>2088370</v>
+        <v>2063612</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H20" s="13" t="n">
-        <v>1001.02</v>
+        <v>-5232.530000000001</v>
       </c>
       <c r="I20" s="14" t="n">
-        <v>0.02256209388183128</v>
+        <v>0.04887352855090976</v>
       </c>
       <c r="J20" s="13" t="n">
-        <v>479.3307699306157</v>
-      </c>
-      <c r="K20" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="L20" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+        <v>0</v>
+      </c>
+      <c r="K20" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="L20" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -1665,38 +1683,38 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Live Aqua Cancún</t>
+          <t>Hilton Cleveland Downtown</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>GRUPO POSADAS</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>Estados Unidos de América</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>Cancún</t>
+          <t>Cleveland Area</t>
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>2087608</v>
+        <v>2061000</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="H21" s="13" t="n">
-        <v>1306.97</v>
+        <v>826.5900000000004</v>
       </c>
       <c r="I21" s="14" t="n">
-        <v>0.01249899406401968</v>
+        <v>0.002290635613779719</v>
       </c>
       <c r="J21" s="13" t="n">
-        <v>626.061022950669</v>
+        <v>401.0625909752549</v>
       </c>
       <c r="K21" s="10" t="inlineStr">
         <is>
@@ -1715,12 +1733,12 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Occidental at Xcaret Destination</t>
+          <t>Secrets Akumal Riviera Maya</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Barcelo</t>
+          <t>Hyatt Inclusive Collection</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
@@ -1734,23 +1752,23 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>2063612</v>
+        <v>2035755</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H22" s="13" t="n">
-        <v>-5232.530000000001</v>
+        <v>-1175.77</v>
       </c>
       <c r="I22" s="14" t="n">
-        <v>0.04887352855090976</v>
+        <v>0.009904433490277562</v>
       </c>
       <c r="J22" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="K22" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="K22" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="L22" s="7" t="inlineStr">
@@ -1765,7 +1783,7 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Hilton Cleveland Downtown</t>
+          <t>DoubleTree by Hilton San Jose</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
@@ -1780,32 +1798,32 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>Cleveland Area</t>
+          <t>San Jose Area</t>
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>2061000</v>
+        <v>2013929</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="H23" s="13" t="n">
-        <v>826.5900000000004</v>
+        <v>-461.61</v>
       </c>
       <c r="I23" s="14" t="n">
-        <v>0.002290635613779719</v>
+        <v>0.004626776812886651</v>
       </c>
       <c r="J23" s="13" t="n">
-        <v>401.0625909752549</v>
+        <v>0</v>
       </c>
       <c r="K23" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="L23" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="L23" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -1815,38 +1833,38 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Secrets Akumal Riviera Maya</t>
+          <t>Rosen Inn Lake Buena Vista</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>Hyatt Inclusive Collection</t>
+          <t>AA-Independent</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>Estados Unidos de América</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>Riviera Maya</t>
+          <t>Orlando</t>
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>2035755</v>
+        <v>2003740</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H24" s="13" t="n">
-        <v>-1175.77</v>
+        <v>285.94</v>
       </c>
       <c r="I24" s="14" t="n">
-        <v>0.009904433490277562</v>
+        <v>0.02667062592951181</v>
       </c>
       <c r="J24" s="13" t="n">
-        <v>0</v>
+        <v>142.7031451186282</v>
       </c>
       <c r="K24" s="10" t="inlineStr">
         <is>
@@ -1865,47 +1883,47 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>DoubleTree by Hilton San Jose</t>
+          <t>Presidente InterContinental Cancún</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>Presidente Intercontinental</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>Estados Unidos de América</t>
+          <t>México</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>San Jose Area</t>
+          <t>Cancún</t>
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>2013929</v>
+        <v>1984294</v>
       </c>
       <c r="G25" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H25" s="13" t="n">
-        <v>-461.61</v>
+        <v>418.22</v>
       </c>
       <c r="I25" s="14" t="n">
-        <v>0.004626776812886651</v>
+        <v>0.01483096758847227</v>
       </c>
       <c r="J25" s="13" t="n">
-        <v>0</v>
+        <v>210.7651386336904</v>
       </c>
       <c r="K25" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="L25" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="L25" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -1915,7 +1933,7 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Rosen Inn Lake Buena Vista</t>
+          <t>Rosen Centre Hotel</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
@@ -1934,23 +1952,23 @@
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>2003740</v>
+        <v>1976370</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H26" s="13" t="n">
-        <v>285.94</v>
+        <v>-4688.7</v>
       </c>
       <c r="I26" s="14" t="n">
-        <v>0.02667062592951181</v>
+        <v>0.06664845145392816</v>
       </c>
       <c r="J26" s="13" t="n">
-        <v>142.7031451186282</v>
-      </c>
-      <c r="K26" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+        <v>0</v>
+      </c>
+      <c r="K26" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
       <c r="L26" s="7" t="inlineStr">
@@ -1965,47 +1983,47 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Presidente InterContinental Cancún</t>
+          <t>Grand Hyatt Kauai Resort and Spa</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>Presidente Intercontinental</t>
+          <t>Hyatt</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>Estados Unidos de América</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>Cancún</t>
+          <t>Hawái</t>
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>1984294</v>
+        <v>1925656</v>
       </c>
       <c r="G27" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H27" s="13" t="n">
-        <v>418.22</v>
+        <v>-1455.71</v>
       </c>
       <c r="I27" s="14" t="n">
-        <v>0.01483096758847227</v>
+        <v>0.02315938049163506</v>
       </c>
       <c r="J27" s="13" t="n">
-        <v>210.7651386336904</v>
+        <v>0</v>
       </c>
       <c r="K27" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="L27" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="L27" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -2015,42 +2033,42 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>Rosen Centre Hotel</t>
+          <t>Royalton CHIC Cancun, An Autograph Collection All-Inclusive Resort - Adults Only</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>AA-Independent</t>
+          <t>Royalton Hotels &amp; Resorts</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Estados Unidos de América</t>
+          <t>México</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>Orlando</t>
+          <t>Cancún</t>
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>1976370</v>
+        <v>1898756</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H28" s="13" t="n">
-        <v>-4688.7</v>
+        <v>-1050.68</v>
       </c>
       <c r="I28" s="14" t="n">
-        <v>0.06664845145392816</v>
+        <v>0.01647499731403087</v>
       </c>
       <c r="J28" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="K28" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="K28" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="L28" s="7" t="inlineStr">
@@ -2065,12 +2083,12 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Grand Hyatt Kauai Resort and Spa</t>
+          <t>Hilton Anaheim</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>Hyatt</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
@@ -2080,32 +2098,32 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>Hawái</t>
+          <t>Anaheim Area</t>
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>1925656</v>
+        <v>1893678</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H29" s="13" t="n">
-        <v>-1455.71</v>
+        <v>566.36</v>
       </c>
       <c r="I29" s="14" t="n">
-        <v>0.02315938049163506</v>
+        <v>0.04102439802331759</v>
       </c>
       <c r="J29" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="L29" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+        <v>299.0793577366374</v>
+      </c>
+      <c r="K29" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="L29" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -2115,12 +2133,12 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>Royalton CHIC Cancun, An Autograph Collection All-Inclusive Resort - Adults Only</t>
+          <t>The Reef Playacar Beach Resort &amp; Spa - Optional All Inclusive</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>Royalton Hotels &amp; Resorts</t>
+          <t>AA-Independent</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
@@ -2130,20 +2148,20 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>Cancún</t>
+          <t>Riviera Maya</t>
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>1898756</v>
+        <v>1884420</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="H30" s="13" t="n">
-        <v>-1050.68</v>
+        <v>-913.1300000000001</v>
       </c>
       <c r="I30" s="14" t="n">
-        <v>0.01647499731403087</v>
+        <v>0.004930960189342078</v>
       </c>
       <c r="J30" s="13" t="n">
         <v>0</v>
@@ -2165,47 +2183,47 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Hilton Anaheim</t>
+          <t>Barceló Maya Tropical</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>Barcelo</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Estados Unidos de América</t>
+          <t>México</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>Anaheim Area</t>
+          <t>Riviera Maya</t>
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>1893678</v>
+        <v>1878779</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="H31" s="13" t="n">
-        <v>566.36</v>
+        <v>-10589.52</v>
       </c>
       <c r="I31" s="14" t="n">
-        <v>0.04102439802331759</v>
+        <v>0.0007707133196613332</v>
       </c>
       <c r="J31" s="13" t="n">
-        <v>299.0793577366374</v>
-      </c>
-      <c r="K31" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
-        </is>
-      </c>
-      <c r="L31" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+        <v>0</v>
+      </c>
+      <c r="K31" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="L31" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -2215,35 +2233,35 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>The Reef Playacar Beach Resort &amp; Spa - Optional All Inclusive</t>
+          <t>Ocean Blue &amp; Sand Beach Resort</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>AA-Independent</t>
+          <t>Ocean by H10</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>República Dominicana</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>Riviera Maya</t>
+          <t>Punta Cana</t>
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>1884420</v>
+        <v>1873245</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="H32" s="13" t="n">
-        <v>-913.1300000000001</v>
+        <v>-1606.5</v>
       </c>
       <c r="I32" s="14" t="n">
-        <v>0.004930960189342078</v>
+        <v>0.02235745991581453</v>
       </c>
       <c r="J32" s="13" t="n">
         <v>0</v>
@@ -2265,42 +2283,42 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Barceló Maya Tropical</t>
+          <t>Rosen Inn at Pointe Orlando</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>Barcelo</t>
+          <t>AA-Independent</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>Estados Unidos de América</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>Riviera Maya</t>
+          <t>Orlando</t>
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>1878779</v>
+        <v>1866828</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="H33" s="13" t="n">
-        <v>-10589.52</v>
+        <v>222.65</v>
       </c>
       <c r="I33" s="14" t="n">
-        <v>0.0007707133196613332</v>
+        <v>0.09255592909469967</v>
       </c>
       <c r="J33" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+        <v>119.2664776830003</v>
+      </c>
+      <c r="K33" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
       <c r="L33" s="7" t="inlineStr">
@@ -2315,12 +2333,12 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>Ocean Blue &amp; Sand Beach Resort</t>
+          <t>Occidental Punta Cana</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>Ocean by H10</t>
+          <t>Barcelo</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
@@ -2334,23 +2352,23 @@
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>1873245</v>
+        <v>1858432</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H34" s="13" t="n">
-        <v>-1606.5</v>
+        <v>-850.88</v>
       </c>
       <c r="I34" s="14" t="n">
-        <v>0.02235745991581453</v>
+        <v>0.04436320511054481</v>
       </c>
       <c r="J34" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="K34" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="K34" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="L34" s="7" t="inlineStr">
@@ -2365,42 +2383,42 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Rosen Inn at Pointe Orlando</t>
+          <t>Secrets The Vine Cancun</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>AA-Independent</t>
+          <t>Hyatt Inclusive Collection</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>Estados Unidos de América</t>
+          <t>México</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>Orlando</t>
+          <t>Cancún</t>
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>1866828</v>
+        <v>1850138</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H35" s="13" t="n">
-        <v>222.65</v>
+        <v>-1232.49</v>
       </c>
       <c r="I35" s="14" t="n">
-        <v>0.09255592909469967</v>
+        <v>0.009769541515281564</v>
       </c>
       <c r="J35" s="13" t="n">
-        <v>119.2664776830003</v>
-      </c>
-      <c r="K35" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+        <v>0</v>
+      </c>
+      <c r="K35" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="L35" s="7" t="inlineStr">
@@ -2415,7 +2433,7 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>Occidental Punta Cana</t>
+          <t>Barceló Maya Palace</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
@@ -2425,32 +2443,32 @@
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>República Dominicana</t>
+          <t>México</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>Punta Cana</t>
+          <t>Riviera Maya</t>
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>1858432</v>
+        <v>1790943</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H36" s="13" t="n">
-        <v>-850.88</v>
+        <v>-17126.35</v>
       </c>
       <c r="I36" s="14" t="n">
-        <v>0.04436320511054481</v>
+        <v>0.003890687754998344</v>
       </c>
       <c r="J36" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="K36" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="K36" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="L36" s="7" t="inlineStr">
@@ -2465,12 +2483,12 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Secrets The Vine Cancun</t>
+          <t>Hard Rock Hotel Cancún</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>Hyatt Inclusive Collection</t>
+          <t>PAM Hotels</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
@@ -2484,23 +2502,23 @@
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>1850138</v>
+        <v>1789942</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H37" s="13" t="n">
-        <v>-1232.49</v>
+        <v>-6552.57</v>
       </c>
       <c r="I37" s="14" t="n">
-        <v>0.009769541515281564</v>
+        <v>0.1586112846114567</v>
       </c>
       <c r="J37" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="K37" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="K37" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
       <c r="L37" s="7" t="inlineStr">
@@ -2515,47 +2533,47 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>Galería Plaza Reforma</t>
+          <t>Encore Las Vegas</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>Las Brisas</t>
+          <t>Wynn Las Vegas</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>Estados Unidos de América</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>Mexico City - Central Mexico</t>
+          <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
       <c r="F38" s="12" t="n">
-        <v>1845737</v>
+        <v>1764837</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="H38" s="13" t="n">
-        <v>1046.809999999999</v>
+        <v>-1553.43</v>
       </c>
       <c r="I38" s="14" t="n">
-        <v>0.06564207143271225</v>
+        <v>0.02746372611181656</v>
       </c>
       <c r="J38" s="13" t="n">
-        <v>567.1501411089441</v>
-      </c>
-      <c r="K38" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
-        </is>
-      </c>
-      <c r="L38" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+        <v>0</v>
+      </c>
+      <c r="K38" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="L38" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -2565,47 +2583,47 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Hyatt Centric Gran Via Madrid</t>
+          <t>Aquamarina Beach</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>Hyatt</t>
+          <t>AA-Independent</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>España</t>
+          <t>México</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>Madrid</t>
+          <t>Cancún</t>
         </is>
       </c>
       <c r="F39" s="12" t="n">
-        <v>1829136</v>
+        <v>1762148</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="H39" s="13" t="n">
-        <v>1031.33</v>
+        <v>348.8099999999996</v>
       </c>
       <c r="I39" s="14" t="n">
-        <v>0.0361771896676901</v>
+        <v>0.01264990227835573</v>
       </c>
       <c r="J39" s="13" t="n">
-        <v>563.8345098450852</v>
-      </c>
-      <c r="K39" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
-        </is>
-      </c>
-      <c r="L39" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+        <v>197.9459160070548</v>
+      </c>
+      <c r="K39" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="L39" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -2615,35 +2633,35 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>Barceló Maya Palace</t>
+          <t>Hyatt Regency Paris Etoile</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>Barcelo</t>
+          <t>Hyatt</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>Francia</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>Riviera Maya</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F40" s="12" t="n">
-        <v>1790943</v>
+        <v>1748688</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H40" s="13" t="n">
-        <v>-17126.35</v>
+        <v>-4862.650000000001</v>
       </c>
       <c r="I40" s="14" t="n">
-        <v>0.003890687754998344</v>
+        <v>0.02767503408269514</v>
       </c>
       <c r="J40" s="13" t="n">
         <v>0</v>
@@ -2665,12 +2683,12 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Hard Rock Hotel Cancún</t>
+          <t>Hilton Cancun Mar Caribe All-Inclusive Resort</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>PAM Hotels</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
@@ -2684,23 +2702,23 @@
         </is>
       </c>
       <c r="F41" s="12" t="n">
-        <v>1789942</v>
+        <v>1724026</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H41" s="13" t="n">
-        <v>-6552.57</v>
+        <v>-1485.59</v>
       </c>
       <c r="I41" s="14" t="n">
-        <v>0.1586112846114567</v>
+        <v>0.002916429334592402</v>
       </c>
       <c r="J41" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="K41" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="K41" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="L41" s="7" t="inlineStr">
@@ -2715,7 +2733,7 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>Lopesan Costa Bavaro Resort, Spa &amp; Casino</t>
+          <t>The Gallivant Times Square</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
@@ -2725,32 +2743,32 @@
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>República Dominicana</t>
+          <t>Estados Unidos de América</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>Bávaro Area</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="F42" s="12" t="n">
-        <v>1771206</v>
+        <v>1670790</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H42" s="13" t="n">
-        <v>1109.26</v>
+        <v>764.09</v>
       </c>
       <c r="I42" s="14" t="n">
-        <v>0.04849802902655026</v>
+        <v>0.08407280388319298</v>
       </c>
       <c r="J42" s="13" t="n">
-        <v>626.2738495691636</v>
-      </c>
-      <c r="K42" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+        <v>457.3225839273637</v>
+      </c>
+      <c r="K42" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
       <c r="L42" s="8" t="inlineStr">
@@ -2765,35 +2783,35 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Encore Las Vegas</t>
+          <t>Breathless Cancun Soul Resort &amp; Spa - Solo Adultos</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>Wynn Las Vegas</t>
+          <t>Hyatt Inclusive Collection</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>Estados Unidos de América</t>
+          <t>México</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>Las Vegas (and vicinity), NV, US</t>
+          <t>Cancún</t>
         </is>
       </c>
       <c r="F43" s="12" t="n">
-        <v>1764837</v>
+        <v>1633219</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="H43" s="13" t="n">
-        <v>-1553.43</v>
+        <v>-2193.62</v>
       </c>
       <c r="I43" s="14" t="n">
-        <v>0.02746372611181656</v>
+        <v>0.007354188262566135</v>
       </c>
       <c r="J43" s="13" t="n">
         <v>0</v>
@@ -2815,47 +2833,47 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>Aquamarina Beach</t>
+          <t>Universal's Hard Rock Hotel</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>AA-Independent</t>
+          <t>Universal</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>Estados Unidos de América</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>Cancún</t>
+          <t>Orlando</t>
         </is>
       </c>
       <c r="F44" s="12" t="n">
-        <v>1762148</v>
+        <v>1612409</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="H44" s="13" t="n">
-        <v>348.8099999999996</v>
+        <v>494.5500000000002</v>
       </c>
       <c r="I44" s="14" t="n">
-        <v>0.01264990227835573</v>
+        <v>0.01081177294346534</v>
       </c>
       <c r="J44" s="13" t="n">
-        <v>197.9459160070548</v>
+        <v>306.7149836052764</v>
       </c>
       <c r="K44" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="L44" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="L44" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -2865,47 +2883,47 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Hyatt Regency Paris Etoile</t>
+          <t>Hilton Orlando</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>Hyatt</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>Francia</t>
+          <t>Estados Unidos de América</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Orlando</t>
         </is>
       </c>
       <c r="F45" s="12" t="n">
-        <v>1748688</v>
+        <v>1611250</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H45" s="13" t="n">
-        <v>-4862.650000000001</v>
+        <v>615.6799999999999</v>
       </c>
       <c r="I45" s="14" t="n">
-        <v>0.02767503408269514</v>
+        <v>0.06273266097750194</v>
       </c>
       <c r="J45" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K45" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="L45" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+        <v>382.1132660977502</v>
+      </c>
+      <c r="K45" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="L45" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -2915,35 +2933,35 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>Hilton Cancun Mar Caribe All-Inclusive Resort</t>
+          <t>Hotel Indigo Los Angeles Downtown by IHG</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>IHG</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>Estados Unidos de América</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>Cancún</t>
+          <t>Los Angeles (and vicinity), CA, US</t>
         </is>
       </c>
       <c r="F46" s="12" t="n">
-        <v>1724026</v>
+        <v>1610188</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H46" s="13" t="n">
-        <v>-1485.59</v>
+        <v>0</v>
       </c>
       <c r="I46" s="14" t="n">
-        <v>0.002916429334592402</v>
+        <v>0.004456622456508184</v>
       </c>
       <c r="J46" s="13" t="n">
         <v>0</v>
@@ -2965,12 +2983,12 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>The Gallivant Times Square</t>
+          <t>Hilton Garden Inn Seattle Downtown</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>AA-Independent</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
@@ -2980,32 +2998,32 @@
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Seattle Area</t>
         </is>
       </c>
       <c r="F47" s="12" t="n">
-        <v>1670790</v>
+        <v>1583340</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H47" s="13" t="n">
-        <v>764.09</v>
+        <v>-395.61</v>
       </c>
       <c r="I47" s="14" t="n">
-        <v>0.08407280388319298</v>
+        <v>0.001717887503631564</v>
       </c>
       <c r="J47" s="13" t="n">
-        <v>457.3225839273637</v>
-      </c>
-      <c r="K47" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
-        </is>
-      </c>
-      <c r="L47" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+        <v>0</v>
+      </c>
+      <c r="K47" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="L47" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -3015,12 +3033,12 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>Rosen Shingle Creek</t>
+          <t>INNSIDE by Melià New York Nomad</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>AA-Independent</t>
+          <t>Melia</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
@@ -3030,32 +3048,32 @@
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>Orlando</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="F48" s="12" t="n">
-        <v>1667063</v>
+        <v>1582899</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H48" s="13" t="n">
-        <v>858.85</v>
+        <v>-811.13</v>
       </c>
       <c r="I48" s="14" t="n">
-        <v>0.09310985847565449</v>
+        <v>0.01198244486856079</v>
       </c>
       <c r="J48" s="13" t="n">
-        <v>515.1874884152548</v>
-      </c>
-      <c r="K48" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
-        </is>
-      </c>
-      <c r="L48" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+        <v>0</v>
+      </c>
+      <c r="K48" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="L48" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -3065,42 +3083,42 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Breathless Cancun Soul Resort &amp; Spa - Solo Adultos</t>
+          <t>whala!bavaro - All Inclusive</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>Hyatt Inclusive Collection</t>
+          <t>AA-Independent</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>República Dominicana</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>Cancún</t>
+          <t>Bávaro Area</t>
         </is>
       </c>
       <c r="F49" s="12" t="n">
-        <v>1633219</v>
+        <v>1563577</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H49" s="13" t="n">
-        <v>-2193.62</v>
+        <v>-719.41</v>
       </c>
       <c r="I49" s="14" t="n">
-        <v>0.007354188262566135</v>
+        <v>0.05364558317243091</v>
       </c>
       <c r="J49" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="K49" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="K49" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
       <c r="L49" s="7" t="inlineStr">
@@ -3115,47 +3133,47 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>Universal's Hard Rock Hotel</t>
+          <t>Camino Real Polanco México</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>Universal</t>
+          <t>Camino Real</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>Estados Unidos de América</t>
+          <t>México</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>Orlando</t>
+          <t>Mexico City - Central Mexico</t>
         </is>
       </c>
       <c r="F50" s="12" t="n">
-        <v>1612409</v>
+        <v>1537674</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H50" s="13" t="n">
-        <v>494.5500000000002</v>
+        <v>179.18</v>
       </c>
       <c r="I50" s="14" t="n">
-        <v>0.01081177294346534</v>
+        <v>0.03928531015026592</v>
       </c>
       <c r="J50" s="13" t="n">
-        <v>306.7149836052764</v>
-      </c>
-      <c r="K50" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="L50" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+        <v>116.526649992131</v>
+      </c>
+      <c r="K50" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="L50" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -3165,42 +3183,42 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>Hilton Orlando</t>
+          <t>Hotel Imperial Reforma</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>AA-Independent</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>Estados Unidos de América</t>
+          <t>México</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>Orlando</t>
+          <t>Mexico City - Central Mexico</t>
         </is>
       </c>
       <c r="F51" s="12" t="n">
-        <v>1611250</v>
+        <v>1528451</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H51" s="13" t="n">
-        <v>615.6799999999999</v>
+        <v>311.34</v>
       </c>
       <c r="I51" s="14" t="n">
-        <v>0.06273266097750194</v>
+        <v>0.02109586764639495</v>
       </c>
       <c r="J51" s="13" t="n">
-        <v>382.1132660977502</v>
-      </c>
-      <c r="K51" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+        <v>203.6964220639065</v>
+      </c>
+      <c r="K51" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="L51" s="8" t="inlineStr">
@@ -3215,26 +3233,26 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>Hotel Indigo Los Angeles Downtown by IHG</t>
+          <t>Novotel Paris Gare De Lyon</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>IHG</t>
+          <t>Accor</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>Estados Unidos de América</t>
+          <t>Francia</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>Los Angeles (and vicinity), CA, US</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F52" s="12" t="n">
-        <v>1610188</v>
+        <v>1524744</v>
       </c>
       <c r="G52" s="5" t="n">
         <v>2</v>
@@ -3243,14 +3261,14 @@
         <v>0</v>
       </c>
       <c r="I52" s="14" t="n">
-        <v>0.004456622456508184</v>
+        <v>0.03410015058265518</v>
       </c>
       <c r="J52" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="K52" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="K52" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="L52" s="7" t="inlineStr">
@@ -3265,42 +3283,42 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>Hilton Garden Inn Seattle Downtown</t>
+          <t>Riu Palace Punta Cana - All Inclusive</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>RIU</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>Estados Unidos de América</t>
+          <t>República Dominicana</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>Seattle Area</t>
+          <t>Punta Cana</t>
         </is>
       </c>
       <c r="F53" s="12" t="n">
-        <v>1583340</v>
+        <v>1514846</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="H53" s="13" t="n">
-        <v>-395.61</v>
+        <v>-13070.75</v>
       </c>
       <c r="I53" s="14" t="n">
-        <v>0.001717887503631564</v>
+        <v>0.1585303060509121</v>
       </c>
       <c r="J53" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="K53" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="K53" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
       <c r="L53" s="7" t="inlineStr">
@@ -3315,12 +3333,12 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>INNSIDE by Melià New York Nomad</t>
+          <t>Disney's Coronado Springs Resort</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>Melia</t>
+          <t>Disney</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
@@ -3330,20 +3348,20 @@
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Orlando</t>
         </is>
       </c>
       <c r="F54" s="12" t="n">
-        <v>1582899</v>
+        <v>1511533</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H54" s="13" t="n">
-        <v>-811.13</v>
+        <v>-1029.24</v>
       </c>
       <c r="I54" s="14" t="n">
-        <v>0.01198244486856079</v>
+        <v>0.005138491849003627</v>
       </c>
       <c r="J54" s="13" t="n">
         <v>0</v>
@@ -3365,38 +3383,38 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>Sunset Royal Beach Resort - All Inclusive</t>
+          <t>Barceló Bávaro Palace</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>AA-Independent</t>
+          <t>Barcelo</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>República Dominicana</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>Cancún</t>
+          <t>Punta Cana</t>
         </is>
       </c>
       <c r="F55" s="12" t="n">
-        <v>1581635</v>
+        <v>1505615</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H55" s="13" t="n">
-        <v>885.63</v>
+        <v>300.62</v>
       </c>
       <c r="I55" s="14" t="n">
-        <v>0.005209166463817506</v>
+        <v>0.00570066052742567</v>
       </c>
       <c r="J55" s="13" t="n">
-        <v>559.9458787899863</v>
+        <v>199.6659172497617</v>
       </c>
       <c r="K55" s="10" t="inlineStr">
         <is>
@@ -3415,12 +3433,12 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>whala!bavaro - All Inclusive</t>
+          <t>Nickelodeon Hotels and Resorts Punta Cana By Karisma</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>AA-Independent</t>
+          <t>Karisma</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
@@ -3430,27 +3448,27 @@
       </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
-          <t>Bávaro Area</t>
+          <t>Punta Cana</t>
         </is>
       </c>
       <c r="F56" s="12" t="n">
-        <v>1563577</v>
+        <v>1492292</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="H56" s="13" t="n">
-        <v>-719.41</v>
+        <v>-7508.35</v>
       </c>
       <c r="I56" s="14" t="n">
-        <v>0.05364558317243091</v>
+        <v>0.01086516579865067</v>
       </c>
       <c r="J56" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="K56" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="K56" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="L56" s="7" t="inlineStr">
@@ -3465,7 +3483,7 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>DoubleTree by Hilton San Juan</t>
+          <t>Casa Marina Key West, Curio Collection by Hilton</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
@@ -3475,37 +3493,37 @@
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>Puerto Rico</t>
+          <t>Estados Unidos de América</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
-          <t>Puerto Rico</t>
+          <t>Key West Area</t>
         </is>
       </c>
       <c r="F57" s="12" t="n">
-        <v>1561005</v>
+        <v>1491853</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H57" s="13" t="n">
-        <v>830.9200000000001</v>
+        <v>-21565.3</v>
       </c>
       <c r="I57" s="14" t="n">
-        <v>0.002268410415085154</v>
+        <v>0.005914791872925819</v>
       </c>
       <c r="J57" s="13" t="n">
-        <v>532.2981028247829</v>
+        <v>0</v>
       </c>
       <c r="K57" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="L57" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="L57" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -3515,7 +3533,7 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>Hampton Inn Boston - Logan Airport</t>
+          <t>Hilton Garden Inn NYC Financial Center/Manhattan Downtown</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
@@ -3530,32 +3548,32 @@
       </c>
       <c r="E58" s="5" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="F58" s="12" t="n">
-        <v>1555901</v>
+        <v>1482208</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H58" s="13" t="n">
-        <v>842.3500000000001</v>
+        <v>0</v>
       </c>
       <c r="I58" s="14" t="n">
-        <v>0.00771835740191696</v>
+        <v>0.00496151687212591</v>
       </c>
       <c r="J58" s="13" t="n">
-        <v>541.3904869268675</v>
+        <v>0</v>
       </c>
       <c r="K58" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="L58" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="L58" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -3565,47 +3583,47 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>Camino Real Polanco México</t>
+          <t>Hotel Cartagena Plaza</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>Camino Real</t>
+          <t>EM Hotels</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t>Mexico City - Central Mexico</t>
+          <t>Cartagena Area</t>
         </is>
       </c>
       <c r="F59" s="12" t="n">
-        <v>1537674</v>
+        <v>1479772</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H59" s="13" t="n">
-        <v>179.18</v>
+        <v>317.14</v>
       </c>
       <c r="I59" s="14" t="n">
-        <v>0.03928531015026592</v>
+        <v>0.01243434799415045</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>116.526649992131</v>
-      </c>
-      <c r="K59" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
-        </is>
-      </c>
-      <c r="L59" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+        <v>214.3168001556997</v>
+      </c>
+      <c r="K59" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="L59" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -3615,7 +3633,7 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>Hotel Imperial Reforma</t>
+          <t>Drury Inn &amp; Suites near Universal Orlando Resort</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
@@ -3625,37 +3643,37 @@
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>Estados Unidos de América</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
         <is>
-          <t>Mexico City - Central Mexico</t>
+          <t>Orlando</t>
         </is>
       </c>
       <c r="F60" s="12" t="n">
-        <v>1528451</v>
+        <v>1476575</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H60" s="13" t="n">
-        <v>311.34</v>
+        <v>270.8000000000002</v>
       </c>
       <c r="I60" s="14" t="n">
-        <v>0.02109586764639495</v>
+        <v>0.02084215160083301</v>
       </c>
       <c r="J60" s="13" t="n">
-        <v>203.6964220639065</v>
+        <v>183.3973892284511</v>
       </c>
       <c r="K60" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="L60" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="L60" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -3665,42 +3683,42 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>Novotel Paris Gare De Lyon</t>
+          <t>Hilton Garden Inn Bogota Airport</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>Accor</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>Francia</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Bogotá Area</t>
         </is>
       </c>
       <c r="F61" s="12" t="n">
-        <v>1524744</v>
+        <v>1472289</v>
       </c>
       <c r="G61" s="5" t="n">
         <v>2</v>
       </c>
       <c r="H61" s="13" t="n">
-        <v>0</v>
+        <v>106.99</v>
       </c>
       <c r="I61" s="14" t="n">
-        <v>0.03410015058265518</v>
+        <v>0.001274885569341345</v>
       </c>
       <c r="J61" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K61" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+        <v>72.66915666693156</v>
+      </c>
+      <c r="K61" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="L61" s="7" t="inlineStr">
@@ -3715,42 +3733,42 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>Riu Palace Punta Cana - All Inclusive</t>
+          <t>Embassy Suites by Hilton Orlando Lake Buena Vista Resort</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>RIU</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>República Dominicana</t>
+          <t>Estados Unidos de América</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
         <is>
-          <t>Punta Cana</t>
+          <t>Orlando</t>
         </is>
       </c>
       <c r="F62" s="12" t="n">
-        <v>1514846</v>
+        <v>1470361</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="H62" s="13" t="n">
-        <v>-13070.75</v>
+        <v>245.26</v>
       </c>
       <c r="I62" s="14" t="n">
-        <v>0.1585303060509121</v>
+        <v>0.01259894678925788</v>
       </c>
       <c r="J62" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K62" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+        <v>166.8025743337861</v>
+      </c>
+      <c r="K62" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="L62" s="7" t="inlineStr">
@@ -3765,12 +3783,12 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>Disney's Coronado Springs Resort</t>
+          <t>Hilton Miami Downtown</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>Disney</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
@@ -3780,27 +3798,27 @@
       </c>
       <c r="E63" s="5" t="inlineStr">
         <is>
-          <t>Orlando</t>
+          <t>Miami Area</t>
         </is>
       </c>
       <c r="F63" s="12" t="n">
-        <v>1511533</v>
+        <v>1468352</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H63" s="13" t="n">
-        <v>-1029.24</v>
+        <v>-390.14</v>
       </c>
       <c r="I63" s="14" t="n">
-        <v>0.005138491849003627</v>
+        <v>0.05420839144837205</v>
       </c>
       <c r="J63" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="K63" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="K63" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
       <c r="L63" s="7" t="inlineStr">
@@ -3815,38 +3833,38 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>Barceló Bávaro Palace</t>
+          <t>Hilton Garden Inn New York/Manhattan-Midtown East</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>Barcelo</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>República Dominicana</t>
+          <t>Estados Unidos de América</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
         <is>
-          <t>Punta Cana</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="F64" s="12" t="n">
-        <v>1505615</v>
+        <v>1464600</v>
       </c>
       <c r="G64" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H64" s="13" t="n">
-        <v>300.62</v>
+        <v>0</v>
       </c>
       <c r="I64" s="14" t="n">
-        <v>0.00570066052742567</v>
+        <v>0.005942236788201557</v>
       </c>
       <c r="J64" s="13" t="n">
-        <v>199.6659172497617</v>
+        <v>0</v>
       </c>
       <c r="K64" s="10" t="inlineStr">
         <is>
@@ -3865,47 +3883,47 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>Nickelodeon Hotels and Resorts Punta Cana By Karisma</t>
+          <t>Embassy Suites by Hilton Fort Lauderdale 17th Street</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>Karisma</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>República Dominicana</t>
+          <t>Estados Unidos de América</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
         <is>
-          <t>Punta Cana</t>
+          <t>Fort Lauderdale (and vicinity), FL, US</t>
         </is>
       </c>
       <c r="F65" s="12" t="n">
-        <v>1492292</v>
+        <v>1457682</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="H65" s="13" t="n">
-        <v>-7508.35</v>
+        <v>391.63</v>
       </c>
       <c r="I65" s="14" t="n">
-        <v>0.01086516579865067</v>
+        <v>0.01006323738648073</v>
       </c>
       <c r="J65" s="13" t="n">
-        <v>0</v>
+        <v>268.6662797510019</v>
       </c>
       <c r="K65" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="L65" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="L65" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -3915,12 +3933,12 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>Casa Marina Key West, Curio Collection by Hilton</t>
+          <t>Melia Orlando Celebration</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>Melia</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
@@ -3930,32 +3948,32 @@
       </c>
       <c r="E66" s="5" t="inlineStr">
         <is>
-          <t>Key West Area</t>
+          <t>Orlando</t>
         </is>
       </c>
       <c r="F66" s="12" t="n">
-        <v>1491853</v>
+        <v>1448227</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H66" s="13" t="n">
-        <v>-21565.3</v>
+        <v>303.7799999999999</v>
       </c>
       <c r="I66" s="14" t="n">
-        <v>0.005914791872925819</v>
+        <v>0.01177923074214194</v>
       </c>
       <c r="J66" s="13" t="n">
-        <v>0</v>
+        <v>209.759934043489</v>
       </c>
       <c r="K66" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="L66" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="L66" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -3965,7 +3983,7 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>Hilton Garden Inn NYC Financial Center/Manhattan Downtown</t>
+          <t>Conrad Las Vegas at Resorts World</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
@@ -3980,32 +3998,32 @@
       </c>
       <c r="E67" s="5" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
       <c r="F67" s="12" t="n">
-        <v>1482208</v>
+        <v>1443928</v>
       </c>
       <c r="G67" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H67" s="13" t="n">
-        <v>0</v>
+        <v>364.01</v>
       </c>
       <c r="I67" s="14" t="n">
-        <v>0.00496151687212591</v>
+        <v>0.01593500506950485</v>
       </c>
       <c r="J67" s="13" t="n">
-        <v>0</v>
+        <v>252.0970574710096</v>
       </c>
       <c r="K67" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="L67" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="L67" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -4015,38 +4033,38 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>Hotel Cartagena Plaza</t>
+          <t>Hilton Garden Inn San Francisco/Oakland Bay Bridge</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>EM Hotels</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Estados Unidos de América</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
         <is>
-          <t>Cartagena Area</t>
+          <t>Oakland Area</t>
         </is>
       </c>
       <c r="F68" s="12" t="n">
-        <v>1479772</v>
+        <v>1441251</v>
       </c>
       <c r="G68" s="5" t="n">
         <v>2</v>
       </c>
       <c r="H68" s="13" t="n">
-        <v>317.14</v>
+        <v>327.21</v>
       </c>
       <c r="I68" s="14" t="n">
-        <v>0.01243434799415045</v>
+        <v>0.002384733818051124</v>
       </c>
       <c r="J68" s="13" t="n">
-        <v>214.3168001556997</v>
+        <v>227.0319326751551</v>
       </c>
       <c r="K68" s="10" t="inlineStr">
         <is>
@@ -4065,7 +4083,7 @@
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>Drury Inn &amp; Suites near Universal Orlando Resort</t>
+          <t>SAHARA Las Vegas</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
@@ -4080,32 +4098,32 @@
       </c>
       <c r="E69" s="5" t="inlineStr">
         <is>
-          <t>Orlando</t>
+          <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
       <c r="F69" s="12" t="n">
-        <v>1476575</v>
+        <v>1436715</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="H69" s="13" t="n">
-        <v>270.8000000000002</v>
+        <v>326.32</v>
       </c>
       <c r="I69" s="14" t="n">
-        <v>0.02084215160083301</v>
+        <v>0.03299192950585189</v>
       </c>
       <c r="J69" s="13" t="n">
-        <v>183.3973892284511</v>
-      </c>
-      <c r="K69" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="L69" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+        <v>227.1292497120166</v>
+      </c>
+      <c r="K69" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="L69" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -4115,38 +4133,38 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>Hilton Garden Inn Bogota Airport</t>
+          <t>NIZUC Resort &amp; Spa</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>Las Brisas</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>México</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
         <is>
-          <t>Bogotá Area</t>
+          <t>Cancún</t>
         </is>
       </c>
       <c r="F70" s="12" t="n">
-        <v>1472289</v>
+        <v>1430054</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H70" s="13" t="n">
-        <v>106.99</v>
+        <v>-2016.09</v>
       </c>
       <c r="I70" s="14" t="n">
-        <v>0.001274885569341345</v>
+        <v>0.01123454079356444</v>
       </c>
       <c r="J70" s="13" t="n">
-        <v>72.66915666693156</v>
+        <v>0</v>
       </c>
       <c r="K70" s="10" t="inlineStr">
         <is>
@@ -4165,12 +4183,12 @@
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>Embassy Suites by Hilton Orlando Lake Buena Vista Resort</t>
+          <t>Travelodge by Wyndham Downtown Chicago</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>Wyndham</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
@@ -4180,23 +4198,23 @@
       </c>
       <c r="E71" s="5" t="inlineStr">
         <is>
-          <t>Orlando</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="F71" s="12" t="n">
-        <v>1470361</v>
+        <v>1426682</v>
       </c>
       <c r="G71" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H71" s="13" t="n">
-        <v>245.26</v>
+        <v>144.42</v>
       </c>
       <c r="I71" s="14" t="n">
-        <v>0.01259894678925788</v>
+        <v>0.01401363443290096</v>
       </c>
       <c r="J71" s="13" t="n">
-        <v>166.8025743337861</v>
+        <v>101.2278839993776</v>
       </c>
       <c r="K71" s="10" t="inlineStr">
         <is>
@@ -4215,7 +4233,7 @@
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>Hilton Miami Downtown</t>
+          <t>Las Vegas Hilton at Resorts World</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
@@ -4230,27 +4248,27 @@
       </c>
       <c r="E72" s="5" t="inlineStr">
         <is>
-          <t>Miami Area</t>
+          <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
       <c r="F72" s="12" t="n">
-        <v>1468352</v>
+        <v>1415572</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H72" s="13" t="n">
-        <v>-390.14</v>
+        <v>-16.69</v>
       </c>
       <c r="I72" s="14" t="n">
-        <v>0.05420839144837205</v>
+        <v>0.01132051213219815</v>
       </c>
       <c r="J72" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="K72" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="K72" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="L72" s="7" t="inlineStr">
@@ -4265,35 +4283,35 @@
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>Hilton Garden Inn New York/Manhattan-Midtown East</t>
+          <t>Imperial Las Perlas</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>AA-Independent</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>Estados Unidos de América</t>
+          <t>México</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Cancún</t>
         </is>
       </c>
       <c r="F73" s="12" t="n">
-        <v>1464600</v>
+        <v>1409277</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H73" s="13" t="n">
-        <v>0</v>
+        <v>-3812.88</v>
       </c>
       <c r="I73" s="14" t="n">
-        <v>0.005942236788201557</v>
+        <v>0.01265187752301357</v>
       </c>
       <c r="J73" s="13" t="n">
         <v>0</v>
@@ -4315,47 +4333,47 @@
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>Embassy Suites by Hilton Fort Lauderdale 17th Street</t>
+          <t>Nobu Hotel Los Cabos</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>PAM Hotels</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>Estados Unidos de América</t>
+          <t>México</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
         <is>
-          <t>Fort Lauderdale (and vicinity), FL, US</t>
+          <t>Los Cabos Area</t>
         </is>
       </c>
       <c r="F74" s="12" t="n">
-        <v>1457682</v>
+        <v>1404575</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H74" s="13" t="n">
-        <v>391.63</v>
+        <v>-1244.76</v>
       </c>
       <c r="I74" s="14" t="n">
-        <v>0.01006323738648073</v>
+        <v>0.008794831176690459</v>
       </c>
       <c r="J74" s="13" t="n">
-        <v>268.6662797510019</v>
+        <v>0</v>
       </c>
       <c r="K74" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="L74" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="L74" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -4365,47 +4383,47 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>Melia Orlando Celebration</t>
+          <t>Holiday Inn Toronto Downtown Centre by IHG</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>Melia</t>
+          <t>IHG</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>Estados Unidos de América</t>
+          <t>Canadá</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
         <is>
-          <t>Orlando</t>
+          <t>Toronto Area</t>
         </is>
       </c>
       <c r="F75" s="12" t="n">
-        <v>1448227</v>
+        <v>1400554</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H75" s="13" t="n">
-        <v>303.7799999999999</v>
+        <v>-693.54</v>
       </c>
       <c r="I75" s="14" t="n">
-        <v>0.01177923074214194</v>
+        <v>0.1724910285501309</v>
       </c>
       <c r="J75" s="13" t="n">
-        <v>209.759934043489</v>
-      </c>
-      <c r="K75" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="L75" s="8" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="K75" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
+        </is>
+      </c>
+      <c r="L75" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -4415,38 +4433,38 @@
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>Park MGM Las Vegas</t>
+          <t>Caribe Hilton</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>MGM Resorts</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>Estados Unidos de América</t>
+          <t>Puerto Rico</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
         <is>
-          <t>Las Vegas (and vicinity), NV, US</t>
+          <t>Puerto Rico</t>
         </is>
       </c>
       <c r="F76" s="12" t="n">
-        <v>1445284</v>
+        <v>1391463</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="H76" s="13" t="n">
-        <v>917.4000000000001</v>
+        <v>687.76</v>
       </c>
       <c r="I76" s="14" t="n">
-        <v>0.02041536473108399</v>
+        <v>0.006376022934134793</v>
       </c>
       <c r="J76" s="13" t="n">
-        <v>634.754138287008</v>
+        <v>494.2711376443355</v>
       </c>
       <c r="K76" s="10" t="inlineStr">
         <is>
@@ -4465,7 +4483,7 @@
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>Conrad Las Vegas at Resorts World</t>
+          <t>Hilton Vallarta Riviera - All Inclusive</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
@@ -4475,37 +4493,37 @@
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>Estados Unidos de América</t>
+          <t>México</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
         <is>
-          <t>Las Vegas (and vicinity), NV, US</t>
+          <t>Puerto Vallarta Area</t>
         </is>
       </c>
       <c r="F77" s="12" t="n">
-        <v>1443928</v>
+        <v>1385069</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="H77" s="13" t="n">
-        <v>364.01</v>
+        <v>-12674.69</v>
       </c>
       <c r="I77" s="14" t="n">
-        <v>0.01593500506950485</v>
+        <v>0.002010730151349861</v>
       </c>
       <c r="J77" s="13" t="n">
-        <v>252.0970574710096</v>
+        <v>0</v>
       </c>
       <c r="K77" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="L77" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="L77" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -4515,7 +4533,7 @@
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>Hilton Garden Inn San Francisco/Oakland Bay Bridge</t>
+          <t>DoubleTree by Hilton Newark Penn Station</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
@@ -4530,32 +4548,32 @@
       </c>
       <c r="E78" s="5" t="inlineStr">
         <is>
-          <t>Oakland Area</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="F78" s="12" t="n">
-        <v>1441251</v>
+        <v>1361011</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H78" s="13" t="n">
-        <v>327.21</v>
+        <v>-2094.68</v>
       </c>
       <c r="I78" s="14" t="n">
-        <v>0.002384733818051124</v>
+        <v>0.002459201284927161</v>
       </c>
       <c r="J78" s="13" t="n">
-        <v>227.0319326751551</v>
+        <v>0</v>
       </c>
       <c r="K78" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="L78" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="L78" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -4565,7 +4583,7 @@
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>SAHARA Las Vegas</t>
+          <t>DoubleTree by Hilton Philadelphia Center City</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
@@ -4580,32 +4598,32 @@
       </c>
       <c r="E79" s="5" t="inlineStr">
         <is>
-          <t>Las Vegas (and vicinity), NV, US</t>
+          <t>Philadelphia (and vicinity), PA, US</t>
         </is>
       </c>
       <c r="F79" s="12" t="n">
-        <v>1436715</v>
+        <v>1353950</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="H79" s="13" t="n">
-        <v>326.32</v>
+        <v>-4852.61</v>
       </c>
       <c r="I79" s="14" t="n">
-        <v>0.03299192950585189</v>
+        <v>0.009084530447948595</v>
       </c>
       <c r="J79" s="13" t="n">
-        <v>227.1292497120166</v>
-      </c>
-      <c r="K79" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
-        </is>
-      </c>
-      <c r="L79" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+        <v>0</v>
+      </c>
+      <c r="K79" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="L79" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -4615,35 +4633,35 @@
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>NIZUC Resort &amp; Spa</t>
+          <t>Holiday Inn Miami Beach - Oceanfront by IHG</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>Las Brisas</t>
+          <t>IHG</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>Estados Unidos de América</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
         <is>
-          <t>Cancún</t>
+          <t>Miami Area</t>
         </is>
       </c>
       <c r="F80" s="12" t="n">
-        <v>1430054</v>
+        <v>1353657</v>
       </c>
       <c r="G80" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H80" s="13" t="n">
-        <v>-2016.09</v>
+        <v>-713.61</v>
       </c>
       <c r="I80" s="14" t="n">
-        <v>0.01123454079356444</v>
+        <v>0.01526383714633766</v>
       </c>
       <c r="J80" s="13" t="n">
         <v>0</v>
@@ -4665,12 +4683,12 @@
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>Travelodge by Wyndham Downtown Chicago</t>
+          <t>Hyatt Place Waikiki Beach</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>Wyndham</t>
+          <t>Hyatt</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
@@ -4680,23 +4698,23 @@
       </c>
       <c r="E81" s="5" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>Honolulu Area</t>
         </is>
       </c>
       <c r="F81" s="12" t="n">
-        <v>1426682</v>
+        <v>1353103</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H81" s="13" t="n">
-        <v>144.42</v>
+        <v>-993.8000000000002</v>
       </c>
       <c r="I81" s="14" t="n">
-        <v>0.01401363443290096</v>
+        <v>0.003455760574028733</v>
       </c>
       <c r="J81" s="13" t="n">
-        <v>101.2278839993776</v>
+        <v>0</v>
       </c>
       <c r="K81" s="10" t="inlineStr">
         <is>
@@ -4715,47 +4733,47 @@
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>Hilton Copacabana Rio de Janeiro</t>
+          <t>Wyndham Grand Orlando Resort Bonnet Creek</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>Wyndham</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Estados Unidos de América</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
         <is>
-          <t>Río de Janeiro</t>
+          <t>Orlando</t>
         </is>
       </c>
       <c r="F82" s="12" t="n">
-        <v>1426586</v>
+        <v>1344636</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H82" s="13" t="n">
-        <v>844.2099999999999</v>
+        <v>-18.41000000000003</v>
       </c>
       <c r="I82" s="14" t="n">
-        <v>0.1185193181483626</v>
+        <v>0.004821379168786199</v>
       </c>
       <c r="J82" s="13" t="n">
-        <v>591.769441169337</v>
-      </c>
-      <c r="K82" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
-        </is>
-      </c>
-      <c r="L82" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+        <v>0</v>
+      </c>
+      <c r="K82" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="L82" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -4765,12 +4783,12 @@
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>Holiday Inn Club Vacations at Orange Lake Resort, an IHG Hotel</t>
+          <t>Hyatt Regency Washington on Capitol Hill</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>IHG</t>
+          <t>Hyatt</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
@@ -4780,23 +4798,23 @@
       </c>
       <c r="E83" s="5" t="inlineStr">
         <is>
-          <t>Orlando</t>
+          <t>Greenville Area</t>
         </is>
       </c>
       <c r="F83" s="12" t="n">
-        <v>1420424</v>
+        <v>1333109</v>
       </c>
       <c r="G83" s="5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H83" s="13" t="n">
-        <v>870.9400000000001</v>
+        <v>621.4499999999994</v>
       </c>
       <c r="I83" s="14" t="n">
-        <v>0.007844840695454314</v>
+        <v>0.01050401730091088</v>
       </c>
       <c r="J83" s="13" t="n">
-        <v>613.1549452839434</v>
+        <v>466.1659324181289</v>
       </c>
       <c r="K83" s="10" t="inlineStr">
         <is>
@@ -4815,42 +4833,42 @@
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>Las Vegas Hilton at Resorts World</t>
+          <t>Catalonia Royal Bávaro</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>AA-Independent</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>Estados Unidos de América</t>
+          <t>República Dominicana</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
         <is>
-          <t>Las Vegas (and vicinity), NV, US</t>
+          <t>Punta Cana</t>
         </is>
       </c>
       <c r="F84" s="12" t="n">
-        <v>1415572</v>
+        <v>1331323</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H84" s="13" t="n">
-        <v>-16.69</v>
+        <v>136.1000000000001</v>
       </c>
       <c r="I84" s="14" t="n">
-        <v>0.01132051213219815</v>
+        <v>0.3530811080406483</v>
       </c>
       <c r="J84" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K84" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+        <v>102.2291359797736</v>
+      </c>
+      <c r="K84" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
       <c r="L84" s="7" t="inlineStr">
@@ -4865,7 +4883,7 @@
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>Imperial Las Perlas</t>
+          <t>Gold Coast Hotel and Casino</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
@@ -4875,32 +4893,32 @@
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>Estados Unidos de América</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
         <is>
-          <t>Cancún</t>
+          <t>Las Vegas (and vicinity), NV, US</t>
         </is>
       </c>
       <c r="F85" s="12" t="n">
-        <v>1409277</v>
+        <v>1327791</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H85" s="13" t="n">
-        <v>-3812.88</v>
+        <v>-244.25</v>
       </c>
       <c r="I85" s="14" t="n">
-        <v>0.01265187752301357</v>
+        <v>0.0336498741142243</v>
       </c>
       <c r="J85" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="K85" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="K85" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="L85" s="7" t="inlineStr">
@@ -4915,35 +4933,35 @@
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>Nobu Hotel Los Cabos</t>
+          <t>Hotel Figueroa, Unbound Collection by Hyatt</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>PAM Hotels</t>
+          <t>Hyatt</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>Estados Unidos de América</t>
         </is>
       </c>
       <c r="E86" s="5" t="inlineStr">
         <is>
-          <t>Los Cabos Area</t>
+          <t>Los Angeles (and vicinity), CA, US</t>
         </is>
       </c>
       <c r="F86" s="12" t="n">
-        <v>1404575</v>
+        <v>1327437</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H86" s="13" t="n">
-        <v>-1244.76</v>
+        <v>-585.99</v>
       </c>
       <c r="I86" s="14" t="n">
-        <v>0.008794831176690459</v>
+        <v>0.01122087149898639</v>
       </c>
       <c r="J86" s="13" t="n">
         <v>0</v>
@@ -4965,7 +4983,7 @@
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>DoubleTree by Hilton Sunrise - Sawgrass Mills</t>
+          <t>Conrad New York Downtown</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
@@ -4980,32 +4998,32 @@
       </c>
       <c r="E87" s="5" t="inlineStr">
         <is>
-          <t>Fort Lauderdale (and vicinity), FL, US</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="F87" s="12" t="n">
-        <v>1401288</v>
+        <v>1325289</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H87" s="13" t="n">
-        <v>788.8499999999999</v>
+        <v>-2380.440000000001</v>
       </c>
       <c r="I87" s="14" t="n">
-        <v>0.008039746290555545</v>
+        <v>0.03795172222813288</v>
       </c>
       <c r="J87" s="13" t="n">
-        <v>562.9463750492403</v>
-      </c>
-      <c r="K87" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="L87" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+        <v>0</v>
+      </c>
+      <c r="K87" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="L87" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -5015,42 +5033,42 @@
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>Holiday Inn Toronto Downtown Centre by IHG</t>
+          <t>Hilton Garden Inn Veracruz Boca del Rio</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>IHG</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>México</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
         <is>
-          <t>Toronto Area</t>
+          <t>Veracruz Area</t>
         </is>
       </c>
       <c r="F88" s="12" t="n">
-        <v>1400554</v>
+        <v>1315312</v>
       </c>
       <c r="G88" s="5" t="n">
         <v>2</v>
       </c>
       <c r="H88" s="13" t="n">
-        <v>-693.54</v>
+        <v>240.95</v>
       </c>
       <c r="I88" s="14" t="n">
-        <v>0.1724910285501309</v>
+        <v>0.005057355213059715</v>
       </c>
       <c r="J88" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K88" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+        <v>183.1884754339655</v>
+      </c>
+      <c r="K88" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="L88" s="7" t="inlineStr">
@@ -5065,7 +5083,7 @@
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>Caribe Hilton</t>
+          <t>Hilton Cancun, an All Inclusive Resort</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
@@ -5075,37 +5093,37 @@
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>Puerto Rico</t>
+          <t>México</t>
         </is>
       </c>
       <c r="E89" s="5" t="inlineStr">
         <is>
-          <t>Puerto Rico</t>
+          <t>Cancún</t>
         </is>
       </c>
       <c r="F89" s="12" t="n">
-        <v>1391463</v>
+        <v>1310035</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H89" s="13" t="n">
-        <v>687.76</v>
+        <v>-1688.03</v>
       </c>
       <c r="I89" s="14" t="n">
-        <v>0.006376022934134793</v>
+        <v>0.006960119386123271</v>
       </c>
       <c r="J89" s="13" t="n">
-        <v>494.2711376443355</v>
+        <v>0</v>
       </c>
       <c r="K89" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="L89" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="L89" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -5115,47 +5133,47 @@
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>Hilton Vallarta Riviera - All Inclusive</t>
+          <t>Wyndham Grand Pittsburgh Downtown</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>Wyndham</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>Estados Unidos de América</t>
         </is>
       </c>
       <c r="E90" s="5" t="inlineStr">
         <is>
-          <t>Puerto Vallarta Area</t>
+          <t>Pittsburgh Area</t>
         </is>
       </c>
       <c r="F90" s="12" t="n">
-        <v>1385069</v>
+        <v>1301278</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="H90" s="13" t="n">
-        <v>-12674.69</v>
+        <v>268.2999999999999</v>
       </c>
       <c r="I90" s="14" t="n">
-        <v>0.002010730151349861</v>
+        <v>0.005064252219740901</v>
       </c>
       <c r="J90" s="13" t="n">
-        <v>0</v>
+        <v>206.1819226944588</v>
       </c>
       <c r="K90" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="L90" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="L90" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -5165,12 +5183,12 @@
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>DoubleTree by Hilton Newark Penn Station</t>
+          <t>Hyatt Regency Clearwater Beach Resort and Suites</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>Hyatt</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
@@ -5180,32 +5198,32 @@
       </c>
       <c r="E91" s="5" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Clearwater</t>
         </is>
       </c>
       <c r="F91" s="12" t="n">
-        <v>1361011</v>
+        <v>1294678</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H91" s="13" t="n">
-        <v>-2094.68</v>
+        <v>485.79</v>
       </c>
       <c r="I91" s="14" t="n">
-        <v>0.002459201284927161</v>
+        <v>0.008500183057099911</v>
       </c>
       <c r="J91" s="13" t="n">
-        <v>0</v>
+        <v>375.2207112502105</v>
       </c>
       <c r="K91" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="L91" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="L91" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -5215,12 +5233,12 @@
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>DoubleTree by Hilton Philadelphia Center City</t>
+          <t>Motto By Hilton New York City Times Square</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>AA-Independent</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
@@ -5230,20 +5248,20 @@
       </c>
       <c r="E92" s="5" t="inlineStr">
         <is>
-          <t>Philadelphia (and vicinity), PA, US</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="F92" s="12" t="n">
-        <v>1353950</v>
+        <v>1292664</v>
       </c>
       <c r="G92" s="5" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="H92" s="13" t="n">
-        <v>-4852.61</v>
+        <v>-2641.58</v>
       </c>
       <c r="I92" s="14" t="n">
-        <v>0.009084530447948595</v>
+        <v>0.01188243812777334</v>
       </c>
       <c r="J92" s="13" t="n">
         <v>0</v>
@@ -5265,12 +5283,12 @@
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>Holiday Inn Miami Beach - Oceanfront by IHG</t>
+          <t>Hilton Garden Inn Chicago Downtown/Magnificent Mile</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>IHG</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr">
@@ -5280,20 +5298,20 @@
       </c>
       <c r="E93" s="5" t="inlineStr">
         <is>
-          <t>Miami Area</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="F93" s="12" t="n">
-        <v>1353657</v>
+        <v>1292441</v>
       </c>
       <c r="G93" s="5" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H93" s="13" t="n">
-        <v>-713.61</v>
+        <v>-1249.88</v>
       </c>
       <c r="I93" s="14" t="n">
-        <v>0.01526383714633766</v>
+        <v>0.028245003060101</v>
       </c>
       <c r="J93" s="13" t="n">
         <v>0</v>
@@ -5315,7 +5333,7 @@
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>Hyatt Place Waikiki Beach</t>
+          <t>Hyatt Centric Waikiki Beach</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
@@ -5334,16 +5352,16 @@
         </is>
       </c>
       <c r="F94" s="12" t="n">
-        <v>1353103</v>
+        <v>1284552</v>
       </c>
       <c r="G94" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H94" s="13" t="n">
-        <v>-993.8000000000002</v>
+        <v>-507.1599999999999</v>
       </c>
       <c r="I94" s="14" t="n">
-        <v>0.003455760574028733</v>
+        <v>0.005255528775791093</v>
       </c>
       <c r="J94" s="13" t="n">
         <v>0</v>
@@ -5365,35 +5383,35 @@
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>Wyndham Grand Orlando Resort Bonnet Creek</t>
+          <t>Sunscape Curaçao Resort, Spa &amp; Casino</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>Wyndham</t>
+          <t>Hyatt Inclusive Collection</t>
         </is>
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>Estados Unidos de América</t>
+          <t>Curazao</t>
         </is>
       </c>
       <c r="E95" s="5" t="inlineStr">
         <is>
-          <t>Orlando</t>
+          <t>Curacao Area</t>
         </is>
       </c>
       <c r="F95" s="12" t="n">
-        <v>1344636</v>
+        <v>1280590</v>
       </c>
       <c r="G95" s="5" t="n">
         <v>2</v>
       </c>
       <c r="H95" s="13" t="n">
-        <v>-18.41000000000003</v>
+        <v>-895.6799999999999</v>
       </c>
       <c r="I95" s="14" t="n">
-        <v>0.004821379168786199</v>
+        <v>0.005957410256210028</v>
       </c>
       <c r="J95" s="13" t="n">
         <v>0</v>
@@ -5415,47 +5433,47 @@
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>Hyatt Regency Washington on Capitol Hill</t>
+          <t>Dreams Aventuras Riviera Maya - All Inclusive</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>Hyatt</t>
+          <t>Hyatt Inclusive Collection</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>Estados Unidos de América</t>
+          <t>México</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
         <is>
-          <t>Greenville Area</t>
+          <t>Riviera Maya</t>
         </is>
       </c>
       <c r="F96" s="12" t="n">
-        <v>1333109</v>
+        <v>1279430</v>
       </c>
       <c r="G96" s="5" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="H96" s="13" t="n">
-        <v>621.4499999999994</v>
+        <v>-1035.07</v>
       </c>
       <c r="I96" s="14" t="n">
-        <v>0.01050401730091088</v>
+        <v>0.0104937354915861</v>
       </c>
       <c r="J96" s="13" t="n">
-        <v>466.1659324181289</v>
+        <v>0</v>
       </c>
       <c r="K96" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="L96" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="L96" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -5465,42 +5483,42 @@
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>Catalonia Royal Bávaro</t>
+          <t>Hyatt House Jersey City</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>AA-Independent</t>
+          <t>Hyatt</t>
         </is>
       </c>
       <c r="D97" s="5" t="inlineStr">
         <is>
-          <t>República Dominicana</t>
+          <t>Estados Unidos de América</t>
         </is>
       </c>
       <c r="E97" s="5" t="inlineStr">
         <is>
-          <t>Punta Cana</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="F97" s="12" t="n">
-        <v>1331323</v>
+        <v>1267987</v>
       </c>
       <c r="G97" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H97" s="13" t="n">
-        <v>136.1000000000001</v>
+        <v>-891.17</v>
       </c>
       <c r="I97" s="14" t="n">
-        <v>0.3530811080406483</v>
+        <v>0.00333284174049103</v>
       </c>
       <c r="J97" s="13" t="n">
-        <v>102.2291359797736</v>
-      </c>
-      <c r="K97" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+        <v>0</v>
+      </c>
+      <c r="K97" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="L97" s="7" t="inlineStr">
@@ -5515,12 +5533,12 @@
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>Gold Coast Hotel and Casino</t>
+          <t>Holiday Inn Express New York - Manhattan West Side by IHG</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>AA-Independent</t>
+          <t>IHG</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
@@ -5530,27 +5548,27 @@
       </c>
       <c r="E98" s="5" t="inlineStr">
         <is>
-          <t>Las Vegas (and vicinity), NV, US</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="F98" s="12" t="n">
-        <v>1327791</v>
+        <v>1263088</v>
       </c>
       <c r="G98" s="5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H98" s="13" t="n">
-        <v>-244.25</v>
+        <v>-927.49</v>
       </c>
       <c r="I98" s="14" t="n">
-        <v>0.0336498741142243</v>
+        <v>0.01917760282735645</v>
       </c>
       <c r="J98" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="K98" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="K98" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="L98" s="7" t="inlineStr">
@@ -5565,12 +5583,12 @@
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>Hotel Figueroa, Unbound Collection by Hyatt</t>
+          <t>InterContinental New York Barclay by IHG</t>
         </is>
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>Hyatt</t>
+          <t>IHG</t>
         </is>
       </c>
       <c r="D99" s="5" t="inlineStr">
@@ -5580,27 +5598,27 @@
       </c>
       <c r="E99" s="5" t="inlineStr">
         <is>
-          <t>Los Angeles (and vicinity), CA, US</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="F99" s="12" t="n">
-        <v>1327437</v>
+        <v>1262448</v>
       </c>
       <c r="G99" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H99" s="13" t="n">
-        <v>-585.99</v>
+        <v>-2613.76</v>
       </c>
       <c r="I99" s="14" t="n">
-        <v>0.01122087149898639</v>
+        <v>0.05031098310583881</v>
       </c>
       <c r="J99" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="K99" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="K99" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
       <c r="L99" s="7" t="inlineStr">
@@ -5615,7 +5633,7 @@
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t>Conrad New York Downtown</t>
+          <t>Doubletree Resort by Hilton Hollywood Beach</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
@@ -5630,32 +5648,32 @@
       </c>
       <c r="E100" s="5" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Fort Lauderdale (and vicinity), FL, US</t>
         </is>
       </c>
       <c r="F100" s="12" t="n">
-        <v>1325289</v>
+        <v>1257442</v>
       </c>
       <c r="G100" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H100" s="13" t="n">
-        <v>-2380.440000000001</v>
+        <v>354.68</v>
       </c>
       <c r="I100" s="14" t="n">
-        <v>0.03795172222813288</v>
+        <v>0.04186276583731099</v>
       </c>
       <c r="J100" s="13" t="n">
-        <v>0</v>
+        <v>282.064699604435</v>
       </c>
       <c r="K100" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="L100" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="L100" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -5665,7 +5683,7 @@
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>Hilton Garden Inn Veracruz Boca del Rio</t>
+          <t>Hilton San Francisco Union Square</t>
         </is>
       </c>
       <c r="C101" s="5" t="inlineStr">
@@ -5675,32 +5693,32 @@
       </c>
       <c r="D101" s="5" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>Estados Unidos de América</t>
         </is>
       </c>
       <c r="E101" s="5" t="inlineStr">
         <is>
-          <t>Veracruz Area</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F101" s="12" t="n">
-        <v>1315312</v>
+        <v>1253913</v>
       </c>
       <c r="G101" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H101" s="13" t="n">
-        <v>240.95</v>
+        <v>154.85</v>
       </c>
       <c r="I101" s="14" t="n">
-        <v>0.005057355213059715</v>
+        <v>0.06464164579201269</v>
       </c>
       <c r="J101" s="13" t="n">
-        <v>183.1884754339655</v>
-      </c>
-      <c r="K101" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+        <v>123.4934162098965</v>
+      </c>
+      <c r="K101" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
       <c r="L101" s="7" t="inlineStr">
@@ -5715,12 +5733,12 @@
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>Hilton Cancun, an All Inclusive Resort</t>
+          <t>Sandos Caracol Nature Resort &amp; Water Park All Inclusive</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>Sandos</t>
         </is>
       </c>
       <c r="D102" s="5" t="inlineStr">
@@ -5730,27 +5748,27 @@
       </c>
       <c r="E102" s="5" t="inlineStr">
         <is>
-          <t>Cancún</t>
+          <t>Riviera Maya</t>
         </is>
       </c>
       <c r="F102" s="12" t="n">
-        <v>1310035</v>
+        <v>1223013</v>
       </c>
       <c r="G102" s="5" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H102" s="13" t="n">
-        <v>-1688.03</v>
+        <v>-5301.34</v>
       </c>
       <c r="I102" s="14" t="n">
-        <v>0.006960119386123271</v>
+        <v>0.03343627582045326</v>
       </c>
       <c r="J102" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="K102" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="K102" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="L102" s="7" t="inlineStr">
@@ -5765,47 +5783,47 @@
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>Bahia Principe Escape Aquamarine</t>
+          <t>Hilton Philadelphia at Penn's Landing</t>
         </is>
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>Bahia Principe</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
-          <t>República Dominicana</t>
+          <t>Estados Unidos de América</t>
         </is>
       </c>
       <c r="E103" s="5" t="inlineStr">
         <is>
-          <t>Punta Cana</t>
+          <t>Philadelphia (and vicinity), PA, US</t>
         </is>
       </c>
       <c r="F103" s="12" t="n">
-        <v>1303828</v>
+        <v>1217300</v>
       </c>
       <c r="G103" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H103" s="13" t="n">
-        <v>726.64</v>
+        <v>30.12000000000006</v>
       </c>
       <c r="I103" s="14" t="n">
-        <v>0.004977650426283222</v>
+        <v>0.02324735069415921</v>
       </c>
       <c r="J103" s="13" t="n">
-        <v>557.3127743843513</v>
+        <v>24.74328431775245</v>
       </c>
       <c r="K103" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="L103" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="L103" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -5815,38 +5833,38 @@
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
-          <t>Wyndham Grand Pittsburgh Downtown</t>
+          <t>Hotel Maya Caribe Faranda Cancún</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>Wyndham</t>
+          <t>AA-Independent</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>Estados Unidos de América</t>
+          <t>México</t>
         </is>
       </c>
       <c r="E104" s="5" t="inlineStr">
         <is>
-          <t>Pittsburgh Area</t>
+          <t>Cancún</t>
         </is>
       </c>
       <c r="F104" s="12" t="n">
-        <v>1301278</v>
+        <v>1215748</v>
       </c>
       <c r="G104" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H104" s="13" t="n">
-        <v>268.2999999999999</v>
+        <v>403.7</v>
       </c>
       <c r="I104" s="14" t="n">
-        <v>0.005064252219740901</v>
+        <v>0.01127865314193402</v>
       </c>
       <c r="J104" s="13" t="n">
-        <v>206.1819226944588</v>
+        <v>332.0589464263976</v>
       </c>
       <c r="K104" s="10" t="inlineStr">
         <is>
@@ -5865,7 +5883,7 @@
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>Hyatt Regency Clearwater Beach Resort and Suites</t>
+          <t>Hyatt Centric Wall Street New York</t>
         </is>
       </c>
       <c r="C105" s="5" t="inlineStr">
@@ -5880,32 +5898,32 @@
       </c>
       <c r="E105" s="5" t="inlineStr">
         <is>
-          <t>Clearwater</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="F105" s="12" t="n">
-        <v>1294678</v>
+        <v>1215692</v>
       </c>
       <c r="G105" s="5" t="n">
         <v>2</v>
       </c>
       <c r="H105" s="13" t="n">
-        <v>485.79</v>
+        <v>0</v>
       </c>
       <c r="I105" s="14" t="n">
-        <v>0.008500183057099911</v>
+        <v>0.08068408774590932</v>
       </c>
       <c r="J105" s="13" t="n">
-        <v>375.2207112502105</v>
-      </c>
-      <c r="K105" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="L105" s="8" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="K105" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
+        </is>
+      </c>
+      <c r="L105" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -5951,7 +5969,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -9946,7 +9964,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14549,7 +14567,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -16379,9 +16397,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I56" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="I56" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -17652,7 +17670,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -17767,9 +17785,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I7" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="I7" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -18187,9 +18205,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I19" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="I19" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -19027,9 +19045,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I43" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="I43" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -19517,9 +19535,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I57" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="I57" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -19727,9 +19745,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I63" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="I63" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -19867,9 +19885,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I67" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="I67" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -20077,9 +20095,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I73" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="I73" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -20707,9 +20725,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I91" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="I91" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -20742,9 +20760,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I92" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="I92" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -20777,9 +20795,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I93" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="I93" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -21245,7 +21263,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -21500,9 +21518,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I11" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="I11" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -21605,9 +21623,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I14" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="I14" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -21885,9 +21903,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I22" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="I22" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -22200,9 +22218,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I31" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="I31" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -22270,9 +22288,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I33" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="I33" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -22655,9 +22673,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I44" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="I44" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>

--- a/rates-nodispo/week-20/Analisis_Rates_NoDispo_OP_7d.xlsx
+++ b/rates-nodispo/week-20/Analisis_Rates_NoDispo_OP_7d.xlsx
@@ -547,7 +547,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -861,7 +861,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -5969,7 +5969,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -9964,7 +9964,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14567,7 +14567,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -17670,7 +17670,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -21263,7 +21263,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>

--- a/rates-nodispo/week-20/Analisis_Rates_NoDispo_OP_7d.xlsx
+++ b/rates-nodispo/week-20/Analisis_Rates_NoDispo_OP_7d.xlsx
@@ -547,7 +547,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:55 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:55 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -861,7 +861,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:55 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -5969,7 +5969,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:55 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -9964,7 +9964,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:55 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14567,7 +14567,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:55 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -17670,7 +17670,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:55 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -21263,7 +21263,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:55 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>

--- a/rates-nodispo/week-20/Analisis_Rates_NoDispo_OP_7d.xlsx
+++ b/rates-nodispo/week-20/Analisis_Rates_NoDispo_OP_7d.xlsx
@@ -547,7 +547,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:55 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 04:09 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:55 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 04:09 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -861,7 +861,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:55 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 04:09 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -5969,7 +5969,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:55 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 04:09 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -9964,7 +9964,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:55 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 04:09 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14567,7 +14567,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:55 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 04:09 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -17670,7 +17670,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:55 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 04:09 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -21263,7 +21263,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:55 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 04:09 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>

--- a/rates-nodispo/week-20/Analisis_Rates_NoDispo_OP_7d.xlsx
+++ b/rates-nodispo/week-20/Analisis_Rates_NoDispo_OP_7d.xlsx
@@ -547,7 +547,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 04:09 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 05:04 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -585,10 +585,10 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>0.0008630113342155227</v>
+        <v>0.0008435050114121266</v>
       </c>
     </row>
     <row r="7">
@@ -603,10 +603,10 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>256</v>
+        <v>288</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0.01472872677061159</v>
+        <v>0.01428996725215838</v>
       </c>
     </row>
     <row r="8">
@@ -621,10 +621,10 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>1475</v>
+        <v>1603</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>0.08486278119785973</v>
+        <v>0.07953756078197877</v>
       </c>
     </row>
     <row r="9">
@@ -639,10 +639,10 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>945</v>
+        <v>1030</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0.05436971405557793</v>
+        <v>0.05110648010320532</v>
       </c>
     </row>
     <row r="10">
@@ -657,10 +657,10 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>14690</v>
+        <v>17216</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>0.8451757666417352</v>
+        <v>0.8542224868512454</v>
       </c>
     </row>
   </sheetData>
@@ -700,7 +700,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 04:09 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 05:04 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -738,10 +738,10 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>12299</v>
+        <v>14934</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>0.7076117599677809</v>
+        <v>0.7409943435546293</v>
       </c>
     </row>
     <row r="7">
@@ -756,10 +756,10 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>1055</v>
+        <v>1086</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0.0606984638398251</v>
+        <v>0.05388508484668056</v>
       </c>
     </row>
     <row r="8">
@@ -774,10 +774,10 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>0.02151774926644037</v>
+        <v>0.01850749230921901</v>
       </c>
     </row>
     <row r="9">
@@ -795,7 +795,7 @@
         <v>209</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0.01202462459006962</v>
+        <v>0.01037014984618438</v>
       </c>
     </row>
     <row r="10">
@@ -810,10 +810,10 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>3444</v>
+        <v>3552</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>0.198147402335884</v>
+        <v>0.1762429294432867</v>
       </c>
     </row>
   </sheetData>
@@ -861,7 +861,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 04:09 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 05:04 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -5969,7 +5969,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 04:09 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 05:04 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -9964,7 +9964,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 04:09 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 05:04 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14567,7 +14567,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 04:09 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 05:04 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14628,19 +14628,19 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>1244388549</v>
+        <v>1279051832</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>4502</v>
+        <v>4523</v>
       </c>
       <c r="E6" s="13" t="n">
-        <v>916415.29</v>
+        <v>916508.0600000001</v>
       </c>
       <c r="F6" s="14" t="n">
-        <v>0.0107892402343217</v>
+        <v>0.01065309447131146</v>
       </c>
       <c r="G6" s="13" t="n">
-        <v>736.4382215960106</v>
+        <v>716.552712775443</v>
       </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
@@ -14663,19 +14663,19 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>911163892</v>
+        <v>932708520</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>8745</v>
+        <v>8951</v>
       </c>
       <c r="E7" s="13" t="n">
-        <v>1330870.76</v>
+        <v>1363502.2</v>
       </c>
       <c r="F7" s="14" t="n">
-        <v>0.01188948233694932</v>
+        <v>0.01181284802673401</v>
       </c>
       <c r="G7" s="13" t="n">
-        <v>1460.627195266425</v>
+        <v>1461.873855296186</v>
       </c>
       <c r="H7" s="10" t="inlineStr">
         <is>
@@ -14698,7 +14698,7 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>440264951</v>
+        <v>468784341</v>
       </c>
       <c r="D8" s="5" t="n">
         <v>234</v>
@@ -14707,10 +14707,10 @@
         <v>59090.77</v>
       </c>
       <c r="F8" s="14" t="n">
-        <v>0.006619943271387051</v>
+        <v>0.00654135117537981</v>
       </c>
       <c r="G8" s="13" t="n">
-        <v>134.2163846242668</v>
+        <v>126.0510747307577</v>
       </c>
       <c r="H8" s="10" t="inlineStr">
         <is>
@@ -14733,19 +14733,19 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>429613028</v>
+        <v>436803653</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>1902</v>
+        <v>1916</v>
       </c>
       <c r="E9" s="13" t="n">
-        <v>504966.9100000001</v>
+        <v>505974.6100000001</v>
       </c>
       <c r="F9" s="14" t="n">
-        <v>0.04818223762059655</v>
+        <v>0.04847374067176128</v>
       </c>
       <c r="G9" s="13" t="n">
-        <v>1175.399434115858</v>
+        <v>1158.357093684837</v>
       </c>
       <c r="H9" s="9" t="inlineStr">
         <is>
@@ -14768,19 +14768,19 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>400214424</v>
+        <v>402091064</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>2888</v>
+        <v>2904</v>
       </c>
       <c r="E10" s="13" t="n">
-        <v>1018183.16</v>
+        <v>1024068.78</v>
       </c>
       <c r="F10" s="14" t="n">
-        <v>0.01540912228590742</v>
+        <v>0.01538662893537967</v>
       </c>
       <c r="G10" s="13" t="n">
-        <v>2544.094112909834</v>
+        <v>2546.857843127795</v>
       </c>
       <c r="H10" s="10" t="inlineStr">
         <is>
@@ -14799,32 +14799,32 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Accor</t>
+          <t>CHOICE</t>
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>238357281</v>
+        <v>300307868</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>150</v>
+        <v>96</v>
       </c>
       <c r="E11" s="13" t="n">
-        <v>52275.63</v>
+        <v>6778.21</v>
       </c>
       <c r="F11" s="14" t="n">
-        <v>0.05681845313548445</v>
+        <v>0.009440471935953406</v>
       </c>
       <c r="G11" s="13" t="n">
-        <v>219.3162708547594</v>
-      </c>
-      <c r="H11" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
-        </is>
-      </c>
-      <c r="I11" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+        <v>22.57087050413211</v>
+      </c>
+      <c r="H11" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -14838,19 +14838,19 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>231449646</v>
+        <v>260152686</v>
       </c>
       <c r="D12" s="5" t="n">
         <v>110</v>
       </c>
       <c r="E12" s="13" t="n">
-        <v>16203.68</v>
+        <v>19426.52</v>
       </c>
       <c r="F12" s="14" t="n">
-        <v>0.02176582287794901</v>
+        <v>0.02017830790338256</v>
       </c>
       <c r="G12" s="13" t="n">
-        <v>70.00952595969838</v>
+        <v>74.6735322963377</v>
       </c>
       <c r="H12" s="10" t="inlineStr">
         <is>
@@ -14869,32 +14869,32 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>CHOICE</t>
+          <t>Accor</t>
         </is>
       </c>
       <c r="C13" s="12" t="n">
-        <v>231244523</v>
+        <v>246861808</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>81</v>
+        <v>157</v>
       </c>
       <c r="E13" s="13" t="n">
-        <v>4732.12</v>
+        <v>52354.96</v>
       </c>
       <c r="F13" s="14" t="n">
-        <v>0.01089201148344603</v>
+        <v>0.05694859854546638</v>
       </c>
       <c r="G13" s="13" t="n">
-        <v>20.46370629067829</v>
-      </c>
-      <c r="H13" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="I13" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+        <v>212.0820568566848</v>
+      </c>
+      <c r="H13" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="I13" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -14908,19 +14908,19 @@
         </is>
       </c>
       <c r="C14" s="12" t="n">
-        <v>126086283</v>
+        <v>140683269</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E14" s="13" t="n">
-        <v>4036.26</v>
+        <v>4665.290000000001</v>
       </c>
       <c r="F14" s="14" t="n">
-        <v>0.08261690131669597</v>
+        <v>0.08134962374239399</v>
       </c>
       <c r="G14" s="13" t="n">
-        <v>32.01188824005543</v>
+        <v>33.1616547807117</v>
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
@@ -14978,19 +14978,19 @@
         </is>
       </c>
       <c r="C16" s="12" t="n">
-        <v>39087333</v>
+        <v>39809994</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="E16" s="13" t="n">
-        <v>46533.09</v>
+        <v>46405.39</v>
       </c>
       <c r="F16" s="14" t="n">
-        <v>0.03675339015839223</v>
+        <v>0.03705820704218142</v>
       </c>
       <c r="G16" s="13" t="n">
-        <v>1190.490279804969</v>
+        <v>1165.671866215303</v>
       </c>
       <c r="H16" s="9" t="inlineStr">
         <is>
@@ -15114,23 +15114,23 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>MGM Resorts</t>
+          <t>Disney</t>
         </is>
       </c>
       <c r="C20" s="12" t="n">
-        <v>17518133</v>
+        <v>17536052</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>488</v>
+        <v>47</v>
       </c>
       <c r="E20" s="13" t="n">
-        <v>83421.60000000001</v>
+        <v>27333.07</v>
       </c>
       <c r="F20" s="14" t="n">
-        <v>0.02780792907554704</v>
+        <v>0.02459453245234446</v>
       </c>
       <c r="G20" s="13" t="n">
-        <v>4762.014308259905</v>
+        <v>1558.678658115293</v>
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
@@ -15149,23 +15149,23 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Disney</t>
+          <t>MGM Resorts</t>
         </is>
       </c>
       <c r="C21" s="12" t="n">
-        <v>17440445</v>
+        <v>17518133</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>47</v>
+        <v>488</v>
       </c>
       <c r="E21" s="13" t="n">
-        <v>27333.07</v>
+        <v>83421.60000000001</v>
       </c>
       <c r="F21" s="14" t="n">
-        <v>0.02420907264694221</v>
+        <v>0.02780792907554704</v>
       </c>
       <c r="G21" s="13" t="n">
-        <v>1567.223198719987</v>
+        <v>4762.014308259905</v>
       </c>
       <c r="H21" s="10" t="inlineStr">
         <is>
@@ -15188,7 +15188,7 @@
         </is>
       </c>
       <c r="C22" s="12" t="n">
-        <v>16644977</v>
+        <v>16736902</v>
       </c>
       <c r="D22" s="5" t="n">
         <v>20</v>
@@ -15197,7 +15197,7 @@
         <v>-1810.83</v>
       </c>
       <c r="F22" s="14" t="n">
-        <v>0.04657603311797907</v>
+        <v>0.04637859503509072</v>
       </c>
       <c r="G22" s="13" t="n">
         <v>0</v>
@@ -15363,19 +15363,19 @@
         </is>
       </c>
       <c r="C27" s="12" t="n">
-        <v>11952056</v>
+        <v>12041892</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E27" s="13" t="n">
-        <v>21278.16</v>
+        <v>19782.47</v>
       </c>
       <c r="F27" s="14" t="n">
-        <v>0.005869868748941604</v>
+        <v>0.005848914771864754</v>
       </c>
       <c r="G27" s="13" t="n">
-        <v>1780.292863420319</v>
+        <v>1642.804137422923</v>
       </c>
       <c r="H27" s="10" t="inlineStr">
         <is>
@@ -15398,7 +15398,7 @@
         </is>
       </c>
       <c r="C28" s="12" t="n">
-        <v>10895236</v>
+        <v>11161272</v>
       </c>
       <c r="D28" s="5" t="n">
         <v>85</v>
@@ -15407,10 +15407,10 @@
         <v>8137.240000000003</v>
       </c>
       <c r="F28" s="14" t="n">
-        <v>0.02103763516458019</v>
+        <v>0.02141315075916079</v>
       </c>
       <c r="G28" s="13" t="n">
-        <v>746.8622065644107</v>
+        <v>729.060271983337</v>
       </c>
       <c r="H28" s="10" t="inlineStr">
         <is>
@@ -15573,7 +15573,7 @@
         </is>
       </c>
       <c r="C33" s="12" t="n">
-        <v>8944258</v>
+        <v>9028231</v>
       </c>
       <c r="D33" s="5" t="n">
         <v>31</v>
@@ -15582,7 +15582,7 @@
         <v>-14415.05</v>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0.1732095608154416</v>
+        <v>0.1762666462566144</v>
       </c>
       <c r="G33" s="13" t="n">
         <v>0</v>
@@ -15643,7 +15643,7 @@
         </is>
       </c>
       <c r="C35" s="12" t="n">
-        <v>8600824</v>
+        <v>8687481</v>
       </c>
       <c r="D35" s="5" t="n">
         <v>82</v>
@@ -15652,10 +15652,10 @@
         <v>17467.9</v>
       </c>
       <c r="F35" s="14" t="n">
-        <v>0.0216310669768385</v>
+        <v>0.02209915624563668</v>
       </c>
       <c r="G35" s="13" t="n">
-        <v>2030.956568812477</v>
+        <v>2010.697922677472</v>
       </c>
       <c r="H35" s="10" t="inlineStr">
         <is>
@@ -15709,27 +15709,27 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Sandos</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="C37" s="12" t="n">
-        <v>7322039</v>
+        <v>7386891</v>
       </c>
       <c r="D37" s="5" t="n">
-        <v>52</v>
+        <v>1</v>
       </c>
       <c r="E37" s="13" t="n">
-        <v>-2813.73</v>
+        <v>100.39</v>
       </c>
       <c r="F37" s="14" t="n">
-        <v>0.02337709482290384</v>
+        <v>0.1192586976036333</v>
       </c>
       <c r="G37" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+        <v>13.59029123348375</v>
+      </c>
+      <c r="H37" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
       <c r="I37" s="7" t="inlineStr">
@@ -15744,27 +15744,27 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>Sandos</t>
         </is>
       </c>
       <c r="C38" s="12" t="n">
-        <v>7292486</v>
+        <v>7322039</v>
       </c>
       <c r="D38" s="5" t="n">
-        <v>1</v>
+        <v>52</v>
       </c>
       <c r="E38" s="13" t="n">
-        <v>100.39</v>
+        <v>-2813.73</v>
       </c>
       <c r="F38" s="14" t="n">
-        <v>0.1205708176882342</v>
+        <v>0.02337709482290384</v>
       </c>
       <c r="G38" s="13" t="n">
-        <v>13.76622457691383</v>
-      </c>
-      <c r="H38" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+        <v>0</v>
+      </c>
+      <c r="H38" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="I38" s="7" t="inlineStr">
@@ -15884,32 +15884,32 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>Karisma</t>
+          <t>Oyo Rooms</t>
         </is>
       </c>
       <c r="C42" s="12" t="n">
-        <v>4703675</v>
+        <v>4866050</v>
       </c>
       <c r="D42" s="5" t="n">
-        <v>69</v>
+        <v>7</v>
       </c>
       <c r="E42" s="13" t="n">
-        <v>16182.51</v>
+        <v>36.77999999999996</v>
       </c>
       <c r="F42" s="14" t="n">
-        <v>0.007038751614429145</v>
+        <v>0.02846682627593223</v>
       </c>
       <c r="G42" s="13" t="n">
-        <v>3440.397136281737</v>
+        <v>7.558492000698711</v>
       </c>
       <c r="H42" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I42" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I42" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15919,27 +15919,27 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Wynn Las Vegas</t>
+          <t>Karisma</t>
         </is>
       </c>
       <c r="C43" s="12" t="n">
-        <v>4666787</v>
+        <v>4792938</v>
       </c>
       <c r="D43" s="5" t="n">
-        <v>29</v>
+        <v>69</v>
       </c>
       <c r="E43" s="13" t="n">
-        <v>4041.049999999999</v>
+        <v>16182.51</v>
       </c>
       <c r="F43" s="14" t="n">
-        <v>0.05207929995519401</v>
+        <v>0.00713299441803754</v>
       </c>
       <c r="G43" s="13" t="n">
-        <v>865.9169574270262</v>
-      </c>
-      <c r="H43" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+        <v>3376.323666193888</v>
+      </c>
+      <c r="H43" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="I43" s="10" t="inlineStr">
@@ -15954,32 +15954,32 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>Oyo Rooms</t>
+          <t>Wynn Las Vegas</t>
         </is>
       </c>
       <c r="C44" s="12" t="n">
-        <v>4610474</v>
+        <v>4666787</v>
       </c>
       <c r="D44" s="5" t="n">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="E44" s="13" t="n">
-        <v>36.77999999999996</v>
+        <v>4041.049999999999</v>
       </c>
       <c r="F44" s="14" t="n">
-        <v>0.02762644361512504</v>
+        <v>0.05207929995519401</v>
       </c>
       <c r="G44" s="13" t="n">
-        <v>7.977487781082803</v>
-      </c>
-      <c r="H44" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="I44" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+        <v>865.9169574270262</v>
+      </c>
+      <c r="H44" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="I44" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -15989,32 +15989,32 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Villa Group</t>
+          <t>Estelar</t>
         </is>
       </c>
       <c r="C45" s="12" t="n">
-        <v>4599217</v>
+        <v>4662963</v>
       </c>
       <c r="D45" s="5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E45" s="13" t="n">
-        <v>622.96</v>
+        <v>1150.79</v>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0.006832249924280588</v>
+        <v>0.01292075446448964</v>
       </c>
       <c r="G45" s="13" t="n">
-        <v>135.4491427562562</v>
+        <v>246.7937232184772</v>
       </c>
       <c r="H45" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I45" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I45" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -16024,32 +16024,32 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>Americas Hotels Group</t>
+          <t>Villa Group</t>
         </is>
       </c>
       <c r="C46" s="12" t="n">
-        <v>4529430</v>
+        <v>4599217</v>
       </c>
       <c r="D46" s="5" t="n">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="E46" s="13" t="n">
-        <v>6962.73</v>
+        <v>622.96</v>
       </c>
       <c r="F46" s="14" t="n">
-        <v>0.03082772004424398</v>
+        <v>0.006832249924280588</v>
       </c>
       <c r="G46" s="13" t="n">
-        <v>1537.219915088654</v>
-      </c>
-      <c r="H46" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
-        </is>
-      </c>
-      <c r="I46" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+        <v>135.4491427562562</v>
+      </c>
+      <c r="H46" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I46" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16059,32 +16059,32 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Estelar</t>
+          <t>Americas Hotels Group</t>
         </is>
       </c>
       <c r="C47" s="12" t="n">
-        <v>4480967</v>
+        <v>4529430</v>
       </c>
       <c r="D47" s="5" t="n">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="E47" s="13" t="n">
-        <v>981.9300000000001</v>
+        <v>6962.73</v>
       </c>
       <c r="F47" s="14" t="n">
-        <v>0.01280259372586319</v>
+        <v>0.03082772004424398</v>
       </c>
       <c r="G47" s="13" t="n">
-        <v>219.1335039959009</v>
-      </c>
-      <c r="H47" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="I47" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+        <v>1537.219915088654</v>
+      </c>
+      <c r="H47" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I47" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -16094,32 +16094,32 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>Hoteles Xcaret</t>
+          <t>Mision</t>
         </is>
       </c>
       <c r="C48" s="12" t="n">
-        <v>4084322</v>
+        <v>4103271</v>
       </c>
       <c r="D48" s="5" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="E48" s="13" t="n">
-        <v>-21943.09000000001</v>
+        <v>5286.26</v>
       </c>
       <c r="F48" s="14" t="n">
-        <v>0.009237763330119417</v>
+        <v>0.04337222669426417</v>
       </c>
       <c r="G48" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="I48" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+        <v>1288.303892187477</v>
+      </c>
+      <c r="H48" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I48" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -16129,32 +16129,32 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Mision</t>
+          <t>Hoteles Xcaret</t>
         </is>
       </c>
       <c r="C49" s="12" t="n">
-        <v>4011214</v>
+        <v>4084322</v>
       </c>
       <c r="D49" s="5" t="n">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="E49" s="13" t="n">
-        <v>5286.26</v>
+        <v>-21943.09000000001</v>
       </c>
       <c r="F49" s="14" t="n">
-        <v>0.0437800127342994</v>
+        <v>0.009237763330119417</v>
       </c>
       <c r="G49" s="13" t="n">
-        <v>1317.870350472451</v>
-      </c>
-      <c r="H49" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
-        </is>
-      </c>
-      <c r="I49" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+        <v>0</v>
+      </c>
+      <c r="H49" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I49" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16199,23 +16199,23 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>BH Hoteles</t>
+          <t>Hoteles Geh Suites</t>
         </is>
       </c>
       <c r="C51" s="12" t="n">
-        <v>3563952</v>
+        <v>3647578</v>
       </c>
       <c r="D51" s="5" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E51" s="13" t="n">
-        <v>1566.32</v>
+        <v>1250.82</v>
       </c>
       <c r="F51" s="14" t="n">
-        <v>0.02636258849726371</v>
+        <v>0.00577808068806205</v>
       </c>
       <c r="G51" s="13" t="n">
-        <v>439.4896452028534</v>
+        <v>342.9179581629235</v>
       </c>
       <c r="H51" s="10" t="inlineStr">
         <is>
@@ -16234,23 +16234,23 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>Hoteles Geh Suites</t>
+          <t>BH Hoteles</t>
         </is>
       </c>
       <c r="C52" s="12" t="n">
-        <v>3557365</v>
+        <v>3563952</v>
       </c>
       <c r="D52" s="5" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E52" s="13" t="n">
-        <v>1250.82</v>
+        <v>1566.32</v>
       </c>
       <c r="F52" s="14" t="n">
-        <v>0.005343280771020122</v>
+        <v>0.02636258849726371</v>
       </c>
       <c r="G52" s="13" t="n">
-        <v>351.6141863429814</v>
+        <v>439.4896452028534</v>
       </c>
       <c r="H52" s="10" t="inlineStr">
         <is>
@@ -16269,32 +16269,32 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>Faranda Hotels</t>
+          <t>Nacional Inn</t>
         </is>
       </c>
       <c r="C53" s="12" t="n">
-        <v>3274820</v>
+        <v>3463520</v>
       </c>
       <c r="D53" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E53" s="13" t="n">
-        <v>595.02</v>
+        <v>0</v>
       </c>
       <c r="F53" s="14" t="n">
-        <v>0.01267428438814958</v>
+        <v>0.03406072434979443</v>
       </c>
       <c r="G53" s="13" t="n">
-        <v>181.6954824998015</v>
-      </c>
-      <c r="H53" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="I53" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+        <v>0</v>
+      </c>
+      <c r="H53" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I53" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -16304,32 +16304,32 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>Dann</t>
+          <t>Faranda Hotels</t>
         </is>
       </c>
       <c r="C54" s="12" t="n">
-        <v>3210505</v>
+        <v>3274820</v>
       </c>
       <c r="D54" s="5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E54" s="13" t="n">
-        <v>2089.87</v>
+        <v>595.02</v>
       </c>
       <c r="F54" s="14" t="n">
-        <v>0.02065998962779999</v>
+        <v>0.01267428438814958</v>
       </c>
       <c r="G54" s="13" t="n">
-        <v>650.9474366182268</v>
+        <v>181.6954824998015</v>
       </c>
       <c r="H54" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I54" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I54" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16339,32 +16339,32 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>Nacional Inn</t>
+          <t>Dann</t>
         </is>
       </c>
       <c r="C55" s="12" t="n">
-        <v>3207500</v>
+        <v>3210505</v>
       </c>
       <c r="D55" s="5" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E55" s="13" t="n">
-        <v>0</v>
+        <v>2089.87</v>
       </c>
       <c r="F55" s="14" t="n">
-        <v>0.03249633671083398</v>
+        <v>0.02065998962779999</v>
       </c>
       <c r="G55" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H55" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
-        </is>
-      </c>
-      <c r="I55" s="11" t="inlineStr">
-        <is>
-          <t>Sin Conversión</t>
+        <v>650.9474366182268</v>
+      </c>
+      <c r="H55" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I55" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -16448,16 +16448,16 @@
         </is>
       </c>
       <c r="C58" s="12" t="n">
-        <v>2783110</v>
+        <v>2872657</v>
       </c>
       <c r="D58" s="5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E58" s="13" t="n">
         <v>-418.7400000000001</v>
       </c>
       <c r="F58" s="14" t="n">
-        <v>0.003953131568640837</v>
+        <v>0.003890474915731325</v>
       </c>
       <c r="G58" s="13" t="n">
         <v>0</v>
@@ -16518,7 +16518,7 @@
         </is>
       </c>
       <c r="C60" s="12" t="n">
-        <v>2129778</v>
+        <v>2220618</v>
       </c>
       <c r="D60" s="5" t="n">
         <v>2</v>
@@ -16527,10 +16527,10 @@
         <v>65.01000000000001</v>
       </c>
       <c r="F60" s="14" t="n">
-        <v>0.04288522090095776</v>
+        <v>0.0413623594873139</v>
       </c>
       <c r="G60" s="13" t="n">
-        <v>30.52430816733012</v>
+        <v>29.27563408024253</v>
       </c>
       <c r="H60" s="9" t="inlineStr">
         <is>
@@ -16728,7 +16728,7 @@
         </is>
       </c>
       <c r="C66" s="12" t="n">
-        <v>1067257</v>
+        <v>1154368</v>
       </c>
       <c r="D66" s="5" t="n">
         <v>0</v>
@@ -16737,7 +16737,7 @@
         <v>0</v>
       </c>
       <c r="F66" s="14" t="n">
-        <v>0.09783679095100807</v>
+        <v>0.1001561027332705</v>
       </c>
       <c r="G66" s="13" t="n">
         <v>0</v>
@@ -16794,11 +16794,11 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>Costa del Sol</t>
+          <t>Sonesta</t>
         </is>
       </c>
       <c r="C68" s="12" t="n">
-        <v>847100</v>
+        <v>900253</v>
       </c>
       <c r="D68" s="5" t="n">
         <v>0</v>
@@ -16807,14 +16807,14 @@
         <v>0</v>
       </c>
       <c r="F68" s="14" t="n">
-        <v>0.02238578680203046</v>
+        <v>0.05933887473854574</v>
       </c>
       <c r="G68" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H68" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="H68" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
       <c r="I68" s="11" t="inlineStr">
@@ -16829,11 +16829,11 @@
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>Sonesta</t>
+          <t>Costa del Sol</t>
         </is>
       </c>
       <c r="C69" s="12" t="n">
-        <v>810547</v>
+        <v>847100</v>
       </c>
       <c r="D69" s="5" t="n">
         <v>0</v>
@@ -16842,14 +16842,14 @@
         <v>0</v>
       </c>
       <c r="F69" s="14" t="n">
-        <v>0.05640265154272363</v>
+        <v>0.02238578680203046</v>
       </c>
       <c r="G69" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H69" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="H69" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="I69" s="11" t="inlineStr">
@@ -17039,32 +17039,32 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>Blue Doors</t>
+          <t>Red Roof</t>
         </is>
       </c>
       <c r="C75" s="12" t="n">
-        <v>443253</v>
+        <v>504391</v>
       </c>
       <c r="D75" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E75" s="13" t="n">
-        <v>620.96</v>
+        <v>0</v>
       </c>
       <c r="F75" s="14" t="n">
-        <v>0.01391530344972284</v>
+        <v>0.005733647111070578</v>
       </c>
       <c r="G75" s="13" t="n">
-        <v>1400.915504237986</v>
+        <v>0</v>
       </c>
       <c r="H75" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I75" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I75" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -17074,32 +17074,32 @@
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>Hoteles Cosmos</t>
+          <t>Blue Doors</t>
         </is>
       </c>
       <c r="C76" s="12" t="n">
-        <v>439489</v>
+        <v>443253</v>
       </c>
       <c r="D76" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E76" s="13" t="n">
-        <v>0</v>
+        <v>620.96</v>
       </c>
       <c r="F76" s="14" t="n">
-        <v>0.02133386728678078</v>
+        <v>0.01391530344972284</v>
       </c>
       <c r="G76" s="13" t="n">
-        <v>0</v>
+        <v>1400.915504237986</v>
       </c>
       <c r="H76" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I76" s="11" t="inlineStr">
-        <is>
-          <t>Sin Conversión</t>
+      <c r="I76" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -17109,32 +17109,32 @@
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>Grupo Welcome</t>
+          <t>Hoteles Cosmos</t>
         </is>
       </c>
       <c r="C77" s="12" t="n">
-        <v>379013</v>
+        <v>439489</v>
       </c>
       <c r="D77" s="5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E77" s="13" t="n">
-        <v>1849.4</v>
+        <v>0</v>
       </c>
       <c r="F77" s="14" t="n">
-        <v>0.03371124473303026</v>
+        <v>0.02133386728678078</v>
       </c>
       <c r="G77" s="13" t="n">
-        <v>4879.516006047286</v>
-      </c>
-      <c r="H77" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
-        </is>
-      </c>
-      <c r="I77" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+        <v>0</v>
+      </c>
+      <c r="H77" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I77" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -17144,32 +17144,32 @@
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>DOT Hotels</t>
+          <t>Grupo Welcome</t>
         </is>
       </c>
       <c r="C78" s="12" t="n">
-        <v>370621</v>
+        <v>379013</v>
       </c>
       <c r="D78" s="5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E78" s="13" t="n">
-        <v>0</v>
+        <v>1849.4</v>
       </c>
       <c r="F78" s="14" t="n">
-        <v>0.02111051451482782</v>
+        <v>0.03371124473303026</v>
       </c>
       <c r="G78" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H78" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="I78" s="11" t="inlineStr">
-        <is>
-          <t>Sin Conversión</t>
+        <v>4879.516006047286</v>
+      </c>
+      <c r="H78" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I78" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -17179,11 +17179,11 @@
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>Red Roof</t>
+          <t>DOT Hotels</t>
         </is>
       </c>
       <c r="C79" s="12" t="n">
-        <v>327987</v>
+        <v>370621</v>
       </c>
       <c r="D79" s="5" t="n">
         <v>0</v>
@@ -17192,7 +17192,7 @@
         <v>0</v>
       </c>
       <c r="F79" s="14" t="n">
-        <v>0.007424074734669362</v>
+        <v>0.02111051451482782</v>
       </c>
       <c r="G79" s="13" t="n">
         <v>0</v>
@@ -17670,7 +17670,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 04:09 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 05:04 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -17731,19 +17731,19 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>184546942</v>
+        <v>185620394</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="E6" s="13" t="n">
-        <v>171275.98</v>
+        <v>171654.98</v>
       </c>
       <c r="F6" s="14" t="n">
-        <v>0.02842346203710057</v>
+        <v>0.02863141751546977</v>
       </c>
       <c r="G6" s="13" t="n">
-        <v>928.0889628612756</v>
+        <v>924.763579588135</v>
       </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
@@ -17766,19 +17766,19 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>178193828</v>
+        <v>179681898</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="E7" s="13" t="n">
-        <v>99242.77</v>
+        <v>97747.08</v>
       </c>
       <c r="F7" s="14" t="n">
-        <v>0.02700473441762528</v>
+        <v>0.02702213775591351</v>
       </c>
       <c r="G7" s="13" t="n">
-        <v>556.9371908885644</v>
+        <v>544.000709520555</v>
       </c>
       <c r="H7" s="10" t="inlineStr">
         <is>
@@ -17801,7 +17801,7 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>138580223</v>
+        <v>138850597</v>
       </c>
       <c r="D8" s="5" t="n">
         <v>642</v>
@@ -17810,10 +17810,10 @@
         <v>241664.21</v>
       </c>
       <c r="F8" s="14" t="n">
-        <v>0.03112739975891076</v>
+        <v>0.03114722654019269</v>
       </c>
       <c r="G8" s="13" t="n">
-        <v>1743.857851924513</v>
+        <v>1740.462160202307</v>
       </c>
       <c r="H8" s="9" t="inlineStr">
         <is>
@@ -17836,7 +17836,7 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>116702724</v>
+        <v>117617497</v>
       </c>
       <c r="D9" s="5" t="n">
         <v>731</v>
@@ -17845,10 +17845,10 @@
         <v>105696.26</v>
       </c>
       <c r="F9" s="14" t="n">
-        <v>0.03348001542791752</v>
+        <v>0.03345257381221095</v>
       </c>
       <c r="G9" s="13" t="n">
-        <v>905.6880283274278</v>
+        <v>898.6440172247502</v>
       </c>
       <c r="H9" s="9" t="inlineStr">
         <is>
@@ -17871,19 +17871,19 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>102073284</v>
+        <v>104558569</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="E10" s="13" t="n">
-        <v>156563.48</v>
+        <v>158323.81</v>
       </c>
       <c r="F10" s="14" t="n">
-        <v>0.02178647450982375</v>
+        <v>0.0216445387656367</v>
       </c>
       <c r="G10" s="13" t="n">
-        <v>1533.834063769321</v>
+        <v>1514.211714202018</v>
       </c>
       <c r="H10" s="10" t="inlineStr">
         <is>
@@ -17906,19 +17906,19 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>100196686</v>
+        <v>101193981</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="E11" s="13" t="n">
-        <v>35910.15</v>
+        <v>36547.78</v>
       </c>
       <c r="F11" s="14" t="n">
-        <v>0.02776502009258071</v>
+        <v>0.02809072211518193</v>
       </c>
       <c r="G11" s="13" t="n">
-        <v>358.3965840946076</v>
+        <v>361.165551931394</v>
       </c>
       <c r="H11" s="10" t="inlineStr">
         <is>
@@ -17941,7 +17941,7 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>97534529</v>
+        <v>98328588</v>
       </c>
       <c r="D12" s="5" t="n">
         <v>1085</v>
@@ -17950,10 +17950,10 @@
         <v>161244.63</v>
       </c>
       <c r="F12" s="14" t="n">
-        <v>0.02873823279548518</v>
+        <v>0.02867800766141379</v>
       </c>
       <c r="G12" s="13" t="n">
-        <v>1653.205604755625</v>
+        <v>1639.855033817835</v>
       </c>
       <c r="H12" s="10" t="inlineStr">
         <is>
@@ -17976,7 +17976,7 @@
         </is>
       </c>
       <c r="C13" s="12" t="n">
-        <v>89054518</v>
+        <v>90619910</v>
       </c>
       <c r="D13" s="5" t="n">
         <v>166</v>
@@ -17985,10 +17985,10 @@
         <v>41719.73</v>
       </c>
       <c r="F13" s="14" t="n">
-        <v>0.0127236778711216</v>
+        <v>0.01268781882480351</v>
       </c>
       <c r="G13" s="13" t="n">
-        <v>468.4740419346271</v>
+        <v>460.3814989443269</v>
       </c>
       <c r="H13" s="10" t="inlineStr">
         <is>
@@ -18011,19 +18011,19 @@
         </is>
       </c>
       <c r="C14" s="12" t="n">
-        <v>80963313</v>
+        <v>85236978</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="E14" s="13" t="n">
-        <v>75966.7</v>
+        <v>76185.89999999999</v>
       </c>
       <c r="F14" s="14" t="n">
-        <v>0.01067135185043626</v>
+        <v>0.01054148118672157</v>
       </c>
       <c r="G14" s="13" t="n">
-        <v>938.2854676413748</v>
+        <v>893.8127768912689</v>
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
@@ -18046,7 +18046,7 @@
         </is>
       </c>
       <c r="C15" s="12" t="n">
-        <v>79748692</v>
+        <v>81685375</v>
       </c>
       <c r="D15" s="5" t="n">
         <v>39</v>
@@ -18055,7 +18055,7 @@
         <v>-8330.43</v>
       </c>
       <c r="F15" s="14" t="n">
-        <v>0.07643979916310101</v>
+        <v>0.07598089621306139</v>
       </c>
       <c r="G15" s="13" t="n">
         <v>0</v>
@@ -18081,19 +18081,19 @@
         </is>
       </c>
       <c r="C16" s="12" t="n">
-        <v>78926039</v>
+        <v>79733335</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E16" s="13" t="n">
-        <v>77558.23</v>
+        <v>77865.74000000001</v>
       </c>
       <c r="F16" s="14" t="n">
-        <v>0.03832025575235063</v>
+        <v>0.03813121575812676</v>
       </c>
       <c r="G16" s="13" t="n">
-        <v>982.6697371700104</v>
+        <v>976.5769862755648</v>
       </c>
       <c r="H16" s="9" t="inlineStr">
         <is>
@@ -18116,7 +18116,7 @@
         </is>
       </c>
       <c r="C17" s="12" t="n">
-        <v>75977850</v>
+        <v>76165259</v>
       </c>
       <c r="D17" s="5" t="n">
         <v>249</v>
@@ -18125,10 +18125,10 @@
         <v>68927.64</v>
       </c>
       <c r="F17" s="14" t="n">
-        <v>0.04867075075169935</v>
+        <v>0.04862068413631995</v>
       </c>
       <c r="G17" s="13" t="n">
-        <v>907.2070346818184</v>
+        <v>904.9747995999068</v>
       </c>
       <c r="H17" s="9" t="inlineStr">
         <is>
@@ -18147,23 +18147,23 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Puerto Vallarta Area</t>
+          <t>Houston (and vicinity), TX, US</t>
         </is>
       </c>
       <c r="C18" s="12" t="n">
-        <v>51580959</v>
+        <v>54816471</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>299</v>
+        <v>221</v>
       </c>
       <c r="E18" s="13" t="n">
-        <v>51389.18</v>
+        <v>37991.56</v>
       </c>
       <c r="F18" s="14" t="n">
-        <v>0.02451315416605573</v>
+        <v>0.006534878905283779</v>
       </c>
       <c r="G18" s="13" t="n">
-        <v>996.2819807208315</v>
+        <v>693.0683297726334</v>
       </c>
       <c r="H18" s="10" t="inlineStr">
         <is>
@@ -18182,32 +18182,32 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Houston (and vicinity), TX, US</t>
+          <t>Atlanta Area</t>
         </is>
       </c>
       <c r="C19" s="12" t="n">
-        <v>51489747</v>
+        <v>54809589</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>213</v>
+        <v>249</v>
       </c>
       <c r="E19" s="13" t="n">
-        <v>32697.09</v>
+        <v>41621.96</v>
       </c>
       <c r="F19" s="14" t="n">
-        <v>0.0064132768024671</v>
+        <v>0.01112588164089317</v>
       </c>
       <c r="G19" s="13" t="n">
-        <v>635.0213761974787</v>
+        <v>759.3919377866525</v>
       </c>
       <c r="H19" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I19" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I19" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -18217,23 +18217,23 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Atlanta Area</t>
+          <t>Puerto Vallarta Area</t>
         </is>
       </c>
       <c r="C20" s="12" t="n">
-        <v>51325120</v>
+        <v>51668076</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>247</v>
+        <v>299</v>
       </c>
       <c r="E20" s="13" t="n">
-        <v>41368.31</v>
+        <v>51389.18</v>
       </c>
       <c r="F20" s="14" t="n">
-        <v>0.01141815157957741</v>
+        <v>0.02448546758350359</v>
       </c>
       <c r="G20" s="13" t="n">
-        <v>806.0051296519131</v>
+        <v>994.6021601423673</v>
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
@@ -18256,7 +18256,7 @@
         </is>
       </c>
       <c r="C21" s="12" t="n">
-        <v>49685181</v>
+        <v>50326845</v>
       </c>
       <c r="D21" s="5" t="n">
         <v>184</v>
@@ -18265,10 +18265,10 @@
         <v>34941.71</v>
       </c>
       <c r="F21" s="14" t="n">
-        <v>0.04692533977082623</v>
+        <v>0.04731667562311923</v>
       </c>
       <c r="G21" s="13" t="n">
-        <v>703.2622060891757</v>
+        <v>694.2956587085878</v>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
@@ -18287,32 +18287,32 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="C22" s="12" t="n">
-        <v>46927804</v>
+        <v>47938709</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>105</v>
+        <v>258</v>
       </c>
       <c r="E22" s="13" t="n">
-        <v>17170</v>
+        <v>82462.35000000001</v>
       </c>
       <c r="F22" s="14" t="n">
-        <v>0.009398266324160406</v>
+        <v>0.01195826946445304</v>
       </c>
       <c r="G22" s="13" t="n">
-        <v>365.8811735575779</v>
+        <v>1720.162092808966</v>
       </c>
       <c r="H22" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I22" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="I22" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -18322,32 +18322,32 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="C23" s="12" t="n">
-        <v>46788131</v>
+        <v>47274989</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>258</v>
+        <v>108</v>
       </c>
       <c r="E23" s="13" t="n">
-        <v>82462.35000000001</v>
+        <v>17993.9</v>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0.01123898280955057</v>
+        <v>0.009613455436235003</v>
       </c>
       <c r="G23" s="13" t="n">
-        <v>1762.46300584223</v>
+        <v>380.6219817417621</v>
       </c>
       <c r="H23" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I23" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I23" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -18361,19 +18361,19 @@
         </is>
       </c>
       <c r="C24" s="12" t="n">
-        <v>42339189</v>
+        <v>43425982</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E24" s="13" t="n">
-        <v>38517.56</v>
+        <v>38841.36</v>
       </c>
       <c r="F24" s="14" t="n">
-        <v>0.009062384260596017</v>
+        <v>0.008924818326503244</v>
       </c>
       <c r="G24" s="13" t="n">
-        <v>909.7377845381025</v>
+        <v>894.4267512476748</v>
       </c>
       <c r="H24" s="10" t="inlineStr">
         <is>
@@ -18392,23 +18392,23 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Seattle Area</t>
+          <t>Denver (and vicinity), CO, US</t>
         </is>
       </c>
       <c r="C25" s="12" t="n">
-        <v>41309438</v>
+        <v>42192616</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>391</v>
+        <v>196</v>
       </c>
       <c r="E25" s="13" t="n">
-        <v>74749.53999999999</v>
+        <v>50011.37</v>
       </c>
       <c r="F25" s="14" t="n">
-        <v>0.009221597253392796</v>
+        <v>0.008467642774271214</v>
       </c>
       <c r="G25" s="13" t="n">
-        <v>1809.502709768165</v>
+        <v>1185.310955831703</v>
       </c>
       <c r="H25" s="10" t="inlineStr">
         <is>
@@ -18427,23 +18427,23 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Denver (and vicinity), CO, US</t>
+          <t>Seattle Area</t>
         </is>
       </c>
       <c r="C26" s="12" t="n">
-        <v>40661297</v>
+        <v>42019636</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>195</v>
+        <v>391</v>
       </c>
       <c r="E26" s="13" t="n">
-        <v>49934.05</v>
+        <v>74749.53999999999</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>0.008089928857901409</v>
+        <v>0.009444608230304517</v>
       </c>
       <c r="G26" s="13" t="n">
-        <v>1228.048628158615</v>
+        <v>1778.919265269218</v>
       </c>
       <c r="H26" s="10" t="inlineStr">
         <is>
@@ -18466,19 +18466,19 @@
         </is>
       </c>
       <c r="C27" s="12" t="n">
-        <v>40420133</v>
+        <v>41927297</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E27" s="13" t="n">
         <v>78270.25999999999</v>
       </c>
       <c r="F27" s="14" t="n">
-        <v>0.009898581976462076</v>
+        <v>0.009979250510711435</v>
       </c>
       <c r="G27" s="13" t="n">
-        <v>1936.417675815169</v>
+        <v>1866.809110064977</v>
       </c>
       <c r="H27" s="10" t="inlineStr">
         <is>
@@ -18501,19 +18501,19 @@
         </is>
       </c>
       <c r="C28" s="12" t="n">
-        <v>37821870</v>
+        <v>38552028</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="E28" s="13" t="n">
-        <v>44944.60000000001</v>
+        <v>44936</v>
       </c>
       <c r="F28" s="14" t="n">
-        <v>0.0265834291112523</v>
+        <v>0.02713079062922449</v>
       </c>
       <c r="G28" s="13" t="n">
-        <v>1188.323052244641</v>
+        <v>1165.593675123913</v>
       </c>
       <c r="H28" s="10" t="inlineStr">
         <is>
@@ -18536,19 +18536,19 @@
         </is>
       </c>
       <c r="C29" s="12" t="n">
-        <v>36612517</v>
+        <v>36884373</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E29" s="13" t="n">
-        <v>29050.22</v>
+        <v>29299.68</v>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0.01308740942339474</v>
+        <v>0.01318013457894486</v>
       </c>
       <c r="G29" s="13" t="n">
-        <v>793.4505021875443</v>
+        <v>794.3656789285805</v>
       </c>
       <c r="H29" s="10" t="inlineStr">
         <is>
@@ -18571,7 +18571,7 @@
         </is>
       </c>
       <c r="C30" s="12" t="n">
-        <v>35410219</v>
+        <v>35673470</v>
       </c>
       <c r="D30" s="5" t="n">
         <v>138</v>
@@ -18580,10 +18580,10 @@
         <v>14577.18</v>
       </c>
       <c r="F30" s="14" t="n">
-        <v>0.01257586122243412</v>
+        <v>0.01266215481701107</v>
       </c>
       <c r="G30" s="13" t="n">
-        <v>411.6659092111235</v>
+        <v>408.6280364651939</v>
       </c>
       <c r="H30" s="10" t="inlineStr">
         <is>
@@ -18606,7 +18606,7 @@
         </is>
       </c>
       <c r="C31" s="12" t="n">
-        <v>35196919</v>
+        <v>35458951</v>
       </c>
       <c r="D31" s="5" t="n">
         <v>99</v>
@@ -18615,10 +18615,10 @@
         <v>47123.16</v>
       </c>
       <c r="F31" s="14" t="n">
-        <v>0.0244965191413487</v>
+        <v>0.02451443078505058</v>
       </c>
       <c r="G31" s="13" t="n">
-        <v>1338.843323189737</v>
+        <v>1328.949635312111</v>
       </c>
       <c r="H31" s="10" t="inlineStr">
         <is>
@@ -18637,32 +18637,32 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>Anaheim Area</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="C32" s="12" t="n">
-        <v>34141348</v>
+        <v>35283426</v>
       </c>
       <c r="D32" s="5" t="n">
-        <v>58</v>
+        <v>110</v>
       </c>
       <c r="E32" s="13" t="n">
-        <v>11518.65</v>
+        <v>32129.5</v>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0.01764048683725083</v>
+        <v>0.006785650577129329</v>
       </c>
       <c r="G32" s="13" t="n">
-        <v>337.3812305243483</v>
+        <v>910.6116849310495</v>
       </c>
       <c r="H32" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I32" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="I32" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -18672,32 +18672,32 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Anaheim Area</t>
         </is>
       </c>
       <c r="C33" s="12" t="n">
-        <v>34132037</v>
+        <v>34317102</v>
       </c>
       <c r="D33" s="5" t="n">
-        <v>110</v>
+        <v>58</v>
       </c>
       <c r="E33" s="13" t="n">
-        <v>32129.5</v>
+        <v>11518.65</v>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0.006879636278373892</v>
+        <v>0.01756561495198516</v>
       </c>
       <c r="G33" s="13" t="n">
-        <v>941.3296956170533</v>
+        <v>335.6533427560404</v>
       </c>
       <c r="H33" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I33" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I33" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -18711,7 +18711,7 @@
         </is>
       </c>
       <c r="C34" s="12" t="n">
-        <v>31016098</v>
+        <v>31383688</v>
       </c>
       <c r="D34" s="5" t="n">
         <v>161</v>
@@ -18720,10 +18720,10 @@
         <v>28656.68</v>
       </c>
       <c r="F34" s="14" t="n">
-        <v>0.01237051159691332</v>
+        <v>0.01249547217012864</v>
       </c>
       <c r="G34" s="13" t="n">
-        <v>923.9292447425205</v>
+        <v>913.1074716266615</v>
       </c>
       <c r="H34" s="10" t="inlineStr">
         <is>
@@ -18746,7 +18746,7 @@
         </is>
       </c>
       <c r="C35" s="12" t="n">
-        <v>30698560</v>
+        <v>31048677</v>
       </c>
       <c r="D35" s="5" t="n">
         <v>65</v>
@@ -18755,10 +18755,10 @@
         <v>30432.47</v>
       </c>
       <c r="F35" s="14" t="n">
-        <v>0.0454830454588098</v>
+        <v>0.04513461233791057</v>
       </c>
       <c r="G35" s="13" t="n">
-        <v>991.3321667205238</v>
+        <v>980.1535182964479</v>
       </c>
       <c r="H35" s="9" t="inlineStr">
         <is>
@@ -18781,19 +18781,19 @@
         </is>
       </c>
       <c r="C36" s="12" t="n">
-        <v>28311757</v>
+        <v>30368930</v>
       </c>
       <c r="D36" s="5" t="n">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E36" s="13" t="n">
-        <v>57486.31</v>
+        <v>57668.73</v>
       </c>
       <c r="F36" s="14" t="n">
-        <v>0.008964226416608479</v>
+        <v>0.009277738794221594</v>
       </c>
       <c r="G36" s="13" t="n">
-        <v>2030.474830650744</v>
+        <v>1898.938487460704</v>
       </c>
       <c r="H36" s="10" t="inlineStr">
         <is>
@@ -18816,19 +18816,19 @@
         </is>
       </c>
       <c r="C37" s="12" t="n">
-        <v>28249127</v>
+        <v>28960684</v>
       </c>
       <c r="D37" s="5" t="n">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="E37" s="13" t="n">
-        <v>12156.88</v>
+        <v>11968.02</v>
       </c>
       <c r="F37" s="14" t="n">
-        <v>0.01105910281758442</v>
+        <v>0.01108520088821107</v>
       </c>
       <c r="G37" s="13" t="n">
-        <v>430.345334211567</v>
+        <v>413.2505986391758</v>
       </c>
       <c r="H37" s="10" t="inlineStr">
         <is>
@@ -18847,23 +18847,23 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>Philadelphia (and vicinity), PA, US</t>
+          <t>New Orleans</t>
         </is>
       </c>
       <c r="C38" s="12" t="n">
-        <v>27825181</v>
+        <v>28616268</v>
       </c>
       <c r="D38" s="5" t="n">
-        <v>119</v>
+        <v>154</v>
       </c>
       <c r="E38" s="13" t="n">
-        <v>20326.58</v>
+        <v>20065.41</v>
       </c>
       <c r="F38" s="14" t="n">
-        <v>0.01239068310103715</v>
+        <v>0.01799336657037179</v>
       </c>
       <c r="G38" s="13" t="n">
-        <v>730.5102525658325</v>
+        <v>701.1889181356563</v>
       </c>
       <c r="H38" s="10" t="inlineStr">
         <is>
@@ -18882,23 +18882,23 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>New Orleans</t>
+          <t>Greenville Area</t>
         </is>
       </c>
       <c r="C39" s="12" t="n">
-        <v>27650745</v>
+        <v>28222316</v>
       </c>
       <c r="D39" s="5" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E39" s="13" t="n">
-        <v>20065.41</v>
+        <v>36605.81</v>
       </c>
       <c r="F39" s="14" t="n">
-        <v>0.01823911073643766</v>
+        <v>0.01704590792619571</v>
       </c>
       <c r="G39" s="13" t="n">
-        <v>725.6733950568059</v>
+        <v>1297.051949953363</v>
       </c>
       <c r="H39" s="10" t="inlineStr">
         <is>
@@ -18917,23 +18917,23 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>Greenville Area</t>
+          <t>Philadelphia (and vicinity), PA, US</t>
         </is>
       </c>
       <c r="C40" s="12" t="n">
-        <v>27411629</v>
+        <v>28004860</v>
       </c>
       <c r="D40" s="5" t="n">
-        <v>155</v>
+        <v>119</v>
       </c>
       <c r="E40" s="13" t="n">
-        <v>36605.81</v>
+        <v>20326.58</v>
       </c>
       <c r="F40" s="14" t="n">
-        <v>0.01704980758348948</v>
+        <v>0.01235207031922316</v>
       </c>
       <c r="G40" s="13" t="n">
-        <v>1335.411696984517</v>
+        <v>725.8233035266022</v>
       </c>
       <c r="H40" s="10" t="inlineStr">
         <is>
@@ -18956,19 +18956,19 @@
         </is>
       </c>
       <c r="C41" s="12" t="n">
-        <v>27159938</v>
+        <v>27868149</v>
       </c>
       <c r="D41" s="5" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E41" s="13" t="n">
-        <v>20555.89</v>
+        <v>20738.7</v>
       </c>
       <c r="F41" s="14" t="n">
-        <v>0.003352548153828628</v>
+        <v>0.003360646593356451</v>
       </c>
       <c r="G41" s="13" t="n">
-        <v>756.8459839635863</v>
+        <v>744.1721371591632</v>
       </c>
       <c r="H41" s="10" t="inlineStr">
         <is>
@@ -18987,32 +18987,32 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>Riviera Nayarit</t>
+          <t>Istanbul Area</t>
         </is>
       </c>
       <c r="C42" s="12" t="n">
-        <v>24578354</v>
+        <v>25043194</v>
       </c>
       <c r="D42" s="5" t="n">
-        <v>816</v>
+        <v>32</v>
       </c>
       <c r="E42" s="13" t="n">
-        <v>336653.25</v>
+        <v>12517.67</v>
       </c>
       <c r="F42" s="14" t="n">
-        <v>0.02507474666529744</v>
+        <v>0.11750106635759</v>
       </c>
       <c r="G42" s="13" t="n">
-        <v>13697.14383640174</v>
-      </c>
-      <c r="H42" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="I42" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+        <v>499.8431909284415</v>
+      </c>
+      <c r="H42" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="I42" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -19022,32 +19022,32 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Istanbul Area</t>
+          <t>Riviera Nayarit</t>
         </is>
       </c>
       <c r="C43" s="12" t="n">
-        <v>24326442</v>
+        <v>24763025</v>
       </c>
       <c r="D43" s="5" t="n">
-        <v>32</v>
+        <v>816</v>
       </c>
       <c r="E43" s="13" t="n">
-        <v>12517.67</v>
+        <v>336653.25</v>
       </c>
       <c r="F43" s="14" t="n">
-        <v>0.117456305365166</v>
+        <v>0.02489401032385987</v>
       </c>
       <c r="G43" s="13" t="n">
-        <v>514.5705237124278</v>
-      </c>
-      <c r="H43" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
-        </is>
-      </c>
-      <c r="I43" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+        <v>13594.99697633871</v>
+      </c>
+      <c r="H43" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I43" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -19061,7 +19061,7 @@
         </is>
       </c>
       <c r="C44" s="12" t="n">
-        <v>23263370</v>
+        <v>23780921</v>
       </c>
       <c r="D44" s="5" t="n">
         <v>73</v>
@@ -19070,10 +19070,10 @@
         <v>10442.13</v>
       </c>
       <c r="F44" s="14" t="n">
-        <v>0.115874097347031</v>
+        <v>0.1158967308288859</v>
       </c>
       <c r="G44" s="13" t="n">
-        <v>448.8657490294829</v>
+        <v>439.0969550758779</v>
       </c>
       <c r="H44" s="8" t="inlineStr">
         <is>
@@ -19092,23 +19092,23 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Tampa Area</t>
+          <t>Detroit Area</t>
         </is>
       </c>
       <c r="C45" s="12" t="n">
-        <v>21450518</v>
+        <v>23161295</v>
       </c>
       <c r="D45" s="5" t="n">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="E45" s="13" t="n">
-        <v>20600.06</v>
+        <v>17251.9</v>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0.009399773003150787</v>
+        <v>0.005656894400766451</v>
       </c>
       <c r="G45" s="13" t="n">
-        <v>960.3525658447969</v>
+        <v>744.8590417763775</v>
       </c>
       <c r="H45" s="10" t="inlineStr">
         <is>
@@ -19127,23 +19127,23 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>Detroit Area</t>
+          <t>Tampa Area</t>
         </is>
       </c>
       <c r="C46" s="12" t="n">
-        <v>21127845</v>
+        <v>22167168</v>
       </c>
       <c r="D46" s="5" t="n">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="E46" s="13" t="n">
-        <v>17251.9</v>
+        <v>20873.09</v>
       </c>
       <c r="F46" s="14" t="n">
-        <v>0.005455312645468575</v>
+        <v>0.009291579330296049</v>
       </c>
       <c r="G46" s="13" t="n">
-        <v>816.5480199234707</v>
+        <v>941.6218616649633</v>
       </c>
       <c r="H46" s="10" t="inlineStr">
         <is>
@@ -19166,7 +19166,7 @@
         </is>
       </c>
       <c r="C47" s="12" t="n">
-        <v>19602135</v>
+        <v>20127543</v>
       </c>
       <c r="D47" s="5" t="n">
         <v>129</v>
@@ -19175,10 +19175,10 @@
         <v>19449.26</v>
       </c>
       <c r="F47" s="14" t="n">
-        <v>0.05037956324655452</v>
+        <v>0.05167963123964013</v>
       </c>
       <c r="G47" s="13" t="n">
-        <v>992.201104624573</v>
+        <v>966.3007551393632</v>
       </c>
       <c r="H47" s="8" t="inlineStr">
         <is>
@@ -19197,27 +19197,27 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>Monterrey</t>
+          <t>Indianápolis Area</t>
         </is>
       </c>
       <c r="C48" s="12" t="n">
-        <v>18808120</v>
+        <v>19254221</v>
       </c>
       <c r="D48" s="5" t="n">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="E48" s="13" t="n">
-        <v>23279</v>
+        <v>26258.98</v>
       </c>
       <c r="F48" s="14" t="n">
-        <v>0.03322373528029383</v>
+        <v>0.0139025619369384</v>
       </c>
       <c r="G48" s="13" t="n">
-        <v>1237.710095426869</v>
-      </c>
-      <c r="H48" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+        <v>1363.8038121615</v>
+      </c>
+      <c r="H48" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="I48" s="10" t="inlineStr">
@@ -19232,27 +19232,27 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Montreal</t>
+          <t>Columbus (and vicinity), OH, US</t>
         </is>
       </c>
       <c r="C49" s="12" t="n">
-        <v>18098183</v>
+        <v>19221573</v>
       </c>
       <c r="D49" s="5" t="n">
-        <v>60</v>
+        <v>109</v>
       </c>
       <c r="E49" s="13" t="n">
-        <v>17289.68</v>
+        <v>27787.45</v>
       </c>
       <c r="F49" s="14" t="n">
-        <v>0.04949745507601509</v>
+        <v>0.00687040545537038</v>
       </c>
       <c r="G49" s="13" t="n">
-        <v>955.326841374076</v>
-      </c>
-      <c r="H49" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+        <v>1445.638710213779</v>
+      </c>
+      <c r="H49" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="I49" s="10" t="inlineStr">
@@ -19267,27 +19267,27 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>Raleigh Area</t>
+          <t>Monterrey</t>
         </is>
       </c>
       <c r="C50" s="12" t="n">
-        <v>17635016</v>
+        <v>19083601</v>
       </c>
       <c r="D50" s="5" t="n">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="E50" s="13" t="n">
-        <v>20689.66</v>
+        <v>23279</v>
       </c>
       <c r="F50" s="14" t="n">
-        <v>0.00226322448474104</v>
+        <v>0.03356913613945293</v>
       </c>
       <c r="G50" s="13" t="n">
-        <v>1173.214699663442</v>
-      </c>
-      <c r="H50" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+        <v>1219.843152243646</v>
+      </c>
+      <c r="H50" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="I50" s="10" t="inlineStr">
@@ -19302,32 +19302,32 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>Indianápolis Area</t>
+          <t>Dubai Area</t>
         </is>
       </c>
       <c r="C51" s="12" t="n">
-        <v>17446115</v>
+        <v>18860917</v>
       </c>
       <c r="D51" s="5" t="n">
-        <v>98</v>
+        <v>14</v>
       </c>
       <c r="E51" s="13" t="n">
-        <v>24742.89</v>
+        <v>1694.34</v>
       </c>
       <c r="F51" s="14" t="n">
-        <v>0.0144463108262212</v>
+        <v>0.08864712145226025</v>
       </c>
       <c r="G51" s="13" t="n">
-        <v>1418.246411880238</v>
-      </c>
-      <c r="H51" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="I51" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+        <v>89.83338402899498</v>
+      </c>
+      <c r="H51" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="I51" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -19337,32 +19337,32 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>Dubai Area</t>
+          <t>Raleigh Area</t>
         </is>
       </c>
       <c r="C52" s="12" t="n">
-        <v>17443025</v>
+        <v>18514777</v>
       </c>
       <c r="D52" s="5" t="n">
-        <v>13</v>
+        <v>81</v>
       </c>
       <c r="E52" s="13" t="n">
-        <v>1945.64</v>
+        <v>20689.66</v>
       </c>
       <c r="F52" s="14" t="n">
-        <v>0.08801844863491282</v>
+        <v>0.002241776933095116</v>
       </c>
       <c r="G52" s="13" t="n">
-        <v>111.5425793404527</v>
-      </c>
-      <c r="H52" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
-        </is>
-      </c>
-      <c r="I52" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+        <v>1117.467415351533</v>
+      </c>
+      <c r="H52" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I52" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -19372,27 +19372,27 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>Columbus (and vicinity), OH, US</t>
+          <t>Montreal</t>
         </is>
       </c>
       <c r="C53" s="12" t="n">
-        <v>17273522</v>
+        <v>18448353</v>
       </c>
       <c r="D53" s="5" t="n">
-        <v>108</v>
+        <v>60</v>
       </c>
       <c r="E53" s="13" t="n">
-        <v>27545.87</v>
+        <v>17289.68</v>
       </c>
       <c r="F53" s="14" t="n">
-        <v>0.006843827217170881</v>
+        <v>0.05209581581618696</v>
       </c>
       <c r="G53" s="13" t="n">
-        <v>1594.687522324631</v>
-      </c>
-      <c r="H53" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+        <v>937.1936887807817</v>
+      </c>
+      <c r="H53" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
       <c r="I53" s="10" t="inlineStr">
@@ -19407,23 +19407,23 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>Honolulu Area</t>
+          <t>Charlotte Area</t>
         </is>
       </c>
       <c r="C54" s="12" t="n">
-        <v>17086690</v>
+        <v>17882111</v>
       </c>
       <c r="D54" s="5" t="n">
-        <v>145</v>
+        <v>72</v>
       </c>
       <c r="E54" s="13" t="n">
-        <v>53652.33999999999</v>
+        <v>14284.77</v>
       </c>
       <c r="F54" s="14" t="n">
-        <v>0.01249059940807728</v>
+        <v>0.004714767736314801</v>
       </c>
       <c r="G54" s="13" t="n">
-        <v>3140.007807246458</v>
+        <v>798.8301828570463</v>
       </c>
       <c r="H54" s="10" t="inlineStr">
         <is>
@@ -19442,23 +19442,23 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>Charlotte Area</t>
+          <t>Charleston Area</t>
         </is>
       </c>
       <c r="C55" s="12" t="n">
-        <v>16984802</v>
+        <v>17631276</v>
       </c>
       <c r="D55" s="5" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E55" s="13" t="n">
-        <v>14284.77</v>
+        <v>11501.3</v>
       </c>
       <c r="F55" s="14" t="n">
-        <v>0.004535819728719828</v>
+        <v>0.003646134289996935</v>
       </c>
       <c r="G55" s="13" t="n">
-        <v>841.0324712646047</v>
+        <v>652.3237455984469</v>
       </c>
       <c r="H55" s="10" t="inlineStr">
         <is>
@@ -19477,23 +19477,23 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>Charleston Area</t>
+          <t>Honolulu Area</t>
         </is>
       </c>
       <c r="C56" s="12" t="n">
-        <v>16644974</v>
+        <v>17086690</v>
       </c>
       <c r="D56" s="5" t="n">
-        <v>72</v>
+        <v>145</v>
       </c>
       <c r="E56" s="13" t="n">
-        <v>11281.91</v>
+        <v>53652.33999999999</v>
       </c>
       <c r="F56" s="14" t="n">
-        <v>0.003791594988373067</v>
+        <v>0.01249059940807728</v>
       </c>
       <c r="G56" s="13" t="n">
-        <v>677.7967931941497</v>
+        <v>3140.007807246458</v>
       </c>
       <c r="H56" s="10" t="inlineStr">
         <is>
@@ -19512,32 +19512,32 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>Medellin Area</t>
+          <t>Salt Lake City Area</t>
         </is>
       </c>
       <c r="C57" s="12" t="n">
-        <v>16404082</v>
+        <v>16942604</v>
       </c>
       <c r="D57" s="5" t="n">
-        <v>85</v>
+        <v>124</v>
       </c>
       <c r="E57" s="13" t="n">
-        <v>8931.370000000001</v>
+        <v>36511.36</v>
       </c>
       <c r="F57" s="14" t="n">
-        <v>0.01869522476173918</v>
+        <v>0.006132705456611038</v>
       </c>
       <c r="G57" s="13" t="n">
-        <v>544.460214232043</v>
+        <v>2155.002855523272</v>
       </c>
       <c r="H57" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I57" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I57" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -19551,7 +19551,7 @@
         </is>
       </c>
       <c r="C58" s="12" t="n">
-        <v>16364692</v>
+        <v>16888577</v>
       </c>
       <c r="D58" s="5" t="n">
         <v>37</v>
@@ -19560,10 +19560,10 @@
         <v>11061.23</v>
       </c>
       <c r="F58" s="14" t="n">
-        <v>0.03147844151298417</v>
+        <v>0.03077701573081024</v>
       </c>
       <c r="G58" s="13" t="n">
-        <v>675.9204511762274</v>
+        <v>654.9533450923662</v>
       </c>
       <c r="H58" s="9" t="inlineStr">
         <is>
@@ -19582,32 +19582,32 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>Salt Lake City Area</t>
+          <t>Medellin Area</t>
         </is>
       </c>
       <c r="C59" s="12" t="n">
-        <v>16319548</v>
+        <v>16666627</v>
       </c>
       <c r="D59" s="5" t="n">
-        <v>124</v>
+        <v>85</v>
       </c>
       <c r="E59" s="13" t="n">
-        <v>36511.36</v>
+        <v>8931.370000000001</v>
       </c>
       <c r="F59" s="14" t="n">
-        <v>0.006271681053911542</v>
+        <v>0.01854352413358744</v>
       </c>
       <c r="G59" s="13" t="n">
-        <v>2237.27765009178</v>
+        <v>535.8834754026715</v>
       </c>
       <c r="H59" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I59" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I59" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -19621,7 +19621,7 @@
         </is>
       </c>
       <c r="C60" s="12" t="n">
-        <v>16184429</v>
+        <v>16445800</v>
       </c>
       <c r="D60" s="5" t="n">
         <v>16</v>
@@ -19630,7 +19630,7 @@
         <v>-1231.33</v>
       </c>
       <c r="F60" s="14" t="n">
-        <v>0.1445524584154313</v>
+        <v>0.1441633730192511</v>
       </c>
       <c r="G60" s="13" t="n">
         <v>0</v>
@@ -19652,32 +19652,32 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>Vancouver</t>
+          <t>Sacramento Area</t>
         </is>
       </c>
       <c r="C61" s="12" t="n">
-        <v>15324466</v>
+        <v>16094788</v>
       </c>
       <c r="D61" s="5" t="n">
-        <v>130</v>
+        <v>55</v>
       </c>
       <c r="E61" s="13" t="n">
-        <v>20898.53</v>
+        <v>10272.85</v>
       </c>
       <c r="F61" s="14" t="n">
-        <v>0.02158672282610043</v>
+        <v>0.005294260477366959</v>
       </c>
       <c r="G61" s="13" t="n">
-        <v>1363.73626330601</v>
+        <v>638.2718430339064</v>
       </c>
       <c r="H61" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I61" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I61" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -19687,32 +19687,32 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>Sacramento Area</t>
+          <t>Clearwater</t>
         </is>
       </c>
       <c r="C62" s="12" t="n">
-        <v>15280514</v>
+        <v>15587581</v>
       </c>
       <c r="D62" s="5" t="n">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="E62" s="13" t="n">
-        <v>10272.85</v>
+        <v>7848.83</v>
       </c>
       <c r="F62" s="14" t="n">
-        <v>0.005318734697013465</v>
+        <v>0.005782231380225064</v>
       </c>
       <c r="G62" s="13" t="n">
-        <v>672.2843223729254</v>
+        <v>503.5309840571157</v>
       </c>
       <c r="H62" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I62" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I62" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -19722,32 +19722,32 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>Clearwater</t>
+          <t>Vancouver</t>
         </is>
       </c>
       <c r="C63" s="12" t="n">
-        <v>15143797</v>
+        <v>15505066</v>
       </c>
       <c r="D63" s="5" t="n">
-        <v>39</v>
+        <v>130</v>
       </c>
       <c r="E63" s="13" t="n">
-        <v>7848.83</v>
+        <v>20898.53</v>
       </c>
       <c r="F63" s="14" t="n">
-        <v>0.005900897905591312</v>
+        <v>0.02187078726398198</v>
       </c>
       <c r="G63" s="13" t="n">
-        <v>518.2867942564205</v>
+        <v>1347.851727944918</v>
       </c>
       <c r="H63" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I63" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I63" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -19757,23 +19757,23 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>Calgary Area</t>
+          <t>Jacksonville Area</t>
         </is>
       </c>
       <c r="C64" s="12" t="n">
-        <v>14841484</v>
+        <v>15304220</v>
       </c>
       <c r="D64" s="5" t="n">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="E64" s="13" t="n">
-        <v>10575.92</v>
+        <v>14677.22</v>
       </c>
       <c r="F64" s="14" t="n">
-        <v>0.008722375740862572</v>
+        <v>0.004860620142679601</v>
       </c>
       <c r="G64" s="13" t="n">
-        <v>712.5918135949208</v>
+        <v>959.0309078149687</v>
       </c>
       <c r="H64" s="10" t="inlineStr">
         <is>
@@ -19792,27 +19792,27 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>Mazatlán</t>
+          <t>Calgary Area</t>
         </is>
       </c>
       <c r="C65" s="12" t="n">
-        <v>14713557</v>
+        <v>15071990</v>
       </c>
       <c r="D65" s="5" t="n">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="E65" s="13" t="n">
-        <v>23476.24</v>
+        <v>10575.92</v>
       </c>
       <c r="F65" s="14" t="n">
-        <v>0.04022229295064409</v>
+        <v>0.008720281794242167</v>
       </c>
       <c r="G65" s="13" t="n">
-        <v>1595.551639892379</v>
-      </c>
-      <c r="H65" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+        <v>701.6936715058862</v>
+      </c>
+      <c r="H65" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="I65" s="10" t="inlineStr">
@@ -19827,23 +19827,23 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>Acapulco</t>
+          <t>Mazatlán</t>
         </is>
       </c>
       <c r="C66" s="12" t="n">
-        <v>14678812</v>
+        <v>14975318</v>
       </c>
       <c r="D66" s="5" t="n">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="E66" s="13" t="n">
-        <v>18722.58</v>
+        <v>24228.63</v>
       </c>
       <c r="F66" s="14" t="n">
-        <v>0.04567222470047304</v>
+        <v>0.03982700066870033</v>
       </c>
       <c r="G66" s="13" t="n">
-        <v>1275.483329304851</v>
+        <v>1617.904207443207</v>
       </c>
       <c r="H66" s="9" t="inlineStr">
         <is>
@@ -19862,32 +19862,32 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>Berlin Area</t>
+          <t>Rome Area</t>
         </is>
       </c>
       <c r="C67" s="12" t="n">
-        <v>14318031</v>
+        <v>14728605</v>
       </c>
       <c r="D67" s="5" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="E67" s="13" t="n">
-        <v>7683.45</v>
+        <v>4615.190000000001</v>
       </c>
       <c r="F67" s="14" t="n">
-        <v>0.05657391019756837</v>
+        <v>0.1337472897127732</v>
       </c>
       <c r="G67" s="13" t="n">
-        <v>536.6275572388411</v>
+        <v>313.3487523088575</v>
       </c>
       <c r="H67" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I67" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I67" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -19897,32 +19897,32 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>Rome Area</t>
+          <t>Acapulco</t>
         </is>
       </c>
       <c r="C68" s="12" t="n">
-        <v>14293008</v>
+        <v>14678812</v>
       </c>
       <c r="D68" s="5" t="n">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="E68" s="13" t="n">
-        <v>4615.190000000001</v>
+        <v>18722.58</v>
       </c>
       <c r="F68" s="14" t="n">
-        <v>0.1326678051254152</v>
+        <v>0.04567222470047304</v>
       </c>
       <c r="G68" s="13" t="n">
-        <v>322.8984409719774</v>
-      </c>
-      <c r="H68" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
-        </is>
-      </c>
-      <c r="I68" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+        <v>1275.483329304851</v>
+      </c>
+      <c r="H68" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I68" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -19936,7 +19936,7 @@
         </is>
       </c>
       <c r="C69" s="12" t="n">
-        <v>14208719</v>
+        <v>14561208</v>
       </c>
       <c r="D69" s="5" t="n">
         <v>131</v>
@@ -19945,10 +19945,10 @@
         <v>24930.33</v>
       </c>
       <c r="F69" s="14" t="n">
-        <v>0.008691142389401888</v>
+        <v>0.008795424115911263</v>
       </c>
       <c r="G69" s="13" t="n">
-        <v>1754.579705601891</v>
+        <v>1712.10589121452</v>
       </c>
       <c r="H69" s="10" t="inlineStr">
         <is>
@@ -19967,32 +19967,32 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>Hawái</t>
+          <t>Berlin Area</t>
         </is>
       </c>
       <c r="C70" s="12" t="n">
-        <v>14148411</v>
+        <v>14413669</v>
       </c>
       <c r="D70" s="5" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E70" s="13" t="n">
-        <v>22478.52</v>
+        <v>7683.45</v>
       </c>
       <c r="F70" s="14" t="n">
-        <v>0.02896523150196867</v>
+        <v>0.05691076990875814</v>
       </c>
       <c r="G70" s="13" t="n">
-        <v>1588.766399279749</v>
-      </c>
-      <c r="H70" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="I70" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+        <v>533.066910305766</v>
+      </c>
+      <c r="H70" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="I70" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -20002,23 +20002,23 @@
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>Jacksonville Area</t>
+          <t>Portland (and vicinity), OR, US</t>
         </is>
       </c>
       <c r="C71" s="12" t="n">
-        <v>13962789</v>
+        <v>14385827</v>
       </c>
       <c r="D71" s="5" t="n">
-        <v>85</v>
+        <v>147</v>
       </c>
       <c r="E71" s="13" t="n">
-        <v>14677.22</v>
+        <v>24192.25</v>
       </c>
       <c r="F71" s="14" t="n">
-        <v>0.004357367285289493</v>
+        <v>0.004499984602901175</v>
       </c>
       <c r="G71" s="13" t="n">
-        <v>1051.166783369712</v>
+        <v>1681.672523936232</v>
       </c>
       <c r="H71" s="10" t="inlineStr">
         <is>
@@ -20037,23 +20037,23 @@
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>Portland (and vicinity), OR, US</t>
+          <t>Hawái</t>
         </is>
       </c>
       <c r="C72" s="12" t="n">
-        <v>13844645</v>
+        <v>14338091</v>
       </c>
       <c r="D72" s="5" t="n">
-        <v>147</v>
+        <v>29</v>
       </c>
       <c r="E72" s="13" t="n">
-        <v>24192.25</v>
+        <v>22478.52</v>
       </c>
       <c r="F72" s="14" t="n">
-        <v>0.004587333225228961</v>
+        <v>0.0296467639938957</v>
       </c>
       <c r="G72" s="13" t="n">
-        <v>1747.408474540156</v>
+        <v>1567.74845410034</v>
       </c>
       <c r="H72" s="10" t="inlineStr">
         <is>
@@ -20072,32 +20072,32 @@
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>West Palm Beach Area</t>
+          <t>Cleveland Area</t>
         </is>
       </c>
       <c r="C73" s="12" t="n">
-        <v>13346759</v>
+        <v>14116001</v>
       </c>
       <c r="D73" s="5" t="n">
-        <v>33</v>
+        <v>76</v>
       </c>
       <c r="E73" s="13" t="n">
-        <v>7276.08</v>
+        <v>14325.15</v>
       </c>
       <c r="F73" s="14" t="n">
-        <v>0.003692506922467095</v>
+        <v>0.002702323412983606</v>
       </c>
       <c r="G73" s="13" t="n">
-        <v>545.1570677195864</v>
+        <v>1014.816448369478</v>
       </c>
       <c r="H73" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I73" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I73" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -20107,32 +20107,32 @@
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>San Andres, Providencia y Santa Catalina</t>
+          <t>West Palm Beach Area</t>
         </is>
       </c>
       <c r="C74" s="12" t="n">
-        <v>13282359</v>
+        <v>13435361</v>
       </c>
       <c r="D74" s="5" t="n">
-        <v>141</v>
+        <v>33</v>
       </c>
       <c r="E74" s="13" t="n">
-        <v>21357.76</v>
+        <v>7276.08</v>
       </c>
       <c r="F74" s="14" t="n">
-        <v>0.01837166123879049</v>
+        <v>0.003671654226484871</v>
       </c>
       <c r="G74" s="13" t="n">
-        <v>1607.97942594384</v>
+        <v>541.5619275135221</v>
       </c>
       <c r="H74" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I74" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I74" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -20142,27 +20142,27 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>Ixtapa / Zihuatanejo</t>
+          <t>San Andres, Providencia y Santa Catalina</t>
         </is>
       </c>
       <c r="C75" s="12" t="n">
-        <v>13207196</v>
+        <v>13373199</v>
       </c>
       <c r="D75" s="5" t="n">
-        <v>598</v>
+        <v>141</v>
       </c>
       <c r="E75" s="13" t="n">
-        <v>273452.5800000001</v>
+        <v>21357.76</v>
       </c>
       <c r="F75" s="14" t="n">
-        <v>0.03681992756070251</v>
+        <v>0.01828530331448743</v>
       </c>
       <c r="G75" s="13" t="n">
-        <v>20704.81728294182</v>
-      </c>
-      <c r="H75" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+        <v>1597.056919589696</v>
+      </c>
+      <c r="H75" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="I75" s="10" t="inlineStr">
@@ -20177,27 +20177,27 @@
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>Long Island Area</t>
+          <t>Ixtapa / Zihuatanejo</t>
         </is>
       </c>
       <c r="C76" s="12" t="n">
-        <v>12970043</v>
+        <v>13207196</v>
       </c>
       <c r="D76" s="5" t="n">
-        <v>58</v>
+        <v>598</v>
       </c>
       <c r="E76" s="13" t="n">
-        <v>25592.94</v>
+        <v>273452.5800000001</v>
       </c>
       <c r="F76" s="14" t="n">
-        <v>0.004023116962680848</v>
+        <v>0.03681992756070251</v>
       </c>
       <c r="G76" s="13" t="n">
-        <v>1973.234784186914</v>
-      </c>
-      <c r="H76" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+        <v>20704.81728294182</v>
+      </c>
+      <c r="H76" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="I76" s="10" t="inlineStr">
@@ -20212,23 +20212,23 @@
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>Cleveland Area</t>
+          <t>Portland (and vicinity), ME, US</t>
         </is>
       </c>
       <c r="C77" s="12" t="n">
-        <v>12865187</v>
+        <v>13106279</v>
       </c>
       <c r="D77" s="5" t="n">
-        <v>76</v>
+        <v>42</v>
       </c>
       <c r="E77" s="13" t="n">
-        <v>14325.15</v>
+        <v>9242.48</v>
       </c>
       <c r="F77" s="14" t="n">
-        <v>0.002803768029178278</v>
+        <v>0.004528211248974632</v>
       </c>
       <c r="G77" s="13" t="n">
-        <v>1113.481677335899</v>
+        <v>705.194815401076</v>
       </c>
       <c r="H77" s="10" t="inlineStr">
         <is>
@@ -20247,23 +20247,23 @@
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>Portland (and vicinity), ME, US</t>
+          <t>Long Island Area</t>
         </is>
       </c>
       <c r="C78" s="12" t="n">
-        <v>12848605</v>
+        <v>12970043</v>
       </c>
       <c r="D78" s="5" t="n">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="E78" s="13" t="n">
-        <v>9242.48</v>
+        <v>25592.94</v>
       </c>
       <c r="F78" s="14" t="n">
-        <v>0.004513486094404801</v>
+        <v>0.004023116962680848</v>
       </c>
       <c r="G78" s="13" t="n">
-        <v>719.3372354430695</v>
+        <v>1973.234784186914</v>
       </c>
       <c r="H78" s="10" t="inlineStr">
         <is>
@@ -20282,23 +20282,23 @@
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>Puerto Rico</t>
+          <t>San Jose - Silicon Valley Area</t>
         </is>
       </c>
       <c r="C79" s="12" t="n">
-        <v>12597318</v>
+        <v>12926485</v>
       </c>
       <c r="D79" s="5" t="n">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="E79" s="13" t="n">
-        <v>14869.4</v>
+        <v>10488.35</v>
       </c>
       <c r="F79" s="14" t="n">
-        <v>0.005398212540161327</v>
+        <v>0.006550736723865768</v>
       </c>
       <c r="G79" s="13" t="n">
-        <v>1180.362359670527</v>
+        <v>811.3845333824315</v>
       </c>
       <c r="H79" s="10" t="inlineStr">
         <is>
@@ -20317,23 +20317,23 @@
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>San Jose - Silicon Valley Area</t>
+          <t>Puerto Rico</t>
         </is>
       </c>
       <c r="C80" s="12" t="n">
-        <v>12569761</v>
+        <v>12685563</v>
       </c>
       <c r="D80" s="5" t="n">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="E80" s="13" t="n">
-        <v>10488.35</v>
+        <v>14869.4</v>
       </c>
       <c r="F80" s="14" t="n">
-        <v>0.006602273503847846</v>
+        <v>0.005494040745373303</v>
       </c>
       <c r="G80" s="13" t="n">
-        <v>834.4112509378659</v>
+        <v>1172.151366084422</v>
       </c>
       <c r="H80" s="10" t="inlineStr">
         <is>
@@ -20356,7 +20356,7 @@
         </is>
       </c>
       <c r="C81" s="12" t="n">
-        <v>11872385</v>
+        <v>12507282</v>
       </c>
       <c r="D81" s="5" t="n">
         <v>74</v>
@@ -20365,10 +20365,10 @@
         <v>16033.8</v>
       </c>
       <c r="F81" s="14" t="n">
-        <v>0.002802553993995309</v>
+        <v>0.002752316610435425</v>
       </c>
       <c r="G81" s="13" t="n">
-        <v>1350.512133829892</v>
+        <v>1281.957183023458</v>
       </c>
       <c r="H81" s="10" t="inlineStr">
         <is>
@@ -20391,7 +20391,7 @@
         </is>
       </c>
       <c r="C82" s="12" t="n">
-        <v>11839240</v>
+        <v>12016970</v>
       </c>
       <c r="D82" s="5" t="n">
         <v>85</v>
@@ -20400,10 +20400,10 @@
         <v>18201.5</v>
       </c>
       <c r="F82" s="14" t="n">
-        <v>0.01577829320125278</v>
+        <v>0.01593471565627608</v>
       </c>
       <c r="G82" s="13" t="n">
-        <v>1537.387535010693</v>
+        <v>1514.649699549887</v>
       </c>
       <c r="H82" s="10" t="inlineStr">
         <is>
@@ -20422,23 +20422,23 @@
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>Edmonton Area</t>
+          <t>Norfolk - Virginia Beach Area</t>
         </is>
       </c>
       <c r="C83" s="12" t="n">
-        <v>11351557</v>
+        <v>11651615</v>
       </c>
       <c r="D83" s="5" t="n">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="E83" s="13" t="n">
-        <v>5491.45</v>
+        <v>4447.38</v>
       </c>
       <c r="F83" s="14" t="n">
-        <v>0.003871275103494613</v>
+        <v>0.003311558097310974</v>
       </c>
       <c r="G83" s="13" t="n">
-        <v>483.7618310862554</v>
+        <v>381.6964429394552</v>
       </c>
       <c r="H83" s="10" t="inlineStr">
         <is>
@@ -20457,32 +20457,32 @@
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Edmonton Area</t>
         </is>
       </c>
       <c r="C84" s="12" t="n">
-        <v>11351439</v>
+        <v>11627657</v>
       </c>
       <c r="D84" s="5" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="E84" s="13" t="n">
-        <v>63670.14</v>
+        <v>5491.45</v>
       </c>
       <c r="F84" s="14" t="n">
-        <v>0.04271564160279591</v>
+        <v>0.003824760224695311</v>
       </c>
       <c r="G84" s="13" t="n">
-        <v>5608.992833419622</v>
-      </c>
-      <c r="H84" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
-        </is>
-      </c>
-      <c r="I84" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+        <v>472.274852964789</v>
+      </c>
+      <c r="H84" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I84" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -20492,32 +20492,32 @@
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>Merida</t>
+          <t>Savannah Area</t>
         </is>
       </c>
       <c r="C85" s="12" t="n">
-        <v>11310613</v>
+        <v>11601689</v>
       </c>
       <c r="D85" s="5" t="n">
-        <v>92</v>
+        <v>25</v>
       </c>
       <c r="E85" s="13" t="n">
-        <v>12325.69</v>
+        <v>6154.76</v>
       </c>
       <c r="F85" s="14" t="n">
-        <v>0.02056581725499759</v>
+        <v>0.005705720951492494</v>
       </c>
       <c r="G85" s="13" t="n">
-        <v>1089.745533685928</v>
+        <v>530.5055151883489</v>
       </c>
       <c r="H85" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I85" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I85" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -20527,23 +20527,23 @@
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>London Area</t>
+          <t>Orange County Area</t>
         </is>
       </c>
       <c r="C86" s="12" t="n">
-        <v>11296924</v>
+        <v>11503838</v>
       </c>
       <c r="D86" s="5" t="n">
-        <v>72</v>
+        <v>19</v>
       </c>
       <c r="E86" s="13" t="n">
-        <v>11181.81</v>
+        <v>8165.54</v>
       </c>
       <c r="F86" s="14" t="n">
-        <v>0.02598149726421104</v>
+        <v>0.00443112985422778</v>
       </c>
       <c r="G86" s="13" t="n">
-        <v>989.8101465496272</v>
+        <v>709.8100651278295</v>
       </c>
       <c r="H86" s="10" t="inlineStr">
         <is>
@@ -20562,23 +20562,23 @@
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>Orange County Area</t>
+          <t>Merida</t>
         </is>
       </c>
       <c r="C87" s="12" t="n">
-        <v>11245537</v>
+        <v>11478479</v>
       </c>
       <c r="D87" s="5" t="n">
-        <v>19</v>
+        <v>92</v>
       </c>
       <c r="E87" s="13" t="n">
-        <v>8165.54</v>
+        <v>12325.69</v>
       </c>
       <c r="F87" s="14" t="n">
-        <v>0.004470751374523066</v>
+        <v>0.02043032007986424</v>
       </c>
       <c r="G87" s="13" t="n">
-        <v>726.1138352041347</v>
+        <v>1073.808646598561</v>
       </c>
       <c r="H87" s="10" t="inlineStr">
         <is>
@@ -20597,32 +20597,32 @@
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>Norfolk - Virginia Beach Area</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="C88" s="12" t="n">
-        <v>10852037</v>
+        <v>11438679</v>
       </c>
       <c r="D88" s="5" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="E88" s="13" t="n">
-        <v>4447.38</v>
+        <v>62167.27</v>
       </c>
       <c r="F88" s="14" t="n">
-        <v>0.003414842761778273</v>
+        <v>0.04249328091119613</v>
       </c>
       <c r="G88" s="13" t="n">
-        <v>409.8198338247465</v>
-      </c>
-      <c r="H88" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="I88" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+        <v>5434.829493860261</v>
+      </c>
+      <c r="H88" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I88" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -20632,32 +20632,32 @@
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>Louisville Area</t>
+          <t>London Area</t>
         </is>
       </c>
       <c r="C89" s="12" t="n">
-        <v>10827295</v>
+        <v>11296924</v>
       </c>
       <c r="D89" s="5" t="n">
-        <v>43</v>
+        <v>72</v>
       </c>
       <c r="E89" s="13" t="n">
-        <v>3127.99</v>
+        <v>11181.81</v>
       </c>
       <c r="F89" s="14" t="n">
-        <v>0.003616969889524577</v>
+        <v>0.02598149726421104</v>
       </c>
       <c r="G89" s="13" t="n">
-        <v>288.8985660776768</v>
+        <v>989.8101465496272</v>
       </c>
       <c r="H89" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I89" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="I89" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -20667,32 +20667,32 @@
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>Gatlinburg - Pigeon Forge Area</t>
+          <t>Louisville Area</t>
         </is>
       </c>
       <c r="C90" s="12" t="n">
-        <v>10823065</v>
+        <v>11284512</v>
       </c>
       <c r="D90" s="5" t="n">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="E90" s="13" t="n">
-        <v>1637.8</v>
+        <v>3127.99</v>
       </c>
       <c r="F90" s="14" t="n">
-        <v>0.001443306494047666</v>
+        <v>0.003529970990327273</v>
       </c>
       <c r="G90" s="13" t="n">
-        <v>151.324971253522</v>
+        <v>277.1932007338908</v>
       </c>
       <c r="H90" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I90" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I90" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -20702,23 +20702,23 @@
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>Savannah Area</t>
+          <t>Boston Area</t>
         </is>
       </c>
       <c r="C91" s="12" t="n">
-        <v>10801950</v>
+        <v>11062476</v>
       </c>
       <c r="D91" s="5" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E91" s="13" t="n">
-        <v>6154.76</v>
+        <v>5695.280000000001</v>
       </c>
       <c r="F91" s="14" t="n">
-        <v>0.005903934011914516</v>
+        <v>0.00430952347376844</v>
       </c>
       <c r="G91" s="13" t="n">
-        <v>569.7823078240503</v>
+        <v>514.8286875379437</v>
       </c>
       <c r="H91" s="10" t="inlineStr">
         <is>
@@ -20737,32 +20737,32 @@
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>Boston Area</t>
+          <t>Gatlinburg - Pigeon Forge Area</t>
         </is>
       </c>
       <c r="C92" s="12" t="n">
-        <v>10799654</v>
+        <v>11004954</v>
       </c>
       <c r="D92" s="5" t="n">
-        <v>50</v>
+        <v>19</v>
       </c>
       <c r="E92" s="13" t="n">
-        <v>5695.280000000001</v>
+        <v>1637.8</v>
       </c>
       <c r="F92" s="14" t="n">
-        <v>0.004282081629652209</v>
+        <v>0.001429992347082959</v>
       </c>
       <c r="G92" s="13" t="n">
-        <v>527.357635716848</v>
+        <v>148.8238842252317</v>
       </c>
       <c r="H92" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I92" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I92" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -20772,23 +20772,23 @@
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>San Jose Area</t>
+          <t>Richmond Area</t>
         </is>
       </c>
       <c r="C93" s="12" t="n">
-        <v>10502788</v>
+        <v>10883071</v>
       </c>
       <c r="D93" s="5" t="n">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="E93" s="13" t="n">
-        <v>5832.489999999999</v>
+        <v>7020.18</v>
       </c>
       <c r="F93" s="14" t="n">
-        <v>0.008995897089420448</v>
+        <v>0.002022315208639179</v>
       </c>
       <c r="G93" s="13" t="n">
-        <v>555.3277853461385</v>
+        <v>645.0550584481164</v>
       </c>
       <c r="H93" s="10" t="inlineStr">
         <is>
@@ -20807,32 +20807,32 @@
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>Múnich Area</t>
+          <t>San Jose Area</t>
         </is>
       </c>
       <c r="C94" s="12" t="n">
-        <v>10485636</v>
+        <v>10770154</v>
       </c>
       <c r="D94" s="5" t="n">
-        <v>132</v>
+        <v>17</v>
       </c>
       <c r="E94" s="13" t="n">
-        <v>14207.15</v>
+        <v>5832.489999999999</v>
       </c>
       <c r="F94" s="14" t="n">
-        <v>0.03880060303447497</v>
+        <v>0.008808694843174944</v>
       </c>
       <c r="G94" s="13" t="n">
-        <v>1354.915429068871</v>
-      </c>
-      <c r="H94" s="9" t="inlineStr">
+        <v>541.5419315266986</v>
+      </c>
+      <c r="H94" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I94" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
-        </is>
-      </c>
-      <c r="I94" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -20842,32 +20842,32 @@
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>Amsterdam</t>
+          <t>Kansas City (and vicinity), MO, US</t>
         </is>
       </c>
       <c r="C95" s="12" t="n">
-        <v>10400900</v>
+        <v>10607796</v>
       </c>
       <c r="D95" s="5" t="n">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="E95" s="13" t="n">
-        <v>2204.22</v>
+        <v>7337.11</v>
       </c>
       <c r="F95" s="14" t="n">
-        <v>0.06296657020065571</v>
+        <v>0.006905864328461822</v>
       </c>
       <c r="G95" s="13" t="n">
-        <v>211.925891028661</v>
-      </c>
-      <c r="H95" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
-        </is>
-      </c>
-      <c r="I95" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+        <v>691.6714838784607</v>
+      </c>
+      <c r="H95" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I95" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -20877,23 +20877,23 @@
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>Huatulco Area</t>
+          <t>Múnich Area</t>
         </is>
       </c>
       <c r="C96" s="12" t="n">
-        <v>10351293</v>
+        <v>10581203</v>
       </c>
       <c r="D96" s="5" t="n">
-        <v>108</v>
+        <v>132</v>
       </c>
       <c r="E96" s="13" t="n">
-        <v>23514.75</v>
+        <v>14207.15</v>
       </c>
       <c r="F96" s="14" t="n">
-        <v>0.04788425948333218</v>
+        <v>0.038926481232805</v>
       </c>
       <c r="G96" s="13" t="n">
-        <v>2271.672727262189</v>
+        <v>1342.678143496538</v>
       </c>
       <c r="H96" s="9" t="inlineStr">
         <is>
@@ -20912,32 +20912,32 @@
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>Richmond Area</t>
+          <t>Amsterdam</t>
         </is>
       </c>
       <c r="C97" s="12" t="n">
-        <v>9807524</v>
+        <v>10580490</v>
       </c>
       <c r="D97" s="5" t="n">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="E97" s="13" t="n">
-        <v>7020.18</v>
+        <v>2204.22</v>
       </c>
       <c r="F97" s="14" t="n">
-        <v>0.00199938333059394</v>
+        <v>0.0627918933811194</v>
       </c>
       <c r="G97" s="13" t="n">
-        <v>715.7953424330136</v>
-      </c>
-      <c r="H97" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="I97" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+        <v>208.3287257962533</v>
+      </c>
+      <c r="H97" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="I97" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -20947,23 +20947,23 @@
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>Cozumel</t>
+          <t>Huatulco Area</t>
         </is>
       </c>
       <c r="C98" s="12" t="n">
-        <v>9763761</v>
+        <v>10435436</v>
       </c>
       <c r="D98" s="5" t="n">
-        <v>41</v>
+        <v>108</v>
       </c>
       <c r="E98" s="13" t="n">
-        <v>9815.540000000001</v>
+        <v>23514.75</v>
       </c>
       <c r="F98" s="14" t="n">
-        <v>0.03507357461945249</v>
+        <v>0.04828854299906588</v>
       </c>
       <c r="G98" s="13" t="n">
-        <v>1005.303181837409</v>
+        <v>2253.355777372407</v>
       </c>
       <c r="H98" s="9" t="inlineStr">
         <is>
@@ -20982,23 +20982,23 @@
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>Kansas City (and vicinity), MO, US</t>
+          <t>Rochester Area</t>
         </is>
       </c>
       <c r="C99" s="12" t="n">
-        <v>9720438</v>
+        <v>10386462</v>
       </c>
       <c r="D99" s="5" t="n">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="E99" s="13" t="n">
-        <v>7337.11</v>
+        <v>13318.28</v>
       </c>
       <c r="F99" s="14" t="n">
-        <v>0.006917486640005317</v>
+        <v>0.002714398801054681</v>
       </c>
       <c r="G99" s="13" t="n">
-        <v>754.8126946542943</v>
+        <v>1282.273020399054</v>
       </c>
       <c r="H99" s="10" t="inlineStr">
         <is>
@@ -21017,23 +21017,23 @@
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t>Rochester Area</t>
+          <t>Oklahoma City Area</t>
         </is>
       </c>
       <c r="C100" s="12" t="n">
-        <v>9316559</v>
+        <v>10050832</v>
       </c>
       <c r="D100" s="5" t="n">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="E100" s="13" t="n">
-        <v>12306.82</v>
+        <v>7214.73</v>
       </c>
       <c r="F100" s="14" t="n">
-        <v>0.002680388757265424</v>
+        <v>0.001640560701840405</v>
       </c>
       <c r="G100" s="13" t="n">
-        <v>1320.961956018311</v>
+        <v>717.8241562489552</v>
       </c>
       <c r="H100" s="10" t="inlineStr">
         <is>
@@ -21052,32 +21052,32 @@
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>San Luis, Misuri Area</t>
+          <t>Northern Virginia Area</t>
         </is>
       </c>
       <c r="C101" s="12" t="n">
-        <v>9315550</v>
+        <v>9988418</v>
       </c>
       <c r="D101" s="5" t="n">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="E101" s="13" t="n">
-        <v>4535.160000000001</v>
+        <v>11071.7</v>
       </c>
       <c r="F101" s="14" t="n">
-        <v>0.004757958467293933</v>
+        <v>0.004129883230757863</v>
       </c>
       <c r="G101" s="13" t="n">
-        <v>486.8375994976143</v>
+        <v>1108.453811204137</v>
       </c>
       <c r="H101" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I101" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="I101" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -21087,32 +21087,32 @@
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>Fort Walton Beach - Destin Area</t>
+          <t>Cozumel</t>
         </is>
       </c>
       <c r="C102" s="12" t="n">
-        <v>9170147</v>
+        <v>9763761</v>
       </c>
       <c r="D102" s="5" t="n">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="E102" s="13" t="n">
-        <v>1397.01</v>
+        <v>9815.540000000001</v>
       </c>
       <c r="F102" s="14" t="n">
-        <v>0.003514992725852704</v>
+        <v>0.03507357461945249</v>
       </c>
       <c r="G102" s="13" t="n">
-        <v>152.3432503317559</v>
-      </c>
-      <c r="H102" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="I102" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+        <v>1005.303181837409</v>
+      </c>
+      <c r="H102" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I102" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -21122,32 +21122,32 @@
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>Northern Virginia Area</t>
+          <t>San Luis, Misuri Area</t>
         </is>
       </c>
       <c r="C103" s="12" t="n">
-        <v>9009018</v>
+        <v>9589766</v>
       </c>
       <c r="D103" s="5" t="n">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="E103" s="13" t="n">
-        <v>10465.76</v>
+        <v>4535.160000000001</v>
       </c>
       <c r="F103" s="14" t="n">
-        <v>0.004180144828215462</v>
+        <v>0.0046869756780301</v>
       </c>
       <c r="G103" s="13" t="n">
-        <v>1161.698200625196</v>
+        <v>472.9166488525373</v>
       </c>
       <c r="H103" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I103" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I103" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -21157,23 +21157,23 @@
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
-          <t>Oklahoma City Area</t>
+          <t>Memphis Area</t>
         </is>
       </c>
       <c r="C104" s="12" t="n">
-        <v>8985297</v>
+        <v>9521738</v>
       </c>
       <c r="D104" s="5" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="E104" s="13" t="n">
-        <v>7214.73</v>
+        <v>13315.82</v>
       </c>
       <c r="F104" s="14" t="n">
-        <v>0.00169031697004562</v>
+        <v>0.01749764591296253</v>
       </c>
       <c r="G104" s="13" t="n">
-        <v>802.9484167301314</v>
+        <v>1398.465280183093</v>
       </c>
       <c r="H104" s="10" t="inlineStr">
         <is>
@@ -21192,23 +21192,23 @@
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>Fort Myers Area</t>
+          <t>Fort Walton Beach - Destin Area</t>
         </is>
       </c>
       <c r="C105" s="12" t="n">
-        <v>8974471</v>
+        <v>9256976</v>
       </c>
       <c r="D105" s="5" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E105" s="13" t="n">
-        <v>751.6900000000001</v>
+        <v>1397.01</v>
       </c>
       <c r="F105" s="14" t="n">
-        <v>0.004582665652382185</v>
+        <v>0.003490232663452946</v>
       </c>
       <c r="G105" s="13" t="n">
-        <v>83.75869730928989</v>
+        <v>150.9142942576496</v>
       </c>
       <c r="H105" s="10" t="inlineStr">
         <is>
@@ -21232,7 +21232,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I91"/>
+  <dimension ref="A1:I94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -21263,7 +21263,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 04:09 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 05:04 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -21324,19 +21324,19 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>3087426774</v>
+        <v>3261678050</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>13478</v>
+        <v>13665</v>
       </c>
       <c r="E6" s="13" t="n">
-        <v>2740018.9</v>
+        <v>2779083.72</v>
       </c>
       <c r="F6" s="14" t="n">
-        <v>0.01146903120041415</v>
+        <v>0.01119061429131548</v>
       </c>
       <c r="G6" s="13" t="n">
-        <v>887.4765623834031</v>
+        <v>852.0410897084096</v>
       </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
@@ -21359,19 +21359,19 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>630859092</v>
+        <v>637203113</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>4603</v>
+        <v>4614</v>
       </c>
       <c r="E7" s="13" t="n">
-        <v>1366242.84</v>
+        <v>1367510.59</v>
       </c>
       <c r="F7" s="14" t="n">
-        <v>0.03339240135735414</v>
+        <v>0.0334515911255443</v>
       </c>
       <c r="G7" s="13" t="n">
-        <v>2165.686216344489</v>
+        <v>2146.114107261118</v>
       </c>
       <c r="H7" s="9" t="inlineStr">
         <is>
@@ -21394,19 +21394,19 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>216102258</v>
+        <v>221962775</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>1125</v>
+        <v>1138</v>
       </c>
       <c r="E8" s="13" t="n">
-        <v>203524.27</v>
+        <v>203440.05</v>
       </c>
       <c r="F8" s="14" t="n">
-        <v>0.01656662004892147</v>
+        <v>0.01683107899511528</v>
       </c>
       <c r="G8" s="13" t="n">
-        <v>941.7961287567852</v>
+        <v>916.5503089425692</v>
       </c>
       <c r="H8" s="10" t="inlineStr">
         <is>
@@ -21429,19 +21429,19 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>116826271</v>
+        <v>119331282</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>661</v>
+        <v>671</v>
       </c>
       <c r="E9" s="13" t="n">
-        <v>105203.44</v>
+        <v>105627.34</v>
       </c>
       <c r="F9" s="14" t="n">
-        <v>0.01360827480319046</v>
+        <v>0.01356030013990799</v>
       </c>
       <c r="G9" s="13" t="n">
-        <v>900.5118377868964</v>
+        <v>885.1605231225119</v>
       </c>
       <c r="H9" s="10" t="inlineStr">
         <is>
@@ -21460,32 +21460,32 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>República Dominicana</t>
+          <t>Francia</t>
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>105456805</v>
+        <v>106502657</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>272</v>
+        <v>89</v>
       </c>
       <c r="E10" s="13" t="n">
-        <v>97728.47</v>
+        <v>59693.81</v>
       </c>
       <c r="F10" s="14" t="n">
-        <v>0.05203095238851585</v>
+        <v>0.06803753262230819</v>
       </c>
       <c r="G10" s="13" t="n">
-        <v>926.7156348990471</v>
+        <v>560.4912748796492</v>
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I10" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I10" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -21495,32 +21495,32 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Francia</t>
+          <t>República Dominicana</t>
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>101314032</v>
+        <v>105820412</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>86</v>
+        <v>272</v>
       </c>
       <c r="E11" s="13" t="n">
-        <v>60112.39</v>
+        <v>97728.47</v>
       </c>
       <c r="F11" s="14" t="n">
-        <v>0.06922470522148402</v>
+        <v>0.05194781324419716</v>
       </c>
       <c r="G11" s="13" t="n">
-        <v>593.3273882535836</v>
+        <v>923.531369354336</v>
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I11" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I11" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -21534,19 +21534,19 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>91110802</v>
+        <v>93508618</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="E12" s="13" t="n">
-        <v>80313.28</v>
+        <v>81013.34999999999</v>
       </c>
       <c r="F12" s="14" t="n">
-        <v>0.03570141990408558</v>
+        <v>0.03564348475345876</v>
       </c>
       <c r="G12" s="13" t="n">
-        <v>881.4902101289812</v>
+        <v>866.3730865961467</v>
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
@@ -21569,19 +21569,19 @@
         </is>
       </c>
       <c r="C13" s="12" t="n">
-        <v>75473574</v>
+        <v>78754725</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>532</v>
+        <v>543</v>
       </c>
       <c r="E13" s="13" t="n">
-        <v>61059.84</v>
+        <v>61765.99</v>
       </c>
       <c r="F13" s="14" t="n">
-        <v>0.03518019432867987</v>
+        <v>0.03460423485701969</v>
       </c>
       <c r="G13" s="13" t="n">
-        <v>809.0227713345071</v>
+        <v>784.2829747675456</v>
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
@@ -21604,19 +21604,19 @@
         </is>
       </c>
       <c r="C14" s="12" t="n">
-        <v>56988751</v>
+        <v>59190492</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E14" s="13" t="n">
-        <v>31245.41</v>
+        <v>31437.54</v>
       </c>
       <c r="F14" s="14" t="n">
-        <v>0.1291065670135498</v>
+        <v>0.1292286267868833</v>
       </c>
       <c r="G14" s="13" t="n">
-        <v>548.2732899340082</v>
+        <v>531.1248299811396</v>
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
@@ -21639,19 +21639,19 @@
         </is>
       </c>
       <c r="C15" s="12" t="n">
-        <v>35468282</v>
+        <v>36956266</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E15" s="13" t="n">
-        <v>23952.08</v>
+        <v>26517.26</v>
       </c>
       <c r="F15" s="14" t="n">
-        <v>0.09957674296150008</v>
+        <v>0.101526788447729</v>
       </c>
       <c r="G15" s="13" t="n">
-        <v>675.3098444407316</v>
+        <v>717.5308241368324</v>
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
@@ -21674,19 +21674,19 @@
         </is>
       </c>
       <c r="C16" s="12" t="n">
-        <v>31798093</v>
+        <v>32969134</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E16" s="13" t="n">
-        <v>14106.61</v>
+        <v>14196.26</v>
       </c>
       <c r="F16" s="14" t="n">
-        <v>0.1085320116523969</v>
+        <v>0.1078129622694973</v>
       </c>
       <c r="G16" s="13" t="n">
-        <v>443.6306919411802</v>
+        <v>430.5924444360595</v>
       </c>
       <c r="H16" s="8" t="inlineStr">
         <is>
@@ -21709,16 +21709,16 @@
         </is>
       </c>
       <c r="C17" s="12" t="n">
-        <v>19242576</v>
+        <v>21203907</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E17" s="13" t="n">
-        <v>-1011.38</v>
+        <v>-1262.68</v>
       </c>
       <c r="F17" s="14" t="n">
-        <v>0.08137107006878913</v>
+        <v>0.0810983089107116</v>
       </c>
       <c r="G17" s="13" t="n">
         <v>0</v>
@@ -21744,7 +21744,7 @@
         </is>
       </c>
       <c r="C18" s="12" t="n">
-        <v>14865495</v>
+        <v>15408011</v>
       </c>
       <c r="D18" s="5" t="n">
         <v>37</v>
@@ -21753,7 +21753,7 @@
         <v>-2036.06</v>
       </c>
       <c r="F18" s="14" t="n">
-        <v>0.0513620972594589</v>
+        <v>0.05078754162363981</v>
       </c>
       <c r="G18" s="13" t="n">
         <v>0</v>
@@ -21779,19 +21779,19 @@
         </is>
       </c>
       <c r="C19" s="12" t="n">
-        <v>13551901</v>
+        <v>14812021</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E19" s="13" t="n">
-        <v>11791.3</v>
+        <v>11961.46</v>
       </c>
       <c r="F19" s="14" t="n">
-        <v>0.02627055790918189</v>
+        <v>0.0270580901822918</v>
       </c>
       <c r="G19" s="13" t="n">
-        <v>870.0845733746136</v>
+        <v>807.5508399562759</v>
       </c>
       <c r="H19" s="10" t="inlineStr">
         <is>
@@ -21814,19 +21814,19 @@
         </is>
       </c>
       <c r="C20" s="12" t="n">
-        <v>13064160</v>
+        <v>14127217</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="E20" s="13" t="n">
-        <v>37590.69</v>
+        <v>35603.18</v>
       </c>
       <c r="F20" s="14" t="n">
-        <v>0.0643575247088217</v>
+        <v>0.06075251764024011</v>
       </c>
       <c r="G20" s="13" t="n">
-        <v>2877.390509607966</v>
+        <v>2520.18355773823</v>
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
@@ -21849,7 +21849,7 @@
         </is>
       </c>
       <c r="C21" s="12" t="n">
-        <v>12597318</v>
+        <v>12685563</v>
       </c>
       <c r="D21" s="5" t="n">
         <v>49</v>
@@ -21858,10 +21858,10 @@
         <v>14869.4</v>
       </c>
       <c r="F21" s="14" t="n">
-        <v>0.005398212540161327</v>
+        <v>0.005494040745373303</v>
       </c>
       <c r="G21" s="13" t="n">
-        <v>1180.362359670527</v>
+        <v>1172.151366084422</v>
       </c>
       <c r="H21" s="10" t="inlineStr">
         <is>
@@ -21884,7 +21884,7 @@
         </is>
       </c>
       <c r="C22" s="12" t="n">
-        <v>12291543</v>
+        <v>12383417</v>
       </c>
       <c r="D22" s="5" t="n">
         <v>29</v>
@@ -21893,10 +21893,10 @@
         <v>6519.11</v>
       </c>
       <c r="F22" s="14" t="n">
-        <v>0.04721669199709101</v>
+        <v>0.04710089307337385</v>
       </c>
       <c r="G22" s="13" t="n">
-        <v>530.3736072842929</v>
+        <v>526.4387042768567</v>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
@@ -21919,19 +21919,19 @@
         </is>
       </c>
       <c r="C23" s="12" t="n">
-        <v>11351439</v>
+        <v>11438679</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E23" s="13" t="n">
-        <v>63670.14</v>
+        <v>62167.27</v>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0.04271564160279591</v>
+        <v>0.04249328091119613</v>
       </c>
       <c r="G23" s="13" t="n">
-        <v>5608.992833419622</v>
+        <v>5434.829493860261</v>
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
@@ -21954,7 +21954,7 @@
         </is>
       </c>
       <c r="C24" s="12" t="n">
-        <v>9273511</v>
+        <v>9629837</v>
       </c>
       <c r="D24" s="5" t="n">
         <v>40</v>
@@ -21963,10 +21963,10 @@
         <v>6456.860000000001</v>
       </c>
       <c r="F24" s="14" t="n">
-        <v>0.06716668584315046</v>
+        <v>0.06732035028214911</v>
       </c>
       <c r="G24" s="13" t="n">
-        <v>696.2691908167253</v>
+        <v>670.5056378420529</v>
       </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
@@ -21985,27 +21985,27 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Jamaica</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="C25" s="12" t="n">
-        <v>7605637</v>
+        <v>7715024</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="E25" s="13" t="n">
-        <v>28980.88</v>
+        <v>6663.11</v>
       </c>
       <c r="F25" s="14" t="n">
-        <v>0.06492158382000086</v>
+        <v>0.04651495575386415</v>
       </c>
       <c r="G25" s="13" t="n">
-        <v>3810.447435237837</v>
-      </c>
-      <c r="H25" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+        <v>863.6538266115568</v>
+      </c>
+      <c r="H25" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="I25" s="10" t="inlineStr">
@@ -22020,27 +22020,27 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Jamaica</t>
         </is>
       </c>
       <c r="C26" s="12" t="n">
-        <v>7537588</v>
+        <v>7605637</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E26" s="13" t="n">
-        <v>6973.96</v>
+        <v>28980.88</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>0.04708548676313962</v>
+        <v>0.06492158382000086</v>
       </c>
       <c r="G26" s="13" t="n">
-        <v>925.224355589613</v>
-      </c>
-      <c r="H26" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+        <v>3810.447435237837</v>
+      </c>
+      <c r="H26" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
       <c r="I26" s="10" t="inlineStr">
@@ -22055,32 +22055,32 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="C27" s="12" t="n">
-        <v>6973925</v>
+        <v>7486418</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="E27" s="13" t="n">
-        <v>-938.1599999999999</v>
+        <v>2966.79</v>
       </c>
       <c r="F27" s="14" t="n">
-        <v>0.02549611588882874</v>
+        <v>0.101378389504834</v>
       </c>
       <c r="G27" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="I27" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+        <v>396.2896541443451</v>
+      </c>
+      <c r="H27" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="I27" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -22090,32 +22090,32 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Bélgica</t>
         </is>
       </c>
       <c r="C28" s="12" t="n">
-        <v>6949750</v>
+        <v>7245680</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E28" s="13" t="n">
-        <v>3190.66</v>
+        <v>-938.1599999999999</v>
       </c>
       <c r="F28" s="14" t="n">
-        <v>0.1037786970754344</v>
+        <v>0.02530266310408409</v>
       </c>
       <c r="G28" s="13" t="n">
-        <v>459.1042843267743</v>
-      </c>
-      <c r="H28" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
-        </is>
-      </c>
-      <c r="I28" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+        <v>0</v>
+      </c>
+      <c r="H28" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I28" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -22125,32 +22125,32 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Costa Rica</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="C29" s="12" t="n">
-        <v>6847304</v>
+        <v>7154056</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="E29" s="13" t="n">
-        <v>3327.9</v>
+        <v>237</v>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0.02402858117589054</v>
+        <v>0.03950793787468256</v>
       </c>
       <c r="G29" s="13" t="n">
-        <v>486.0161021038353</v>
-      </c>
-      <c r="H29" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="I29" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+        <v>33.12806050162313</v>
+      </c>
+      <c r="H29" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I29" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -22160,32 +22160,32 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Costa Rica</t>
         </is>
       </c>
       <c r="C30" s="12" t="n">
-        <v>6793589</v>
+        <v>7110463</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="E30" s="13" t="n">
-        <v>237</v>
+        <v>3327.9</v>
       </c>
       <c r="F30" s="14" t="n">
-        <v>0.03548889990254047</v>
+        <v>0.02320481802661796</v>
       </c>
       <c r="G30" s="13" t="n">
-        <v>34.88583133304061</v>
-      </c>
-      <c r="H30" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
-        </is>
-      </c>
-      <c r="I30" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+        <v>468.0285939185675</v>
+      </c>
+      <c r="H30" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I30" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -22199,7 +22199,7 @@
         </is>
       </c>
       <c r="C31" s="12" t="n">
-        <v>6083816</v>
+        <v>6175804</v>
       </c>
       <c r="D31" s="5" t="n">
         <v>15</v>
@@ -22208,10 +22208,10 @@
         <v>3121.49</v>
       </c>
       <c r="F31" s="14" t="n">
-        <v>0.02347506893699612</v>
+        <v>0.02312913427952053</v>
       </c>
       <c r="G31" s="13" t="n">
-        <v>513.080934729124</v>
+        <v>505.4386441020473</v>
       </c>
       <c r="H31" s="10" t="inlineStr">
         <is>
@@ -22234,7 +22234,7 @@
         </is>
       </c>
       <c r="C32" s="12" t="n">
-        <v>4877688</v>
+        <v>5053637</v>
       </c>
       <c r="D32" s="5" t="n">
         <v>16</v>
@@ -22243,10 +22243,10 @@
         <v>3581.11</v>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0.04230077856558271</v>
+        <v>0.04260238715206494</v>
       </c>
       <c r="G32" s="13" t="n">
-        <v>734.1818500896326</v>
+        <v>708.6203460992548</v>
       </c>
       <c r="H32" s="9" t="inlineStr">
         <is>
@@ -22269,28 +22269,28 @@
         </is>
       </c>
       <c r="C33" s="12" t="n">
-        <v>4342993</v>
+        <v>4531067</v>
       </c>
       <c r="D33" s="5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E33" s="13" t="n">
-        <v>2693.73</v>
+        <v>3511.52</v>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0.06760936524650166</v>
+        <v>0.06646293246160341</v>
       </c>
       <c r="G33" s="13" t="n">
-        <v>620.2473731825035</v>
+        <v>774.9874367339966</v>
       </c>
       <c r="H33" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I33" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I33" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -22300,32 +22300,32 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>Curazao</t>
+          <t>Egipto</t>
         </is>
       </c>
       <c r="C34" s="12" t="n">
-        <v>3782149</v>
+        <v>3878178</v>
       </c>
       <c r="D34" s="5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E34" s="13" t="n">
-        <v>-643.8600000000001</v>
+        <v>1871.01</v>
       </c>
       <c r="F34" s="14" t="n">
-        <v>0.01635419440111957</v>
+        <v>0.07076776775073243</v>
       </c>
       <c r="G34" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="I34" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+        <v>482.4456226609506</v>
+      </c>
+      <c r="H34" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="I34" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -22335,32 +22335,32 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>Curazao</t>
         </is>
       </c>
       <c r="C35" s="12" t="n">
-        <v>3597252</v>
+        <v>3877024</v>
       </c>
       <c r="D35" s="5" t="n">
-        <v>67</v>
+        <v>8</v>
       </c>
       <c r="E35" s="13" t="n">
-        <v>17128.09</v>
+        <v>-643.8600000000001</v>
       </c>
       <c r="F35" s="14" t="n">
-        <v>0.04991615822299911</v>
+        <v>0.03014322325577556</v>
       </c>
       <c r="G35" s="13" t="n">
-        <v>4761.43734161521</v>
+        <v>0</v>
       </c>
       <c r="H35" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I35" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I35" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -22370,32 +22370,32 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>Egipto</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="C36" s="12" t="n">
-        <v>3337218</v>
+        <v>3785048</v>
       </c>
       <c r="D36" s="5" t="n">
-        <v>4</v>
+        <v>77</v>
       </c>
       <c r="E36" s="13" t="n">
-        <v>1453.62</v>
+        <v>17222.59</v>
       </c>
       <c r="F36" s="14" t="n">
-        <v>0.06893855900333751</v>
+        <v>0.0490976600560944</v>
       </c>
       <c r="G36" s="13" t="n">
-        <v>435.5783769594914</v>
-      </c>
-      <c r="H36" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
-        </is>
-      </c>
-      <c r="I36" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+        <v>4550.164225130037</v>
+      </c>
+      <c r="H36" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I36" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -22409,7 +22409,7 @@
         </is>
       </c>
       <c r="C37" s="12" t="n">
-        <v>3261871</v>
+        <v>3350779</v>
       </c>
       <c r="D37" s="5" t="n">
         <v>93</v>
@@ -22418,10 +22418,10 @@
         <v>10059.92</v>
       </c>
       <c r="F37" s="14" t="n">
-        <v>0.04390792891564381</v>
+        <v>0.042904948371707</v>
       </c>
       <c r="G37" s="13" t="n">
-        <v>3084.09498720213</v>
+        <v>3002.263055844626</v>
       </c>
       <c r="H37" s="9" t="inlineStr">
         <is>
@@ -22444,28 +22444,28 @@
         </is>
       </c>
       <c r="C38" s="12" t="n">
-        <v>2375890</v>
+        <v>3089388</v>
       </c>
       <c r="D38" s="5" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E38" s="13" t="n">
-        <v>673.2299999999996</v>
+        <v>358.3599999999999</v>
       </c>
       <c r="F38" s="14" t="n">
-        <v>0.06991443206545758</v>
+        <v>0.05482089009214771</v>
       </c>
       <c r="G38" s="13" t="n">
-        <v>283.359078071796</v>
+        <v>115.9970842121481</v>
       </c>
       <c r="H38" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I38" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="I38" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -22479,7 +22479,7 @@
         </is>
       </c>
       <c r="C39" s="12" t="n">
-        <v>2330706</v>
+        <v>2426303</v>
       </c>
       <c r="D39" s="5" t="n">
         <v>2</v>
@@ -22488,10 +22488,10 @@
         <v>443.03</v>
       </c>
       <c r="F39" s="14" t="n">
-        <v>0.1384267256359232</v>
+        <v>0.1540941094331582</v>
       </c>
       <c r="G39" s="13" t="n">
-        <v>190.0840346229855</v>
+        <v>182.5946718113937</v>
       </c>
       <c r="H39" s="8" t="inlineStr">
         <is>
@@ -22510,27 +22510,27 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>Grecia</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C40" s="12" t="n">
-        <v>2133766</v>
+        <v>2136634</v>
       </c>
       <c r="D40" s="5" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="E40" s="13" t="n">
-        <v>3613.669999999999</v>
+        <v>12117</v>
       </c>
       <c r="F40" s="14" t="n">
-        <v>0.1448823348014731</v>
+        <v>0.02083276780206624</v>
       </c>
       <c r="G40" s="13" t="n">
-        <v>1693.564336483006</v>
-      </c>
-      <c r="H40" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+        <v>5671.069542092843</v>
+      </c>
+      <c r="H40" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="I40" s="10" t="inlineStr">
@@ -22545,27 +22545,27 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>Grecia</t>
         </is>
       </c>
       <c r="C41" s="12" t="n">
-        <v>1800937</v>
+        <v>2133766</v>
       </c>
       <c r="D41" s="5" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E41" s="13" t="n">
-        <v>3356.8</v>
+        <v>3613.669999999999</v>
       </c>
       <c r="F41" s="14" t="n">
-        <v>0.03487962099729196</v>
+        <v>0.1448823348014731</v>
       </c>
       <c r="G41" s="13" t="n">
-        <v>1863.918615698384</v>
-      </c>
-      <c r="H41" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+        <v>1693.564336483006</v>
+      </c>
+      <c r="H41" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
       <c r="I41" s="10" t="inlineStr">
@@ -22580,32 +22580,32 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>Bahamas</t>
+          <t>Tailandia</t>
         </is>
       </c>
       <c r="C42" s="12" t="n">
-        <v>1759492</v>
+        <v>2129962</v>
       </c>
       <c r="D42" s="5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E42" s="13" t="n">
-        <v>3858.700000000001</v>
+        <v>-9.230000000000018</v>
       </c>
       <c r="F42" s="14" t="n">
-        <v>0.2994114210237955</v>
+        <v>0.2486495064231193</v>
       </c>
       <c r="G42" s="13" t="n">
-        <v>2193.076183352923</v>
+        <v>0</v>
       </c>
       <c r="H42" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
       </c>
-      <c r="I42" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I42" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -22615,27 +22615,27 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Irlanda</t>
         </is>
       </c>
       <c r="C43" s="12" t="n">
-        <v>1698772</v>
+        <v>1800937</v>
       </c>
       <c r="D43" s="5" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="E43" s="13" t="n">
-        <v>12117</v>
+        <v>3356.8</v>
       </c>
       <c r="F43" s="14" t="n">
-        <v>0.02436642468795106</v>
+        <v>0.03487962099729196</v>
       </c>
       <c r="G43" s="13" t="n">
-        <v>7132.79945749047</v>
-      </c>
-      <c r="H43" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+        <v>1863.918615698384</v>
+      </c>
+      <c r="H43" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="I43" s="10" t="inlineStr">
@@ -22650,32 +22650,32 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>El Salvador</t>
+          <t>Bahamas</t>
         </is>
       </c>
       <c r="C44" s="12" t="n">
-        <v>1570437</v>
+        <v>1759492</v>
       </c>
       <c r="D44" s="5" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E44" s="13" t="n">
-        <v>796.8399999999999</v>
+        <v>3858.700000000001</v>
       </c>
       <c r="F44" s="14" t="n">
-        <v>0.00815123433795816</v>
+        <v>0.2994114210237955</v>
       </c>
       <c r="G44" s="13" t="n">
-        <v>507.4001695069588</v>
-      </c>
-      <c r="H44" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="I44" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+        <v>2193.076183352923</v>
+      </c>
+      <c r="H44" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+      <c r="I44" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -22689,7 +22689,7 @@
         </is>
       </c>
       <c r="C45" s="12" t="n">
-        <v>1539780</v>
+        <v>1629650</v>
       </c>
       <c r="D45" s="5" t="n">
         <v>11</v>
@@ -22698,10 +22698,10 @@
         <v>1734.1</v>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0.01891698814116302</v>
+        <v>0.01975638940876875</v>
       </c>
       <c r="G45" s="13" t="n">
-        <v>1126.199846731351</v>
+        <v>1064.093517012855</v>
       </c>
       <c r="H45" s="10" t="inlineStr">
         <is>
@@ -22720,32 +22720,32 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>Tailandia</t>
+          <t>El Salvador</t>
         </is>
       </c>
       <c r="C46" s="12" t="n">
-        <v>1503258</v>
+        <v>1570437</v>
       </c>
       <c r="D46" s="5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E46" s="13" t="n">
-        <v>-9.230000000000018</v>
+        <v>796.8399999999999</v>
       </c>
       <c r="F46" s="14" t="n">
-        <v>0.2502604343366209</v>
+        <v>0.00815123433795816</v>
       </c>
       <c r="G46" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
-        </is>
-      </c>
-      <c r="I46" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+        <v>507.4001695069588</v>
+      </c>
+      <c r="H46" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I46" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -22759,7 +22759,7 @@
         </is>
       </c>
       <c r="C47" s="12" t="n">
-        <v>1257378</v>
+        <v>1341136</v>
       </c>
       <c r="D47" s="5" t="n">
         <v>32</v>
@@ -22768,7 +22768,7 @@
         <v>-967.53</v>
       </c>
       <c r="F47" s="14" t="n">
-        <v>0.008588507195131457</v>
+        <v>0.008493545770153065</v>
       </c>
       <c r="G47" s="13" t="n">
         <v>0</v>
@@ -22794,7 +22794,7 @@
         </is>
       </c>
       <c r="C48" s="12" t="n">
-        <v>1221421</v>
+        <v>1308033</v>
       </c>
       <c r="D48" s="5" t="n">
         <v>1</v>
@@ -22803,10 +22803,10 @@
         <v>120.42</v>
       </c>
       <c r="F48" s="14" t="n">
-        <v>0.01289645421193839</v>
+        <v>0.01209678960699004</v>
       </c>
       <c r="G48" s="13" t="n">
-        <v>98.59008482742642</v>
+        <v>92.06189752093411</v>
       </c>
       <c r="H48" s="10" t="inlineStr">
         <is>
@@ -22864,7 +22864,7 @@
         </is>
       </c>
       <c r="C50" s="12" t="n">
-        <v>1077535</v>
+        <v>1173036</v>
       </c>
       <c r="D50" s="5" t="n">
         <v>6</v>
@@ -22873,7 +22873,7 @@
         <v>-82.58999999999989</v>
       </c>
       <c r="F50" s="14" t="n">
-        <v>0.0681657672372591</v>
+        <v>0.06291367016869047</v>
       </c>
       <c r="G50" s="13" t="n">
         <v>0</v>
@@ -22969,7 +22969,7 @@
         </is>
       </c>
       <c r="C53" s="12" t="n">
-        <v>733946</v>
+        <v>827367</v>
       </c>
       <c r="D53" s="5" t="n">
         <v>3</v>
@@ -22978,7 +22978,7 @@
         <v>-53.63000000000001</v>
       </c>
       <c r="F53" s="14" t="n">
-        <v>0.05183760113141839</v>
+        <v>0.05001287215951325</v>
       </c>
       <c r="G53" s="13" t="n">
         <v>0</v>
@@ -23000,32 +23000,32 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>Islas Caimán</t>
+          <t>Finlandia</t>
         </is>
       </c>
       <c r="C54" s="12" t="n">
-        <v>664505</v>
+        <v>683848</v>
       </c>
       <c r="D54" s="5" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E54" s="13" t="n">
-        <v>-228.8699999999999</v>
+        <v>1564.87</v>
       </c>
       <c r="F54" s="14" t="n">
-        <v>0.001408567279403466</v>
+        <v>0.01392122225991741</v>
       </c>
       <c r="G54" s="13" t="n">
-        <v>0</v>
+        <v>2288.330155239176</v>
       </c>
       <c r="H54" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I54" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I54" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -23035,20 +23035,20 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>Mónaco</t>
+          <t>Islas Caimán</t>
         </is>
       </c>
       <c r="C55" s="12" t="n">
-        <v>623884</v>
+        <v>664505</v>
       </c>
       <c r="D55" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E55" s="13" t="n">
-        <v>0</v>
+        <v>-228.8699999999999</v>
       </c>
       <c r="F55" s="14" t="n">
-        <v>0.008884664456854159</v>
+        <v>0.001408567279403466</v>
       </c>
       <c r="G55" s="13" t="n">
         <v>0</v>
@@ -23058,9 +23058,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I55" s="11" t="inlineStr">
-        <is>
-          <t>Sin Conversión</t>
+      <c r="I55" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -23070,32 +23070,32 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>Honduras</t>
+          <t>Mónaco</t>
         </is>
       </c>
       <c r="C56" s="12" t="n">
-        <v>540899</v>
+        <v>623884</v>
       </c>
       <c r="D56" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E56" s="13" t="n">
-        <v>1549.48</v>
+        <v>0</v>
       </c>
       <c r="F56" s="14" t="n">
-        <v>0.002566098291917715</v>
+        <v>0.008884664456854159</v>
       </c>
       <c r="G56" s="13" t="n">
-        <v>2864.638315101341</v>
+        <v>0</v>
       </c>
       <c r="H56" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I56" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I56" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -23105,32 +23105,32 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>Anguila</t>
+          <t>Honduras</t>
         </is>
       </c>
       <c r="C57" s="12" t="n">
-        <v>540477</v>
+        <v>540899</v>
       </c>
       <c r="D57" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E57" s="13" t="n">
-        <v>0</v>
+        <v>1549.48</v>
       </c>
       <c r="F57" s="14" t="n">
-        <v>0.0003182374088074053</v>
+        <v>0.002566098291917715</v>
       </c>
       <c r="G57" s="13" t="n">
-        <v>0</v>
+        <v>2864.638315101341</v>
       </c>
       <c r="H57" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I57" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I57" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -23140,32 +23140,32 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>Finlandia</t>
+          <t>Anguila</t>
         </is>
       </c>
       <c r="C58" s="12" t="n">
-        <v>498728</v>
+        <v>540477</v>
       </c>
       <c r="D58" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E58" s="13" t="n">
-        <v>1182.9</v>
+        <v>0</v>
       </c>
       <c r="F58" s="14" t="n">
-        <v>0.01639170048603647</v>
+        <v>0.0003182374088074053</v>
       </c>
       <c r="G58" s="13" t="n">
-        <v>2371.833945557498</v>
+        <v>0</v>
       </c>
       <c r="H58" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I58" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I58" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -23175,23 +23175,23 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>Camboya</t>
+          <t>India</t>
         </is>
       </c>
       <c r="C59" s="12" t="n">
-        <v>498079</v>
+        <v>510183</v>
       </c>
       <c r="D59" s="5" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="E59" s="13" t="n">
-        <v>422.6</v>
+        <v>2888.42</v>
       </c>
       <c r="F59" s="14" t="n">
-        <v>0.002240608417540189</v>
+        <v>0.005566630013152144</v>
       </c>
       <c r="G59" s="13" t="n">
-        <v>848.4597824843048</v>
+        <v>5661.537134714406</v>
       </c>
       <c r="H59" s="10" t="inlineStr">
         <is>
@@ -23210,32 +23210,32 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Montenegro</t>
         </is>
       </c>
       <c r="C60" s="12" t="n">
-        <v>470966</v>
+        <v>501738</v>
       </c>
       <c r="D60" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E60" s="13" t="n">
-        <v>0</v>
+        <v>-473.8299999999999</v>
       </c>
       <c r="F60" s="14" t="n">
-        <v>0.0146762186654663</v>
+        <v>0.03206255057420407</v>
       </c>
       <c r="G60" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H60" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="I60" s="11" t="inlineStr">
-        <is>
-          <t>Sin Conversión</t>
+      <c r="H60" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I60" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -23245,23 +23245,23 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>Mauricio</t>
+          <t>Camboya</t>
         </is>
       </c>
       <c r="C61" s="12" t="n">
-        <v>414080</v>
+        <v>498079</v>
       </c>
       <c r="D61" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E61" s="13" t="n">
-        <v>1896.66</v>
+        <v>422.6</v>
       </c>
       <c r="F61" s="14" t="n">
-        <v>0.02565929289026275</v>
+        <v>0.002240608417540189</v>
       </c>
       <c r="G61" s="13" t="n">
-        <v>4580.419242658423</v>
+        <v>848.4597824843048</v>
       </c>
       <c r="H61" s="10" t="inlineStr">
         <is>
@@ -23280,27 +23280,27 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>Kazajistán</t>
+          <t>Rumania</t>
         </is>
       </c>
       <c r="C62" s="12" t="n">
-        <v>398497</v>
+        <v>491349</v>
       </c>
       <c r="D62" s="5" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E62" s="13" t="n">
-        <v>1218.38</v>
+        <v>4477.35</v>
       </c>
       <c r="F62" s="14" t="n">
-        <v>0.486583336888358</v>
+        <v>0.0300580646343027</v>
       </c>
       <c r="G62" s="13" t="n">
-        <v>3057.438324504325</v>
-      </c>
-      <c r="H62" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+        <v>9112.362088861481</v>
+      </c>
+      <c r="H62" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="I62" s="10" t="inlineStr">
@@ -23315,27 +23315,27 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>Rumania</t>
+          <t>Kazajistán</t>
         </is>
       </c>
       <c r="C63" s="12" t="n">
-        <v>397830</v>
+        <v>490377</v>
       </c>
       <c r="D63" s="5" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E63" s="13" t="n">
-        <v>4477.35</v>
+        <v>1218.38</v>
       </c>
       <c r="F63" s="14" t="n">
-        <v>0.03441168338234924</v>
+        <v>0.4048109923589401</v>
       </c>
       <c r="G63" s="13" t="n">
-        <v>11254.43028429229</v>
-      </c>
-      <c r="H63" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+        <v>2484.578191880941</v>
+      </c>
+      <c r="H63" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
       <c r="I63" s="10" t="inlineStr">
@@ -23350,32 +23350,32 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="C64" s="12" t="n">
-        <v>330191</v>
+        <v>470966</v>
       </c>
       <c r="D64" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E64" s="13" t="n">
-        <v>679.1099999999999</v>
+        <v>0</v>
       </c>
       <c r="F64" s="14" t="n">
-        <v>0.006871780272630084</v>
+        <v>0.0146762186654663</v>
       </c>
       <c r="G64" s="13" t="n">
-        <v>2056.718687062942</v>
+        <v>0</v>
       </c>
       <c r="H64" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I64" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I64" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -23385,32 +23385,32 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>Montenegro</t>
+          <t>Maldivas</t>
         </is>
       </c>
       <c r="C65" s="12" t="n">
-        <v>324622</v>
+        <v>415226</v>
       </c>
       <c r="D65" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E65" s="13" t="n">
-        <v>-473.8299999999999</v>
+        <v>0</v>
       </c>
       <c r="F65" s="14" t="n">
-        <v>0.04145744897141906</v>
+        <v>0.02131128590213522</v>
       </c>
       <c r="G65" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H65" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
-        </is>
-      </c>
-      <c r="I65" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="H65" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I65" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -23420,23 +23420,23 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>San Cristóbal y Nieves</t>
+          <t>Mauricio</t>
         </is>
       </c>
       <c r="C66" s="12" t="n">
-        <v>299323</v>
+        <v>414080</v>
       </c>
       <c r="D66" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E66" s="13" t="n">
-        <v>706.23</v>
+        <v>1896.66</v>
       </c>
       <c r="F66" s="14" t="n">
-        <v>0.0004877673950882491</v>
+        <v>0.02565929289026275</v>
       </c>
       <c r="G66" s="13" t="n">
-        <v>2359.424434473796</v>
+        <v>4580.419242658423</v>
       </c>
       <c r="H66" s="10" t="inlineStr">
         <is>
@@ -23455,27 +23455,27 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>Guyana</t>
+          <t>Chipre</t>
         </is>
       </c>
       <c r="C67" s="12" t="n">
-        <v>296613</v>
+        <v>333610</v>
       </c>
       <c r="D67" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E67" s="13" t="n">
-        <v>1061.78</v>
+        <v>600.5599999999999</v>
       </c>
       <c r="F67" s="14" t="n">
-        <v>0.001389015316253839</v>
+        <v>0.04029855220167261</v>
       </c>
       <c r="G67" s="13" t="n">
-        <v>3579.681268184469</v>
-      </c>
-      <c r="H67" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+        <v>1800.185845748029</v>
+      </c>
+      <c r="H67" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="I67" s="10" t="inlineStr">
@@ -23490,32 +23490,32 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Croacia (Hrvatska)</t>
         </is>
       </c>
       <c r="C68" s="12" t="n">
-        <v>258226</v>
+        <v>333038</v>
       </c>
       <c r="D68" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E68" s="13" t="n">
-        <v>0</v>
+        <v>133.59</v>
       </c>
       <c r="F68" s="14" t="n">
-        <v>0.02011803613888609</v>
+        <v>0.04405203009866743</v>
       </c>
       <c r="G68" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H68" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="I68" s="11" t="inlineStr">
-        <is>
-          <t>Sin Conversión</t>
+        <v>401.1253971018322</v>
+      </c>
+      <c r="H68" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I68" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -23525,11 +23525,11 @@
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>Belice</t>
+          <t>Åland</t>
         </is>
       </c>
       <c r="C69" s="12" t="n">
-        <v>257825</v>
+        <v>316304</v>
       </c>
       <c r="D69" s="5" t="n">
         <v>0</v>
@@ -23538,7 +23538,7 @@
         <v>0</v>
       </c>
       <c r="F69" s="14" t="n">
-        <v>0.0005430039755648211</v>
+        <v>0.01509939804744802</v>
       </c>
       <c r="G69" s="13" t="n">
         <v>0</v>
@@ -23560,23 +23560,23 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>Serbia</t>
+          <t>San Cristóbal y Nieves</t>
         </is>
       </c>
       <c r="C70" s="12" t="n">
-        <v>246080</v>
+        <v>299323</v>
       </c>
       <c r="D70" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E70" s="13" t="n">
-        <v>445.04</v>
+        <v>706.23</v>
       </c>
       <c r="F70" s="14" t="n">
-        <v>0.01864840702210663</v>
+        <v>0.0004877673950882491</v>
       </c>
       <c r="G70" s="13" t="n">
-        <v>1808.51755526658</v>
+        <v>2359.424434473796</v>
       </c>
       <c r="H70" s="10" t="inlineStr">
         <is>
@@ -23595,32 +23595,32 @@
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>Maldivas</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="C71" s="12" t="n">
-        <v>229677</v>
+        <v>296613</v>
       </c>
       <c r="D71" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E71" s="13" t="n">
-        <v>0</v>
+        <v>1061.78</v>
       </c>
       <c r="F71" s="14" t="n">
-        <v>0.02562729398241879</v>
+        <v>0.001389015316253839</v>
       </c>
       <c r="G71" s="13" t="n">
-        <v>0</v>
+        <v>3579.681268184469</v>
       </c>
       <c r="H71" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I71" s="11" t="inlineStr">
-        <is>
-          <t>Sin Conversión</t>
+      <c r="I71" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -23630,11 +23630,11 @@
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>Lituania</t>
+          <t>Estonia</t>
         </is>
       </c>
       <c r="C72" s="12" t="n">
-        <v>226326</v>
+        <v>292404</v>
       </c>
       <c r="D72" s="5" t="n">
         <v>0</v>
@@ -23643,14 +23643,14 @@
         <v>0</v>
       </c>
       <c r="F72" s="14" t="n">
-        <v>0.1311647800075997</v>
+        <v>0.02158315207726296</v>
       </c>
       <c r="G72" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H72" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="H72" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="I72" s="11" t="inlineStr">
@@ -23665,11 +23665,11 @@
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>Åland</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="C73" s="12" t="n">
-        <v>221003</v>
+        <v>258226</v>
       </c>
       <c r="D73" s="5" t="n">
         <v>0</v>
@@ -23678,7 +23678,7 @@
         <v>0</v>
       </c>
       <c r="F73" s="14" t="n">
-        <v>0.008945579924254422</v>
+        <v>0.02011803613888609</v>
       </c>
       <c r="G73" s="13" t="n">
         <v>0</v>
@@ -23700,32 +23700,32 @@
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>Bangladés</t>
+          <t>Belice</t>
         </is>
       </c>
       <c r="C74" s="12" t="n">
-        <v>207785</v>
+        <v>257825</v>
       </c>
       <c r="D74" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E74" s="13" t="n">
-        <v>843.66</v>
+        <v>0</v>
       </c>
       <c r="F74" s="14" t="n">
-        <v>0.001227230069543038</v>
+        <v>0.0005430039755648211</v>
       </c>
       <c r="G74" s="13" t="n">
-        <v>4060.254590081093</v>
+        <v>0</v>
       </c>
       <c r="H74" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I74" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I74" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -23735,27 +23735,27 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>Serbia</t>
         </is>
       </c>
       <c r="C75" s="12" t="n">
-        <v>165829</v>
+        <v>246080</v>
       </c>
       <c r="D75" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E75" s="13" t="n">
-        <v>600.5599999999999</v>
+        <v>445.04</v>
       </c>
       <c r="F75" s="14" t="n">
-        <v>0.04645146506340869</v>
+        <v>0.01864840702210663</v>
       </c>
       <c r="G75" s="13" t="n">
-        <v>3621.56197046355</v>
-      </c>
-      <c r="H75" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+        <v>1808.51755526658</v>
+      </c>
+      <c r="H75" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="I75" s="10" t="inlineStr">
@@ -23770,11 +23770,11 @@
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>Croacia (Hrvatska)</t>
+          <t>Lituania</t>
         </is>
       </c>
       <c r="C76" s="12" t="n">
-        <v>163465</v>
+        <v>226326</v>
       </c>
       <c r="D76" s="5" t="n">
         <v>0</v>
@@ -23783,7 +23783,7 @@
         <v>0</v>
       </c>
       <c r="F76" s="14" t="n">
-        <v>0.0775395344569174</v>
+        <v>0.1311647800075997</v>
       </c>
       <c r="G76" s="13" t="n">
         <v>0</v>
@@ -23805,32 +23805,32 @@
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>Eslovenia</t>
+          <t>Bangladés</t>
         </is>
       </c>
       <c r="C77" s="12" t="n">
-        <v>154785</v>
+        <v>207785</v>
       </c>
       <c r="D77" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E77" s="13" t="n">
-        <v>-61.06999999999994</v>
+        <v>843.66</v>
       </c>
       <c r="F77" s="14" t="n">
-        <v>0.02839422424653552</v>
+        <v>0.001227230069543038</v>
       </c>
       <c r="G77" s="13" t="n">
-        <v>0</v>
+        <v>4060.254590081093</v>
       </c>
       <c r="H77" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I77" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I77" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -23840,32 +23840,32 @@
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>Guam</t>
+          <t>Sri Lanka</t>
         </is>
       </c>
       <c r="C78" s="12" t="n">
-        <v>152464</v>
+        <v>186790</v>
       </c>
       <c r="D78" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E78" s="13" t="n">
-        <v>9182.690000000001</v>
+        <v>0</v>
       </c>
       <c r="F78" s="14" t="n">
-        <v>0.03260441809213978</v>
+        <v>0.01077145457465603</v>
       </c>
       <c r="G78" s="13" t="n">
-        <v>60228.57854969042</v>
-      </c>
-      <c r="H78" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
-        </is>
-      </c>
-      <c r="I78" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+        <v>0</v>
+      </c>
+      <c r="H78" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I78" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -23875,32 +23875,32 @@
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>Nicaragua</t>
+          <t>Eslovenia</t>
         </is>
       </c>
       <c r="C79" s="12" t="n">
-        <v>148396</v>
+        <v>154785</v>
       </c>
       <c r="D79" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E79" s="13" t="n">
-        <v>67.55</v>
+        <v>-61.06999999999994</v>
       </c>
       <c r="F79" s="14" t="n">
-        <v>0.01487236852745357</v>
+        <v>0.02839422424653552</v>
       </c>
       <c r="G79" s="13" t="n">
-        <v>455.2009488126365</v>
+        <v>0</v>
       </c>
       <c r="H79" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I79" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+      <c r="I79" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -23910,32 +23910,32 @@
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>Marruecos</t>
+          <t>Guam</t>
         </is>
       </c>
       <c r="C80" s="12" t="n">
-        <v>127068</v>
+        <v>152464</v>
       </c>
       <c r="D80" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E80" s="13" t="n">
-        <v>0</v>
+        <v>9182.690000000001</v>
       </c>
       <c r="F80" s="14" t="n">
-        <v>0.1761655176755753</v>
+        <v>0.03260441809213978</v>
       </c>
       <c r="G80" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H80" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
-        </is>
-      </c>
-      <c r="I80" s="11" t="inlineStr">
-        <is>
-          <t>Sin Conversión</t>
+        <v>60228.57854969042</v>
+      </c>
+      <c r="H80" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I80" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -23945,32 +23945,32 @@
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>Malasia</t>
+          <t>Nicaragua</t>
         </is>
       </c>
       <c r="C81" s="12" t="n">
-        <v>125316</v>
+        <v>148396</v>
       </c>
       <c r="D81" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E81" s="13" t="n">
-        <v>0</v>
+        <v>67.55</v>
       </c>
       <c r="F81" s="14" t="n">
-        <v>0.2818395097194293</v>
+        <v>0.01487236852745357</v>
       </c>
       <c r="G81" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H81" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
-        </is>
-      </c>
-      <c r="I81" s="11" t="inlineStr">
-        <is>
-          <t>Sin Conversión</t>
+        <v>455.2009488126365</v>
+      </c>
+      <c r="H81" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I81" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -23980,11 +23980,11 @@
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>Eslovaquia</t>
+          <t>Marruecos</t>
         </is>
       </c>
       <c r="C82" s="12" t="n">
-        <v>124380</v>
+        <v>127068</v>
       </c>
       <c r="D82" s="5" t="n">
         <v>0</v>
@@ -23993,14 +23993,14 @@
         <v>0</v>
       </c>
       <c r="F82" s="14" t="n">
-        <v>0.01398134748351825</v>
+        <v>0.1761655176755753</v>
       </c>
       <c r="G82" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H82" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="H82" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
       <c r="I82" s="11" t="inlineStr">
@@ -24015,11 +24015,11 @@
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>Laos</t>
+          <t>Malasia</t>
         </is>
       </c>
       <c r="C83" s="12" t="n">
-        <v>117283</v>
+        <v>125316</v>
       </c>
       <c r="D83" s="5" t="n">
         <v>0</v>
@@ -24028,14 +24028,14 @@
         <v>0</v>
       </c>
       <c r="F83" s="14" t="n">
-        <v>0.004851513007000162</v>
+        <v>0.2818395097194293</v>
       </c>
       <c r="G83" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H83" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="H83" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
       <c r="I83" s="11" t="inlineStr">
@@ -24050,32 +24050,32 @@
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>Kenia</t>
+          <t>Eslovaquia</t>
         </is>
       </c>
       <c r="C84" s="12" t="n">
-        <v>112615</v>
+        <v>124380</v>
       </c>
       <c r="D84" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E84" s="13" t="n">
-        <v>139.06</v>
+        <v>0</v>
       </c>
       <c r="F84" s="14" t="n">
-        <v>0.008462460595835369</v>
+        <v>0.01398134748351825</v>
       </c>
       <c r="G84" s="13" t="n">
-        <v>1234.826621675621</v>
+        <v>0</v>
       </c>
       <c r="H84" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I84" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I84" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -24085,11 +24085,11 @@
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>Armenia</t>
+          <t>Laos</t>
         </is>
       </c>
       <c r="C85" s="12" t="n">
-        <v>108626</v>
+        <v>117283</v>
       </c>
       <c r="D85" s="5" t="n">
         <v>0</v>
@@ -24098,14 +24098,14 @@
         <v>0</v>
       </c>
       <c r="F85" s="14" t="n">
-        <v>0.4896433634673098</v>
+        <v>0.004851513007000162</v>
       </c>
       <c r="G85" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H85" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="H85" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="I85" s="11" t="inlineStr">
@@ -24120,32 +24120,32 @@
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>Estonia</t>
+          <t>Kenia</t>
         </is>
       </c>
       <c r="C86" s="12" t="n">
-        <v>107847</v>
+        <v>112615</v>
       </c>
       <c r="D86" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E86" s="13" t="n">
-        <v>0</v>
+        <v>139.06</v>
       </c>
       <c r="F86" s="14" t="n">
-        <v>0.03359388763711554</v>
+        <v>0.008462460595835369</v>
       </c>
       <c r="G86" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H86" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
-        </is>
-      </c>
-      <c r="I86" s="11" t="inlineStr">
-        <is>
-          <t>Sin Conversión</t>
+        <v>1234.826621675621</v>
+      </c>
+      <c r="H86" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I86" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -24155,11 +24155,11 @@
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>Kirguistán</t>
+          <t>Armenia</t>
         </is>
       </c>
       <c r="C87" s="12" t="n">
-        <v>105233</v>
+        <v>108626</v>
       </c>
       <c r="D87" s="5" t="n">
         <v>0</v>
@@ -24168,14 +24168,14 @@
         <v>0</v>
       </c>
       <c r="F87" s="14" t="n">
-        <v>0.01887240694458963</v>
+        <v>0.4896433634673098</v>
       </c>
       <c r="G87" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H87" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="H87" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
       <c r="I87" s="11" t="inlineStr">
@@ -24190,11 +24190,11 @@
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>Azerbaiyán</t>
+          <t>Kirguistán</t>
         </is>
       </c>
       <c r="C88" s="12" t="n">
-        <v>101794</v>
+        <v>105233</v>
       </c>
       <c r="D88" s="5" t="n">
         <v>0</v>
@@ -24203,14 +24203,14 @@
         <v>0</v>
       </c>
       <c r="F88" s="14" t="n">
-        <v>0.2109849303495294</v>
+        <v>0.01887240694458963</v>
       </c>
       <c r="G88" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H88" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="H88" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="I88" s="11" t="inlineStr">
@@ -24225,11 +24225,11 @@
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>Sri Lanka</t>
+          <t>Azerbaiyán</t>
         </is>
       </c>
       <c r="C89" s="12" t="n">
-        <v>101504</v>
+        <v>101794</v>
       </c>
       <c r="D89" s="5" t="n">
         <v>0</v>
@@ -24238,14 +24238,14 @@
         <v>0</v>
       </c>
       <c r="F89" s="14" t="n">
-        <v>0.01508314943253468</v>
+        <v>0.2109849303495294</v>
       </c>
       <c r="G89" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H89" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="H89" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
       <c r="I89" s="11" t="inlineStr">
@@ -24319,6 +24319,111 @@
         </is>
       </c>
       <c r="I91" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="5" t="n">
+        <v>87</v>
+      </c>
+      <c r="B92" s="5" t="inlineStr">
+        <is>
+          <t>Suecia</t>
+        </is>
+      </c>
+      <c r="C92" s="12" t="n">
+        <v>94208</v>
+      </c>
+      <c r="D92" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E92" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" s="14" t="n">
+        <v>0.06339164402173914</v>
+      </c>
+      <c r="G92" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H92" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="I92" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="5" t="n">
+        <v>88</v>
+      </c>
+      <c r="B93" s="5" t="inlineStr">
+        <is>
+          <t>Macedonia</t>
+        </is>
+      </c>
+      <c r="C93" s="12" t="n">
+        <v>91634</v>
+      </c>
+      <c r="D93" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F93" s="14" t="n">
+        <v>0.008315690682497762</v>
+      </c>
+      <c r="G93" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H93" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I93" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="5" t="n">
+        <v>89</v>
+      </c>
+      <c r="B94" s="5" t="inlineStr">
+        <is>
+          <t>Sint Maarten</t>
+        </is>
+      </c>
+      <c r="C94" s="12" t="n">
+        <v>86424</v>
+      </c>
+      <c r="D94" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E94" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F94" s="14" t="n">
+        <v>0.006074701471813385</v>
+      </c>
+      <c r="G94" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H94" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I94" s="11" t="inlineStr">
         <is>
           <t>Sin Conversión</t>
         </is>

--- a/rates-nodispo/week-20/Analisis_Rates_NoDispo_OP_7d.xlsx
+++ b/rates-nodispo/week-20/Analisis_Rates_NoDispo_OP_7d.xlsx
@@ -547,7 +547,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -861,7 +861,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -5969,7 +5969,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -9964,7 +9964,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14567,7 +14567,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -17670,7 +17670,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -21263,7 +21263,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>

--- a/rates-nodispo/week-20/Analisis_Rates_NoDispo_OP_7d.xlsx
+++ b/rates-nodispo/week-20/Analisis_Rates_NoDispo_OP_7d.xlsx
@@ -547,7 +547,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -861,7 +861,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -5969,7 +5969,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -9964,7 +9964,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14567,7 +14567,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -17670,7 +17670,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -21263,7 +21263,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
